--- a/Result/checksun_type/BIOS(嵌入式軟體).xlsx
+++ b/Result/checksun_type/BIOS(嵌入式軟體).xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>206.8</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>215.12</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>237.84</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>215.12</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>237.84</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>59465.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>54361.6</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>54361.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>70589.7</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>276431.3</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>276431.3</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-14273.87243999919</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>59465</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>59465.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>205.1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>216.28</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>238.68</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>216.28</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>238.68</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>38591.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>57238.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>57238.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>70722.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>281990.78</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>281990.78</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-15428.45781172665</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>38591</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>38591.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>203.5</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>217.82</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>239.69</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>217.82</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>239.69</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>47503.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>84958.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>84958.60000000001</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>77969.6</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>288892.24</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>288892.24</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-14290.34913520422</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>47503</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>47503.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>204.3</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>219.28</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>240.77</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>219.28</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>240.77</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>61758.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>86506.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>86506.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>85538.9</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>301535.26</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>301535.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-13108.9671282006</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>61758</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>61758.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>205.7</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>221.08</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>241.89</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>221.08</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>241.89</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>64491.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>90477.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>90477.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>88643.0</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>317572.5</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>317572.5</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-12480.42257790257</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>64491</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>64491.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>207.5</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>223.02</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>242.66</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>223.02</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>242.66</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>73849.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>86817.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>86817.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>96316.6</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>323072.36</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>323072.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-11429.59384255171</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>73849</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>73849.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>210.6</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>224.92</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>243.61</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>224.92</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>243.61</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>177192.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>84206.6</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>84206.60000000001</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>106919.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>338311.64</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>338311.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-10522.85301195935</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>177192</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>177192.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>213.5</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>226.35</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>244.5</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>226.35</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>244.5</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>55241.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>70980.6</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>70980.60000000001</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>99206.7</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>340311.4</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>340311.4</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-19924.15707497171</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>55241</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>55241.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>215.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>227.22</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>245.03</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>227.22</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>245.03</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>81613.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>84571.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>84571.60000000001</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>99505.5</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>348722.44</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>348722.44</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-19576.83584088321</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>81613</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>81613.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>219.6</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>228.62</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>245.41</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>228.62</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>245.41</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>46194.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>86808.8</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>86808.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>98116.2</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>350258.8</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>350258.8</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-21207.0613692967</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>46194</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>46194.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>222.5</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>229.6</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>245.83</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>229.6</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>245.83</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>60793.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>105815.4</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>105815.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>109142.4</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>353008.04</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>353008.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-18983.66707526967</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>60793</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>60793.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>54.66</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>53.32</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>149413.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>217717.0</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>217717</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>367044.8</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>237158.66</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>237158.66</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-21084.67091178865</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>149413</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>149413.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>56.04</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>52.92</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>49.09</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>52.92</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>49.09</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>216732.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>231160.8</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>231160.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>420206.6</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>235339.22</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>235339.22</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-10587.49947517022</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>216732</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>216732.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>57.18000000000001</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>52.64</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>48.75</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>52.64</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>48.75</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>221658.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>259217.6</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>259217.6</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>453682.5</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>233052.36</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>233052.36</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-2426.165298745036</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>221658</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>221658.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>58.98</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>52.53</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>48.48</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>52.53</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>48.48</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>301588.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>336883.6</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>336883.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>450728.0</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>229641.16</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>229641.16</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>8791.746571103286</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>301588</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>301588.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>60.52</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>52.4</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>48.2</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>52.4</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>48.2</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>199194.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>396703.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>396703.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>425530.3</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>224069.9</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>224069.9</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>15939.41543620441</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>199194</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>199194.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>60.77999999999999</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>51.93</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>47.8</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>51.93</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>47.8</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>216632.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>516372.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>516372.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>418795.8</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>220937.42</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>220937.42</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>36551.8918350559</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>216632</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>216632.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>60.38</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>51.44</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>51.44</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>47.4</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>357016.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>609252.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>609252.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>418153.5</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>218290.42</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>218290.42</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>62824.50483930594</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>357016</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>357016.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>46.95</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>50.92</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>46.95</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>609988.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>648147.4</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>648147.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>393131.5</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>212611.62</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>212611.62</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>83071.93395825941</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>609988</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>609988.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>55.94</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>50.29</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>46.43</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>50.29</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>46.43</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>600689.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>564572.4</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>564572.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>357656.0</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>201223.44</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>201223.44</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>81925.83505825518</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>600689</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>600689.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>53.16</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>49.91</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>45.95</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>797538.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>454356.8</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>454356.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>315081.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>191580.74</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>191580.74</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>78358.94966331136</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>797538</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>797538.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>50.62</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>49.55</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>45.52</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>49.55</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>45.52</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>681031.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>321219.0</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>321219</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>255754.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>176809.8</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>176809.8</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>49373.9008968448</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>681031</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>681031.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>586.6</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>636.0</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>667.3</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>636</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>667.3</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>2251806679.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>2845492684.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>2845492684.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>3254023064.0</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>2250939639.92</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>2250939639.92</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>80988449.20909452</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>2251806679</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>2251806679.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>577.4</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>640.85</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>668.88</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>640.85</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>668.88</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>2303990317.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>2895931468.2</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>2895931468.2</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>3423927956.4</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>2313304958.2</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>2313304958.2</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>168000892.6023631</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>2303990317</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>2303990317.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>572.0</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>646.8</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>670.44</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>646.8</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>670.4400000000001</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>4282414081.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>3701315712.0</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>3701315712</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>3406103963.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>2315429027.54</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>2315429027.54</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>280713247.2140913</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>4282414081</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>4282414081.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>577.0</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>653.25</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>671.96</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>653.25</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>671.96</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>3277325446.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>3639148367.2</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>3639148367.2</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>3149911827.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>2279747515.3</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>2279747515.3</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>219731448.8303423</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>3277325446</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>3277325446.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>589.0</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>659.5</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>673.4</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>659.5</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>673.4</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>2111926901.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>3434438489.8</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>3434438489.8</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>3061336173.2</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>2234436035.54</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>2234436035.54</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>232455110.2881894</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>2111926901</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>2111926901.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>601.0</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>665.8</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>674.84</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>665.8</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>674.84</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>2504000596.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>3662553443.2</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>3662553443.2</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>3053660242.7</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>2215412102.28</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>2215412102.28</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>367193931.1105347</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>2504000596</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>2504000596.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>617.2</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>672.05</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>676.22</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>672.05</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>676.22</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>6330911536.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>3951924444.6</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>3951924444.6</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>3034497195.4</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>2193079344.64</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>2193079344.64</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>504555995.9956522</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>6330911536</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>6330911536.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>636.8</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>678.2</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>677.46</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>678.2</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>677.46</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>3971577357.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>3110892215.0</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>3110892215</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>2577610128.3</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>2089597881.18</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>2089597881.18</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>272741488.1174035</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>3971577357</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>3971577357.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>647.4</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>681.95</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>677.64</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>681.95</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>677.64</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>2253776059.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>2660675287.2</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>2660675287.2</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>2395309044.8</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>2031062259.28</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>2031062259.28</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>184622942.8942842</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>2253776059</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>2253776059.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>653.6</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>684.55</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>677.36</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>684.55</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>677.36</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>3252501668.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>2688233856.6</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>2688233856.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>2353124375.3</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>2012331643.46</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>2012331643.46</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>236195769.4007463</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>3252501668</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>3252501668.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>663.2</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>687.1</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>677.34</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>687.1</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>677.34</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>3950855603.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>2444767042.2</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>2444767042.2</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>2195634921.6</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>1973519631.2</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>1973519631.2</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>194429357.3956661</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>3950855603</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>3950855603.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>

--- a/Result/checksun_type/BIOS(嵌入式軟體).xlsx
+++ b/Result/checksun_type/BIOS(嵌入式軟體).xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>536.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-11.05</t>
+          <t>-4.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>36.11</t>
+          <t>44.44</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>1.13</v>
+        <v>0.47</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.92</v>
+        <v>0.99</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-7.58</t>
+          <t>-7.32</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>212.1</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>210.18</v>
+        <v>209.92</v>
       </c>
       <c r="AN2" t="n">
-        <v>227.41</v>
+        <v>226.5</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>234.38</t>
+          <t>234.11</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>30.54</t>
+          <t>32.01</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>-3.65</v>
+        <v>-3.31</v>
       </c>
       <c r="AR2" t="n">
-        <v>-5.25</v>
+        <v>-4.86</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-114.66</t>
+          <t>-113.57</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>115859.0</t>
+          <t>46536.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>56948.2</v>
+        <v>59923.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>64026.0</t>
+          <t>62733.1</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>123191.08</v>
+        <v>118718.8</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-7077</t>
+          <t>-2809</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-9938.261820763471</t>
+          <t>-9055.389670082863</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-2954.263679330266</t>
+          <t>-4199.592841339516</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>115859.0</t>
+          <t>46536.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>221.0</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>209.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>254.0</t>
+          <t>536.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-22.37</t>
+          <t>-11.05</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-18.57</t>
+          <t>-17.02</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>6.98</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,66 +1436,66 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>8.33</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>36.11</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.71</v>
+        <v>1.13</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-7.97</t>
+          <t>-7.58</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>212.1</t>
         </is>
       </c>
       <c r="AM3" t="n">
         <v>210.18</v>
       </c>
       <c r="AN3" t="n">
-        <v>228.37</v>
+        <v>227.41</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>234.6</t>
+          <t>234.38</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>30.54</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>-4.19</v>
+        <v>-3.65</v>
       </c>
       <c r="AR3" t="n">
-        <v>-5.66</v>
+        <v>-5.25</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-115.77</t>
+          <t>-114.66</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>53321.0</t>
+          <t>115859.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>43704.6</v>
+        <v>56948.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>56299.2</t>
+          <t>64026.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>130190.5</v>
+        <v>123191.08</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-12594</t>
+          <t>-7077</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-11208.07966466042</t>
+          <t>-9938.261820763471</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-8497.1768879124</t>
+          <t>-2954.263679330266</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>53321.0</t>
+          <t>115859.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>-18.57</t>
+          <t>-17.02</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>221.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>211.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>206.0</t>
+          <t>254.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>17.96</t>
+          <t>-22.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-18.76</t>
+          <t>-18.57</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,66 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>52.59</t>
+          <t>27.78</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-1.45</v>
+        <v>-0.71</v>
       </c>
       <c r="AI4" t="n">
-        <v>1.15</v>
+        <v>0.87</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-8.25</t>
+          <t>-7.97</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>213.1</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>210.68</v>
+        <v>210.18</v>
       </c>
       <c r="AN4" t="n">
-        <v>229.61</v>
+        <v>228.37</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>234.8</t>
+          <t>234.6</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>26.90</t>
+          <t>25.98</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>-4.4</v>
+        <v>-4.19</v>
       </c>
       <c r="AR4" t="n">
-        <v>-6.02</v>
+        <v>-5.66</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-116.80</t>
+          <t>-115.77</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>43186.0</t>
+          <t>53321.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>65726.60000000001</v>
+        <v>43704.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>55717.4</t>
+          <t>56299.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>153664.32</v>
+        <v>130190.5</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>10009</t>
+          <t>-12594</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-11700.9710786146</t>
+          <t>-11208.07966466042</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-9411.65372560428</t>
+          <t>-8497.1768879124</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>43186.0</t>
+          <t>53321.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>-18.76</t>
+          <t>-18.57</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,7 +2037,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2107,17 +2107,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>207.0</t>
+          <t>208.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>206.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>14.68</t>
+          <t>17.96</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-17.99</t>
+          <t>-18.76</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-0.69</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>72.99</t>
+          <t>52.59</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.8</v>
+        <v>-1.45</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.15</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-8.39</t>
+          <t>-8.25</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>213.7</t>
+          <t>213.1</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>211.7</v>
+        <v>210.68</v>
       </c>
       <c r="AN5" t="n">
-        <v>231.09</v>
+        <v>229.61</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>235.01</t>
+          <t>234.8</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>26.90</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>-4.56</v>
+        <v>-4.4</v>
       </c>
       <c r="AR5" t="n">
-        <v>-6.43</v>
+        <v>-6.02</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-117.93</t>
+          <t>-116.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>40717.0</t>
+          <t>43186.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>66026.60000000001</v>
+        <v>65726.60000000001</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>57574.6</t>
+          <t>55717.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>166299.48</v>
+        <v>153664.32</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>10009</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-12117.21059734375</t>
+          <t>-11700.9710786146</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-9296.025860678237</t>
+          <t>-9411.65372560428</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>40717.0</t>
+          <t>43186.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>-17.99</t>
+          <t>-18.76</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2469,12 +2469,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.18</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
+          <t>207.0</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>210.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>212.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>148.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.32</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-17.41</t>
+          <t>-17.99</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>82.76</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>89.66</t>
+          <t>72.99</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.05</v>
+        <v>-0.8</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-8.57</t>
+          <t>-8.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-1.18</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>213.4</t>
+          <t>213.7</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>212.55</v>
+        <v>211.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>232.47</v>
+        <v>231.09</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>235.25</t>
+          <t>235.01</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>28.81</t>
+          <t>28.99</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>-4.91</v>
+        <v>-4.56</v>
       </c>
       <c r="AR6" t="n">
-        <v>-6.89</v>
+        <v>-6.43</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-119.23</t>
+          <t>-117.93</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>31658.0</t>
+          <t>40717.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>65542.39999999999</v>
+        <v>66026.60000000001</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>59952.0</t>
+          <t>57574.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>210730.9</v>
+        <v>166299.48</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>5590</t>
+          <t>8452</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-12630.15327673748</t>
+          <t>-12117.21059734375</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-8534.306558616809</t>
+          <t>-9296.025860678237</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>31658.0</t>
+          <t>40717.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>-17.41</t>
+          <t>-17.99</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>9.18</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>216.0</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>216.0</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>212.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>232.0</t>
+          <t>148.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>9.32</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>-17.41</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.63</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,66 +3124,66 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>86.21</t>
+          <t>82.76</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>89.66</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.52</v>
+        <v>0.05</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.06</v>
+        <v>0.4</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-9.07</t>
+          <t>-8.57</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>212.9</t>
+          <t>213.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>212.78</v>
+        <v>212.55</v>
       </c>
       <c r="AN7" t="n">
-        <v>234</v>
+        <v>232.47</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>235.48</t>
+          <t>235.25</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>26.57</t>
+          <t>28.81</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>-5.43</v>
+        <v>-4.91</v>
       </c>
       <c r="AR7" t="n">
-        <v>-7.39</v>
+        <v>-6.89</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-120.61</t>
+          <t>-119.23</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>49641.0</t>
+          <t>31658.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>71103.8</v>
+        <v>65542.39999999999</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>64171.1</t>
+          <t>59952.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>241470</v>
+        <v>210730.9</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>5590</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-13374.85268003215</t>
+          <t>-12630.15327673748</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-6170.732321435586</t>
+          <t>-8534.306558616809</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>49641.0</t>
+          <t>31658.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>-17.41</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>217.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>219.0</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
@@ -3383,7 +3383,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>743.0</t>
+          <t>232.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.47</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-10.44</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-16.44</t>
+          <t>-17.21</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.67</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-1.63</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>86.21</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>95.83</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>2.03</v>
+        <v>0.52</v>
       </c>
       <c r="AI8" t="n">
-        <v>-0.66</v>
+        <v>0.06</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-9.43</t>
+          <t>-9.07</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>211.7</t>
+          <t>212.9</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>213.1</v>
+        <v>212.78</v>
       </c>
       <c r="AN8" t="n">
-        <v>235.29</v>
+        <v>234</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>235.74</t>
+          <t>235.48</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>26.57</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>-6.06</v>
+        <v>-5.43</v>
       </c>
       <c r="AR8" t="n">
-        <v>-7.88</v>
+        <v>-7.39</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-121.98</t>
+          <t>-120.61</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>163431.0</t>
+          <t>49641.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>68893.8</v>
+        <v>71103.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>76926.2</t>
+          <t>64171.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>266979.36</v>
+        <v>241470</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-8032</t>
+          <t>6932</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-14684.69274523153</t>
+          <t>-13374.85268003215</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-4500.564399696857</t>
+          <t>-6170.732321435586</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>163431.0</t>
+          <t>49641.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>-16.44</t>
+          <t>-17.21</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.35</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>217.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>219.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>212.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>743.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>-1.41</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-10.44</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-16.44</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>9.67</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,51 +3983,51 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>93.06</t>
+          <t>95.83</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>1.38</v>
+        <v>2.03</v>
       </c>
       <c r="AI9" t="n">
-        <v>-1.67</v>
+        <v>-0.66</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-9.43</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>-0.19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>210.1</t>
+          <t>211.7</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>213.68</v>
+        <v>213.1</v>
       </c>
       <c r="AN9" t="n">
-        <v>236.13</v>
+        <v>235.29</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>236.07</t>
+          <t>235.74</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>16.17</t>
+          <t>23.08</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>-6.99</v>
+        <v>-6.06</v>
       </c>
       <c r="AR9" t="n">
-        <v>-8.34</v>
+        <v>-7.88</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-123.25</t>
+          <t>-121.98</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>44686.0</t>
+          <t>163431.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>45708.2</v>
+        <v>68893.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>66107.2</t>
+          <t>76926.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>269192.12</v>
+        <v>266979.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-20399</t>
+          <t>-8032</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-16536.35244441965</t>
+          <t>-14684.69274523153</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-14145.66149722379</t>
+          <t>-4500.564399696857</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>44686.0</t>
+          <t>163431.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-16.44</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>9.35</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>225.5</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>215.0</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>210.5</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>1.19</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>181.0</t>
+          <t>209.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-29.62</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-18.57</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,66 +4390,66 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>78.11</t>
+          <t>93.06</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="AI10" t="n">
-        <v>-3.09</v>
+        <v>-1.67</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-9.48</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>207.8</t>
+          <t>210.1</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>214.42</v>
+        <v>213.68</v>
       </c>
       <c r="AN10" t="n">
-        <v>236.89</v>
+        <v>236.13</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>236.16</t>
+          <t>236.07</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>16.17</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>-7.76</v>
+        <v>-6.99</v>
       </c>
       <c r="AR10" t="n">
-        <v>-8.67</v>
+        <v>-8.34</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-124.19</t>
+          <t>-123.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>38296.0</t>
+          <t>44686.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>49122.6</v>
+        <v>45708.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>69799.9</t>
+          <t>66107.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>273535.92</v>
+        <v>269192.12</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-20677</t>
+          <t>-20399</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-16971.02352572799</t>
+          <t>-16536.35244441965</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-14696.49086878997</t>
+          <t>-14145.66149722379</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>38296.0</t>
+          <t>44686.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>-18.57</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>215.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>280.0</t>
+          <t>181.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.99</t>
+          <t>-29.62</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-18.57</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,66 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>63.76</t>
+          <t>78.11</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>2.03</v>
+        <v>1.3</v>
       </c>
       <c r="AI11" t="n">
-        <v>-3.87</v>
+        <v>-3.09</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-9.55</t>
+          <t>-9.48</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>206.8</t>
+          <t>207.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>215.12</v>
+        <v>214.42</v>
       </c>
       <c r="AN11" t="n">
-        <v>237.84</v>
+        <v>236.89</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>236.31</t>
+          <t>236.16</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>5.80</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>-8.380000000000001</v>
+        <v>-7.76</v>
       </c>
       <c r="AR11" t="n">
-        <v>-8.9</v>
+        <v>-8.67</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-124.83</t>
+          <t>-124.19</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>59465.0</t>
+          <t>38296.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>54361.6</v>
+        <v>49122.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>70589.7</t>
+          <t>69799.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>276431.3</v>
+        <v>273535.92</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-16228</t>
+          <t>-20677</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-17384.57491789854</t>
+          <t>-16971.02352572799</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-14273.87243999919</t>
+          <t>-14696.49086878997</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>59465.0</t>
+          <t>38296.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>-18.38</t>
+          <t>-18.57</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>9.11</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>213.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>211.0</t>
+          <t>210.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,42 +5103,42 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>280.0</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>211.0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>184.0</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>208.0</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>3.03</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.07</t>
+          <t>-22.99</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-19.54</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>3.64</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,66 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>220</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>55.17</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>35.98</t>
+          <t>63.76</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>1.41</v>
+        <v>2.03</v>
       </c>
       <c r="AI12" t="n">
-        <v>-5.17</v>
+        <v>-3.87</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>-9.39</t>
+          <t>-9.55</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>205.1</t>
+          <t>206.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>216.28</v>
+        <v>215.12</v>
       </c>
       <c r="AN12" t="n">
-        <v>238.68</v>
+        <v>237.84</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>236.39</t>
+          <t>236.31</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>5.80</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>-9.109999999999999</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="AR12" t="n">
-        <v>-9.029999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-125.19</t>
+          <t>-124.83</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>658192.7372881356</t>
+          <t>657362.8519040903</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>38591.0</t>
+          <t>59465.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>57238.4</v>
+        <v>54361.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>70722.5</t>
+          <t>70589.7</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>281990.78</v>
+        <v>276431.3</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-13484</t>
+          <t>-16228</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-17950.15718660751</t>
+          <t>-17384.57491789854</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-15428.45781172665</t>
+          <t>-14273.87243999919</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>38591.0</t>
+          <t>59465.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>-19.54</t>
+          <t>-18.38</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>3.05</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>32.45</t>
+          <t>32.22</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>22.09</t>
+          <t>21.9</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>209.5</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>214.5</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>209.5</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>211.0</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>211.5</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>207.5</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>208.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2941.0</t>
+          <t>9561.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>13.55</t>
+          <t>39.73</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5635,17 +5635,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>24.44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>5.70</t>
+          <t>6.90</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5656,12 +5656,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5671,51 +5671,51 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>64.44</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AH13" t="n">
-        <v>3.29</v>
+        <v>2.45</v>
       </c>
       <c r="AI13" t="n">
-        <v>-1.33</v>
+        <v>-0.55</v>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>10.59</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>55.86</t>
+          <t>56.32000000000001</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>56.62</v>
+        <v>56.63</v>
       </c>
       <c r="AN13" t="n">
-        <v>52.35</v>
+        <v>52.65</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>47.39</t>
+          <t>47.61</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-15.49</t>
+          <t>-7.03</t>
         </is>
       </c>
       <c r="AQ13" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AR13" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-64.57</t>
+          <t>-65.18</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5734,43 +5734,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>80777.21610169491</t>
+          <t>81797.06276445698</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>164067.0</t>
+          <t>535899.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>138725.8</v>
+        <v>224720.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>122176.0</t>
+          <t>160824.6</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>245378.5</v>
+        <v>252918.68</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>16549</t>
+          <t>63895</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-24740.96059752061</t>
+          <t>-20182.63207101842</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-27545.18399029595</t>
+          <t>4888.174824743648</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>164067.0</t>
+          <t>535899.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5835,12 +5835,12 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -5900,17 +5900,17 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>54.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>58.6</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>53.2</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -5947,12 +5947,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1960.0</t>
+          <t>2941.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -5972,17 +5972,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>13.55</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>2.61</t>
+          <t>7.45</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6057,17 +6057,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.01</t>
+          <t>7.52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>5.70</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6078,17 +6078,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>57.78</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6097,47 +6097,47 @@
         </is>
       </c>
       <c r="AH14" t="n">
-        <v>-0.4</v>
+        <v>3.29</v>
       </c>
       <c r="AI14" t="n">
-        <v>-1.88</v>
+        <v>-1.33</v>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>8.37</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>10.47</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>55.32000000000001</t>
+          <t>55.86</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>56.38</v>
+        <v>56.62</v>
       </c>
       <c r="AN14" t="n">
-        <v>52.03</v>
+        <v>52.35</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>47.16</t>
+          <t>47.39</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-28.26</t>
+          <t>-15.49</t>
         </is>
       </c>
       <c r="AQ14" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AR14" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-63.20</t>
+          <t>-64.57</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6156,43 +6156,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>80777.21610169491</t>
+          <t>81797.06276445698</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>108797.0</t>
+          <t>164067.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>120772.4</v>
+        <v>138725.8</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>127442.5</t>
+          <t>122176.0</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>244402.24</v>
+        <v>245378.5</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-6670</t>
+          <t>16549</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-24231.10179883419</t>
+          <t>-24740.96059752061</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-33055.65429784195</t>
+          <t>-27545.18399029595</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>108797.0</t>
+          <t>164067.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>42.56</t>
+          <t>49.29</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6322,22 +6322,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>56.6</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>54.4</t>
+          <t>54.5</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>57.7</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6369,12 +6369,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-5.1</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2946.0</t>
+          <t>1960.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6394,17 +6394,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>6.24</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-19.71</t>
+          <t>-5.23</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>2.61</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6479,17 +6479,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>5.01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.99</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6500,266 +6500,266 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>35.56</t>
+          <t>57.78</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>78.52</t>
+          <t>64.44</t>
         </is>
       </c>
       <c r="AH15" t="n">
-        <v>-1.81</v>
+        <v>-0.4</v>
       </c>
       <c r="AI15" t="n">
-        <v>-1.67</v>
+        <v>-1.88</v>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>8.37</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>10.17</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
+          <t>55.32000000000001</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>56.38</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>52.03</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>47.16</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-28.26</t>
+        </is>
+      </c>
+      <c r="AQ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>3.8</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-63.20</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/11/12</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>81797.06276445698</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>108797.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>120772.4</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>127442.5</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>244402.24</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>-6670</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-24231.10179883419</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-33055.65429784195</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>108797.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>38.65</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/08/08</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>42.56</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>鑫聯大投控</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>鑫聯大投控</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上櫃</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-4.142025122335156</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>31.9210612054922</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>52.5841306079603</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>77.26</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>13.39</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>6.00%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>3.30%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>49.76</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>7245</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>電腦,零組件及週邊設備99.30%、其他勞務0.70% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>鑫聯大投控-電腦及週邊設備業-上櫃</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>電腦及週邊設備業右上上櫃</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>55.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>56.6</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>54.4</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
           <t>55.1</t>
-        </is>
-      </c>
-      <c r="AM15" t="n">
-        <v>56.03</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>51.75</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>46.97</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-27.74</t>
-        </is>
-      </c>
-      <c r="AQ15" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>3.8</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-60.60</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/11/12</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>80777.21610169491</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>163163.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>111391.4</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>138728.6</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>244385.46</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>-27337</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-22626.6377081055</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-33825.40994084187</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>163163.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>38.65</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/08/08</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>39.97</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>鑫聯大投控</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>鑫聯大投控</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上櫃</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.97</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-4.142025122335156</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>31.9210612054922</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>52.5841306079603</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>2.16</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>77.26</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>13.39</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>6.00%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>3.30%</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>49.86</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>7245</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>電腦,零組件及週邊設備99.30%、其他勞務0.70% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>鑫聯大投控-電腦及週邊設備業-上櫃</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>電腦及週邊設備業右上上櫃</t>
-        </is>
-      </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>56.9</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>57.0</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>53.9</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>54.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6791,12 +6791,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2.9</t>
+          <t>-5.1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2713.0</t>
+          <t>2946.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6816,17 +6816,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>6.24</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-35.58</t>
+          <t>-19.71</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>6.15</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.93</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>-4.99</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6922,66 +6922,66 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.56</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>78.52</t>
         </is>
       </c>
       <c r="AH16" t="n">
-        <v>3.26</v>
+        <v>-1.81</v>
       </c>
       <c r="AI16" t="n">
-        <v>-0.85</v>
+        <v>-1.67</v>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>10.09</t>
+          <t>10.17</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>55.2</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>55.68</v>
+        <v>56.03</v>
       </c>
       <c r="AN16" t="n">
-        <v>51.47</v>
+        <v>51.75</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>46.75</t>
+          <t>46.97</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-20.78</t>
+          <t>-27.74</t>
         </is>
       </c>
       <c r="AQ16" t="n">
-        <v>1.27</v>
+        <v>1.08</v>
       </c>
       <c r="AR16" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
@@ -6990,7 +6990,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-57.86</t>
+          <t>-60.60</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7000,43 +7000,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>80777.21610169491</t>
+          <t>81797.06276445698</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>151676.0</t>
+          <t>163163.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>98285.39999999999</v>
+        <v>111391.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>152571.1</t>
+          <t>138728.6</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>243137.32</v>
+        <v>244385.46</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-54285</t>
+          <t>-27337</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-20590.49730215344</t>
+          <t>-22626.6377081055</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-39541.93907581174</t>
+          <t>-33825.40994084187</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>151676.0</t>
+          <t>163163.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>47.48</t>
+          <t>39.97</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7101,17 +7101,17 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7166,22 +7166,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>53.7</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7213,12 +7213,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1902.0</t>
+          <t>2713.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7228,7 +7228,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7238,17 +7238,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>3.99</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-38.39</t>
+          <t>-35.58</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>6.15</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7323,17 +7323,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>6.93</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.26</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7344,12 +7344,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7359,51 +7359,51 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>53.4</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH17" t="n">
-        <v>1.17</v>
+        <v>3.26</v>
       </c>
       <c r="AI17" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.85</v>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>7.98</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>10.09</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>54.76000000000001</t>
+          <t>55.2</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>55.2</v>
+        <v>55.68</v>
       </c>
       <c r="AN17" t="n">
-        <v>51.12</v>
+        <v>51.47</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>46.52</t>
+          <t>46.75</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-29.20</t>
+          <t>-20.78</t>
         </is>
       </c>
       <c r="AQ17" t="n">
-        <v>1.19</v>
+        <v>1.27</v>
       </c>
       <c r="AR17" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-55.67</t>
+          <t>-57.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7422,43 +7422,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>80777.21610169491</t>
+          <t>81797.06276445698</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>105926.0</t>
+          <t>151676.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>96928.8</v>
+        <v>98285.39999999999</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>157322.9</t>
+          <t>152571.1</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>242300</v>
+        <v>243137.32</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-60394</t>
+          <t>-54285</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-17144.78061603374</t>
+          <t>-20590.49730215344</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-45065.44715877538</t>
+          <t>-39541.93907581174</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>105926.0</t>
+          <t>151676.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7478,7 +7478,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>47.48</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7523,17 +7523,17 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7593,17 +7593,17 @@
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>56.4</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>53.7</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>55.4</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7635,12 +7635,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>1352.0</t>
+          <t>1902.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7650,7 +7650,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7660,17 +7660,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>3.99</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-37.27</t>
+          <t>-38.39</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7735,7 +7735,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7745,17 +7745,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>-1.26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7766,66 +7766,66 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>28.6</t>
+          <t>53.4</t>
         </is>
       </c>
       <c r="AH18" t="n">
-        <v>1.51</v>
+        <v>1.17</v>
       </c>
       <c r="AI18" t="n">
-        <v>-1.26</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>8.0</t>
+          <t>7.98</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.89</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>54.18000000000001</t>
+          <t>54.76000000000001</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>54.87</v>
+        <v>55.2</v>
       </c>
       <c r="AN18" t="n">
-        <v>50.8</v>
+        <v>51.12</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>46.52</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-31.31</t>
+          <t>-29.20</t>
         </is>
       </c>
       <c r="AQ18" t="n">
-        <v>1.24</v>
+        <v>1.19</v>
       </c>
       <c r="AR18" t="n">
-        <v>1.81</v>
+        <v>1.68</v>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-52.44</t>
+          <t>-55.67</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7844,43 +7844,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>80777.21610169491</t>
+          <t>81797.06276445698</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>74300.0</t>
+          <t>105926.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>105626.2</v>
+        <v>96928.8</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>168393.5</t>
+          <t>157322.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>242999.08</v>
+        <v>242300</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-62767</t>
+          <t>-60394</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-12068.29579008071</t>
+          <t>-17144.78061603374</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-46444.90702162433</t>
+          <t>-45065.44715877538</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>74300.0</t>
+          <t>105926.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -7945,7 +7945,7 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|晨星</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -7955,7 +7955,7 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8010,22 +8010,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>56.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>55.4</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8057,12 +8057,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1130.0</t>
+          <t>1352.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8082,17 +8082,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6.41</t>
+          <t>4.68</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-31.81</t>
+          <t>-37.27</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8157,7 +8157,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8167,17 +8167,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>2.89</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.89</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8188,38 +8188,38 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>21.74</t>
+          <t>38.46</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>23.3</t>
+          <t>28.6</t>
         </is>
       </c>
       <c r="AH19" t="n">
-        <v>-0.33</v>
+        <v>1.51</v>
       </c>
       <c r="AI19" t="n">
-        <v>-0.58</v>
+        <v>-1.26</v>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>8.0</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>9.48</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
@@ -8228,26 +8228,26 @@
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>54.49</v>
+        <v>54.87</v>
       </c>
       <c r="AN19" t="n">
-        <v>50.46</v>
+        <v>50.8</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>46.09</t>
+          <t>46.31</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-31.93</t>
+          <t>-31.31</t>
         </is>
       </c>
       <c r="AQ19" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AR19" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-48.72</t>
+          <t>-52.44</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8266,43 +8266,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>80777.21610169491</t>
+          <t>81797.06276445698</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>61892.0</t>
+          <t>74300.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>134112.6</v>
+        <v>105626.2</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>196665.1</t>
+          <t>168393.5</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>241817.16</v>
+        <v>242999.08</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-62552</t>
+          <t>-62767</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-5818.002838890967</t>
+          <t>-12068.29579008071</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-43368.31728920765</t>
+          <t>-46444.90702162433</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>61892.0</t>
+          <t>74300.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>42.30</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8367,7 +8367,7 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -8377,7 +8377,7 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8437,17 +8437,17 @@
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>56.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>54.3</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>54.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8479,12 +8479,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1771.0</t>
+          <t>1130.0</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8504,17 +8504,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>5.37</t>
+          <t>6.41</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-33.96</t>
+          <t>-31.81</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8589,17 +8589,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>2.89</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-3.89</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8610,66 +8610,66 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>21.74</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>16.05</t>
+          <t>23.3</t>
         </is>
       </c>
       <c r="AH20" t="n">
-        <v>0.89</v>
+        <v>-0.33</v>
       </c>
       <c r="AI20" t="n">
-        <v>-0.09</v>
+        <v>-0.58</v>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>8.08</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>9.48</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>54.12</t>
+          <t>54.18000000000001</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>54.17</v>
+        <v>54.49</v>
       </c>
       <c r="AN20" t="n">
-        <v>50.12</v>
+        <v>50.46</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>45.88</t>
+          <t>46.09</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-27.89</t>
+          <t>-31.93</t>
         </is>
       </c>
       <c r="AQ20" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AR20" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-44.62</t>
+          <t>-48.72</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8688,43 +8688,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>80777.21610169491</t>
+          <t>81797.06276445698</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>97633.0</t>
+          <t>61892.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>166065.8</v>
+        <v>134112.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>251474.7</t>
+          <t>196665.1</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>241154.9</v>
+        <v>241817.16</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-85408</t>
+          <t>-62552</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>1009.327061166613</t>
+          <t>-5818.002838890967</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-36094.89205399787</t>
+          <t>-43368.31728920765</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>97633.0</t>
+          <t>61892.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8744,7 +8744,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>39.72</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.16</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8829,7 +8829,7 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -8854,22 +8854,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>56.0</t>
+          <t>55.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>56.1</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>54.1</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>54.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -8901,12 +8901,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2660.0</t>
+          <t>1771.0</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8916,7 +8916,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8926,17 +8926,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>5.03</t>
+          <t>5.37</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-31.45</t>
+          <t>-33.96</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9001,7 +9001,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9011,17 +9011,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.80</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9032,66 +9032,66 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>25.61</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>14.11</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="AH21" t="n">
-        <v>1.82</v>
+        <v>0.89</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>8.08</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>9.24</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>53.82000000000001</t>
+          <t>54.12</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>53.79</v>
+        <v>54.17</v>
       </c>
       <c r="AN21" t="n">
-        <v>49.76</v>
+        <v>50.12</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>45.67</t>
+          <t>45.88</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-25.44</t>
+          <t>-27.89</t>
         </is>
       </c>
       <c r="AQ21" t="n">
-        <v>1.68</v>
+        <v>1.52</v>
       </c>
       <c r="AR21" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
@@ -9100,7 +9100,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-40.76</t>
+          <t>-44.62</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9110,43 +9110,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>80777.21610169491</t>
+          <t>81797.06276445698</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>144893.0</t>
+          <t>97633.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>206856.8</v>
+        <v>166065.8</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>301780.3</t>
+          <t>251474.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>239526.02</v>
+        <v>241154.9</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-94923</t>
+          <t>-85408</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>7755.548718469247</t>
+          <t>1009.327061166613</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-28244.57414462682</t>
+          <t>-36094.89205399787</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>144893.0</t>
+          <t>97633.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>41.79</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9211,7 +9211,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9251,7 +9251,7 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>56.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>55.6</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>52.8</t>
+          <t>54.1</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>54.8</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9323,12 +9323,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-4.52</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2793.0</t>
+          <t>2660.0</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9348,17 +9348,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>5.03</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-40.68</t>
+          <t>-31.45</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9423,7 +9423,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9433,17 +9433,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>6.80</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-5.71</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9454,66 +9454,66 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>8.68</t>
+          <t>14.11</t>
         </is>
       </c>
       <c r="AH22" t="n">
-        <v>-3.95</v>
+        <v>1.82</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.51</v>
+        <v>0.06</v>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>7.92</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>8.73</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>53.82000000000001</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>53.32</v>
+        <v>53.79</v>
       </c>
       <c r="AN22" t="n">
-        <v>49.41</v>
+        <v>49.76</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>45.44</t>
+          <t>45.67</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-23.21</t>
+          <t>-25.44</t>
         </is>
       </c>
       <c r="AQ22" t="n">
-        <v>1.84</v>
+        <v>1.68</v>
       </c>
       <c r="AR22" t="n">
-        <v>2.39</v>
+        <v>2.25</v>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
@@ -9522,7 +9522,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-36.99</t>
+          <t>-40.76</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9532,43 +9532,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>80777.21610169491</t>
+          <t>81797.06276445698</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>217717</v>
+        <v>206856.8</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>367044.8</t>
+          <t>301780.3</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>237158.66</v>
+        <v>239526.02</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-149327</t>
+          <t>-94923</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>14301.02560266853</t>
+          <t>7755.548718469247</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-21084.67091178865</t>
+          <t>-28244.57414462682</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>149413.0</t>
+          <t>144893.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9588,7 +9588,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>35.83</t>
+          <t>41.79</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9643,7 +9643,7 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9673,7 +9673,7 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9698,22 +9698,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>55.7</t>
+          <t>55.6</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>52.3</t>
+          <t>52.8</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>52.5</t>
+          <t>54.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9745,12 +9745,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>-4.52</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3922.0</t>
+          <t>2793.0</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9770,17 +9770,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4.68</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-0.49</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-44.99</t>
+          <t>-40.68</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9845,7 +9845,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -9855,17 +9855,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.03</t>
+          <t>7.14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-5.71</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -9876,66 +9876,66 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>9561</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>9.02</t>
+          <t>8.68</t>
         </is>
       </c>
       <c r="AH23" t="n">
-        <v>-1.86</v>
+        <v>-3.95</v>
       </c>
       <c r="AI23" t="n">
-        <v>5.9</v>
+        <v>2.51</v>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>56.04</t>
+          <t>54.66</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>52.92</v>
+        <v>53.32</v>
       </c>
       <c r="AN23" t="n">
-        <v>49.09</v>
+        <v>49.41</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>45.24</t>
+          <t>45.44</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-11.14</t>
+          <t>-23.21</t>
         </is>
       </c>
       <c r="AQ23" t="n">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.53</v>
+        <v>2.39</v>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-33.34</t>
+          <t>-36.99</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -9954,43 +9954,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>80777.21610169491</t>
+          <t>81797.06276445698</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>231160.8</v>
+        <v>217717</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>420206.6</t>
+          <t>367044.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>235339.22</v>
+        <v>237158.66</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-189045</t>
+          <t>-149327</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>20734.78860529711</t>
+          <t>14301.02560266853</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-10587.49947517022</t>
+          <t>-21084.67091178865</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>216732.0</t>
+          <t>149413.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10010,7 +10010,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>42.30</t>
+          <t>35.83</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10065,7 +10065,7 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>49.86</t>
+          <t>49.76</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10120,22 +10120,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>54.5</t>
+          <t>55.3</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>55.7</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>53.6</t>
+          <t>52.3</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>55.0</t>
+          <t>52.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -10167,12 +10167,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2661.652</t>
+          <t>1888.295</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>596.0</t>
+          <t>595.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-1.55</t>
+          <t>-7.87</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -10267,7 +10267,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-13.75</t>
+          <t>-13.89</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -10277,17 +10277,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12.30</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
@@ -10298,12 +10298,12 @@
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
@@ -10313,51 +10313,51 @@
       </c>
       <c r="AG24" t="inlineStr">
         <is>
-          <t>26.58</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH24" t="n">
-        <v>-1.65</v>
+        <v>-1.13</v>
       </c>
       <c r="AI24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.43</v>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>-7.86</t>
+          <t>-7.99</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>606.0</t>
+          <t>601.8</t>
         </is>
       </c>
       <c r="AM24" t="n">
-        <v>601.85</v>
+        <v>599.25</v>
       </c>
       <c r="AN24" t="n">
-        <v>653.2</v>
+        <v>651.3</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>652.6</t>
+          <t>652.02</t>
         </is>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>18.70</t>
+          <t>16.65</t>
         </is>
       </c>
       <c r="AQ24" t="n">
-        <v>-14</v>
+        <v>-13.78</v>
       </c>
       <c r="AR24" t="n">
-        <v>-17.22</v>
+        <v>-16.53</v>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>-174.21</t>
+          <t>-171.24</t>
         </is>
       </c>
       <c r="AU24" t="inlineStr">
@@ -10376,43 +10376,43 @@
       </c>
       <c r="AV24" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>1593030897.0</t>
+          <t>1130101250.0</t>
         </is>
       </c>
       <c r="AX24" t="n">
-        <v>1687521058.6</v>
+        <v>1475778211.4</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>1714050135.5</t>
+          <t>1601879592.6</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>2162079466.34</v>
+        <v>2149663176.7</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
-          <t>-26529076</t>
+          <t>-126101381</t>
         </is>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>-99564043.09976524</t>
+          <t>-119958275.6339683</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-208171537.375232</t>
+          <t>-232126554.5720854</t>
         </is>
       </c>
       <c r="BD24" t="inlineStr">
         <is>
-          <t>1593030897.0</t>
+          <t>1130101250.0</t>
         </is>
       </c>
       <c r="BE24" t="inlineStr">
@@ -10432,7 +10432,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>-11.44</t>
+          <t>-11.59</t>
         </is>
       </c>
       <c r="BI24" t="inlineStr">
@@ -10477,7 +10477,7 @@
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="BT24" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU24" t="inlineStr">
@@ -10502,7 +10502,7 @@
       </c>
       <c r="BV24" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW24" t="inlineStr">
@@ -10517,12 +10517,12 @@
       </c>
       <c r="BY24" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -10542,22 +10542,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>608.0</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>595.0</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>596.0</t>
+          <t>595.0</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -10589,12 +10589,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2606.032</t>
+          <t>2661.652</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>602.0</t>
+          <t>596.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -10614,17 +10614,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-9.55</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -10689,7 +10689,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-12.88</t>
+          <t>-13.75</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -10699,17 +10699,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>-0.50</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
@@ -10720,66 +10720,66 @@
       <c r="AC25" t="inlineStr"/>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>50.24</t>
+          <t>26.58</t>
         </is>
       </c>
       <c r="AH25" t="n">
-        <v>-1.02</v>
+        <v>-1.65</v>
       </c>
       <c r="AI25" t="n">
-        <v>0.51</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>-7.61</t>
+          <t>-7.86</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>608.2</t>
+          <t>606.0</t>
         </is>
       </c>
       <c r="AM25" t="n">
-        <v>605.1</v>
+        <v>601.85</v>
       </c>
       <c r="AN25" t="n">
-        <v>654.96</v>
+        <v>653.2</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>653.15</t>
+          <t>652.6</t>
         </is>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>18.70</t>
         </is>
       </c>
       <c r="AQ25" t="n">
-        <v>-14.18</v>
+        <v>-14</v>
       </c>
       <c r="AR25" t="n">
-        <v>-18.02</v>
+        <v>-17.22</v>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
@@ -10788,7 +10788,7 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>-177.68</t>
+          <t>-174.21</t>
         </is>
       </c>
       <c r="AU25" t="inlineStr">
@@ -10798,43 +10798,43 @@
       </c>
       <c r="AV25" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>1571975079.0</t>
+          <t>1593030897.0</t>
         </is>
       </c>
       <c r="AX25" t="n">
-        <v>1614634266.2</v>
+        <v>1687521058.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>1785146077.5</t>
+          <t>1714050135.5</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>2161025589.18</v>
+        <v>2162079466.34</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
-          <t>-170511811</t>
+          <t>-26529076</t>
         </is>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>-79817225.95877129</t>
+          <t>-99564043.09976524</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-216114991.5091832</t>
+          <t>-208171537.375232</t>
         </is>
       </c>
       <c r="BD25" t="inlineStr">
         <is>
-          <t>1571975079.0</t>
+          <t>1593030897.0</t>
         </is>
       </c>
       <c r="BE25" t="inlineStr">
@@ -10854,7 +10854,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>-10.55</t>
+          <t>-11.44</t>
         </is>
       </c>
       <c r="BI25" t="inlineStr">
@@ -10899,7 +10899,7 @@
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -10909,12 +10909,12 @@
       </c>
       <c r="BS25" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="BT25" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU25" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="BV25" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW25" t="inlineStr">
@@ -10939,12 +10939,12 @@
       </c>
       <c r="BY25" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -10964,22 +10964,22 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>608.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
         <is>
-          <t>608.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>599.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>602.0</t>
+          <t>596.0</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2230.728</t>
+          <t>2606.032</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11026,7 +11026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11036,17 +11036,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>-1.18</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-22.99</t>
+          <t>-9.55</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-11.87</t>
+          <t>-12.88</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -11121,17 +11121,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10.31</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>-0.50</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
@@ -11142,66 +11142,66 @@
       <c r="AC26" t="inlineStr"/>
       <c r="AD26" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>73.08</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG26" t="inlineStr">
         <is>
-          <t>81.35</t>
+          <t>50.24</t>
         </is>
       </c>
       <c r="AH26" t="n">
-        <v>0.1</v>
+        <v>-1.02</v>
       </c>
       <c r="AI26" t="n">
-        <v>0.04</v>
+        <v>0.51</v>
       </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>-7.38</t>
+          <t>-7.61</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>608.4</t>
+          <t>608.2</t>
         </is>
       </c>
       <c r="AM26" t="n">
-        <v>608.15</v>
+        <v>605.1</v>
       </c>
       <c r="AN26" t="n">
-        <v>656.6</v>
+        <v>654.96</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>653.79</t>
+          <t>653.15</t>
         </is>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>21.33</t>
         </is>
       </c>
       <c r="AQ26" t="n">
-        <v>-14.81</v>
+        <v>-14.18</v>
       </c>
       <c r="AR26" t="n">
-        <v>-18.98</v>
+        <v>-18.02</v>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
-          <t>-181.82</t>
+          <t>-177.68</t>
         </is>
       </c>
       <c r="AU26" t="inlineStr">
@@ -11220,43 +11220,43 @@
       </c>
       <c r="AV26" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>1358151272.0</t>
+          <t>1571975079.0</t>
         </is>
       </c>
       <c r="AX26" t="n">
-        <v>1583427256</v>
+        <v>1614634266.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>2056189977.7</t>
+          <t>1785146077.5</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>2164506952.82</v>
+        <v>2161025589.18</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
-          <t>-472762721</t>
+          <t>-170511811</t>
         </is>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>-55035814.04051458</t>
+          <t>-79817225.95877129</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-217488410.0752137</t>
+          <t>-216114991.5091832</t>
         </is>
       </c>
       <c r="BD26" t="inlineStr">
         <is>
-          <t>1358151272.0</t>
+          <t>1571975079.0</t>
         </is>
       </c>
       <c r="BE26" t="inlineStr">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>-9.51</t>
+          <t>-10.55</t>
         </is>
       </c>
       <c r="BI26" t="inlineStr">
@@ -11321,7 +11321,7 @@
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="BS26" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -11346,7 +11346,7 @@
       </c>
       <c r="BV26" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW26" t="inlineStr">
@@ -11361,12 +11361,12 @@
       </c>
       <c r="BY26" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -11386,22 +11386,22 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>608.0</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>608.0</t>
         </is>
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>603.0</t>
+          <t>599.0</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>609.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -11423,7 +11423,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11433,12 +11433,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-1.45</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2834.061</t>
+          <t>2230.728</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11448,7 +11448,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11458,17 +11458,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-23.35</t>
+          <t>-22.99</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-11.87</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -11543,17 +11543,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13.10</t>
+          <t>10.31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>-1.98</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
@@ -11564,66 +11564,66 @@
       <c r="AC27" t="inlineStr"/>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF27" t="inlineStr">
         <is>
-          <t>70.97</t>
+          <t>73.08</t>
         </is>
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>86.05</t>
+          <t>81.35</t>
         </is>
       </c>
       <c r="AH27" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="AI27" t="n">
-        <v>-0.67</v>
+        <v>0.04</v>
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>-7.17</t>
+          <t>-7.38</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>606.8</t>
+          <t>608.4</t>
         </is>
       </c>
       <c r="AM27" t="n">
-        <v>610.9</v>
+        <v>608.15</v>
       </c>
       <c r="AN27" t="n">
-        <v>658.1</v>
+        <v>656.6</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>654.45</t>
+          <t>653.79</t>
         </is>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>19.50</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AQ27" t="n">
-        <v>-16.12</v>
+        <v>-14.81</v>
       </c>
       <c r="AR27" t="n">
-        <v>-20.03</v>
+        <v>-18.98</v>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>-186.31</t>
+          <t>-181.82</t>
         </is>
       </c>
       <c r="AU27" t="inlineStr">
@@ -11642,43 +11642,43 @@
       </c>
       <c r="AV27" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>1725632559.0</t>
+          <t>1358151272.0</t>
         </is>
       </c>
       <c r="AX27" t="n">
-        <v>1723225612.6</v>
+        <v>1583427256</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>2248107395.1</t>
+          <t>2056189977.7</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>2168047534.76</v>
+        <v>2164506952.82</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
-          <t>-524881782</t>
+          <t>-472762721</t>
         </is>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>-25498978.39784202</t>
+          <t>-55035814.04051458</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-188773299.7739999</t>
+          <t>-217488410.0752137</t>
         </is>
       </c>
       <c r="BD27" t="inlineStr">
         <is>
-          <t>1725632559.0</t>
+          <t>1358151272.0</t>
         </is>
       </c>
       <c r="BE27" t="inlineStr">
@@ -11698,7 +11698,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-9.51</t>
         </is>
       </c>
       <c r="BI27" t="inlineStr">
@@ -11743,7 +11743,7 @@
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="BS27" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="BV27" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW27" t="inlineStr">
@@ -11783,12 +11783,12 @@
       </c>
       <c r="BY27" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -11808,22 +11808,22 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>619.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
         <is>
-          <t>621.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>605.0</t>
+          <t>603.0</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>609.0</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -11855,12 +11855,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-1.45</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3544.654</t>
+          <t>2834.061</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11880,17 +11880,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-24.43</t>
+          <t>-23.35</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -11955,7 +11955,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-10.85</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -11965,17 +11965,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16.38</t>
+          <t>13.10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -11986,66 +11986,66 @@
       <c r="AC28" t="inlineStr"/>
       <c r="AD28" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>70.97</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>86.05</t>
         </is>
       </c>
       <c r="AH28" t="n">
-        <v>1.38</v>
+        <v>0.03</v>
       </c>
       <c r="AI28" t="n">
-        <v>-1.14</v>
+        <v>-0.67</v>
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-7.17</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>607.6</t>
+          <t>606.8</t>
         </is>
       </c>
       <c r="AM28" t="n">
-        <v>614.6</v>
+        <v>610.9</v>
       </c>
       <c r="AN28" t="n">
-        <v>659.3200000000001</v>
+        <v>658.1</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
-          <t>655.36</t>
+          <t>654.45</t>
         </is>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>17.39</t>
+          <t>19.50</t>
         </is>
       </c>
       <c r="AQ28" t="n">
-        <v>-17.35</v>
+        <v>-16.12</v>
       </c>
       <c r="AR28" t="n">
-        <v>-21</v>
+        <v>-20.03</v>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
@@ -12054,7 +12054,7 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>-190.52</t>
+          <t>-186.31</t>
         </is>
       </c>
       <c r="AU28" t="inlineStr">
@@ -12064,43 +12064,43 @@
       </c>
       <c r="AV28" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>2188815486.0</t>
+          <t>1725632559.0</t>
         </is>
       </c>
       <c r="AX28" t="n">
-        <v>1727980973.8</v>
+        <v>1723225612.6</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>2286736829.3</t>
+          <t>2248107395.1</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>2197511210.52</v>
+        <v>2168047534.76</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
-          <t>-558755855</t>
+          <t>-524881782</t>
         </is>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>4187261.852368519</t>
+          <t>-25498978.39784202</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-180382805.1017659</t>
+          <t>-188773299.7739999</t>
         </is>
       </c>
       <c r="BD28" t="inlineStr">
         <is>
-          <t>2188815486.0</t>
+          <t>1725632559.0</t>
         </is>
       </c>
       <c r="BE28" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="BI28" t="inlineStr">
@@ -12165,7 +12165,7 @@
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -12175,12 +12175,12 @@
       </c>
       <c r="BS28" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT28" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU28" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="BV28" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW28" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="BY28" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -12230,22 +12230,22 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
         <is>
-          <t>622.0</t>
+          <t>621.0</t>
         </is>
       </c>
       <c r="CF28" t="inlineStr">
         <is>
+          <t>605.0</t>
+        </is>
+      </c>
+      <c r="CG28" t="inlineStr">
+        <is>
           <t>607.0</t>
-        </is>
-      </c>
-      <c r="CG28" t="inlineStr">
-        <is>
-          <t>616.0</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -12277,12 +12277,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2028.846</t>
+          <t>3544.654</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -12302,17 +12302,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-1.85</t>
+          <t>-3.53</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-24.92</t>
+          <t>-24.43</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>-12.16</t>
+          <t>-10.85</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -12387,17 +12387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>9.38</t>
+          <t>16.38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
@@ -12408,66 +12408,66 @@
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>87.18</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>81.72</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AH29" t="n">
-        <v>0.03</v>
+        <v>1.38</v>
       </c>
       <c r="AI29" t="n">
-        <v>-1.79</v>
+        <v>-1.14</v>
       </c>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>-6.47</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AL29" t="inlineStr">
         <is>
-          <t>606.8</t>
+          <t>607.6</t>
         </is>
       </c>
       <c r="AM29" t="n">
-        <v>617.85</v>
+        <v>614.6</v>
       </c>
       <c r="AN29" t="n">
-        <v>660.6</v>
+        <v>659.3200000000001</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
-          <t>656.19</t>
+          <t>655.36</t>
         </is>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>10.64</t>
+          <t>17.39</t>
         </is>
       </c>
       <c r="AQ29" t="n">
-        <v>-19.58</v>
+        <v>-17.35</v>
       </c>
       <c r="AR29" t="n">
-        <v>-21.91</v>
+        <v>-21</v>
       </c>
       <c r="AS29" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
-          <t>-194.46</t>
+          <t>-190.52</t>
         </is>
       </c>
       <c r="AU29" t="inlineStr">
@@ -12486,43 +12486,43 @@
       </c>
       <c r="AV29" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>1228596935.0</t>
+          <t>2188815486.0</t>
         </is>
       </c>
       <c r="AX29" t="n">
-        <v>1740579212.4</v>
+        <v>1727980973.8</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
-          <t>2318255340.3</t>
+          <t>2286736829.3</t>
         </is>
       </c>
       <c r="AZ29" t="n">
-        <v>2189722054.78</v>
+        <v>2197511210.52</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
-          <t>-577676127</t>
+          <t>-558755855</t>
         </is>
       </c>
       <c r="BB29" t="inlineStr">
         <is>
-          <t>37745455.84402931</t>
+          <t>4187261.852368519</t>
         </is>
       </c>
       <c r="BC29" t="inlineStr">
         <is>
-          <t>-211580883.280654</t>
+          <t>-180382805.1017659</t>
         </is>
       </c>
       <c r="BD29" t="inlineStr">
         <is>
-          <t>1228596935.0</t>
+          <t>2188815486.0</t>
         </is>
       </c>
       <c r="BE29" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="BI29" t="inlineStr">
@@ -12587,7 +12587,7 @@
       </c>
       <c r="BQ29" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR29" t="inlineStr">
@@ -12597,12 +12597,12 @@
       </c>
       <c r="BS29" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="BT29" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU29" t="inlineStr">
@@ -12612,7 +12612,7 @@
       </c>
       <c r="BV29" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW29" t="inlineStr">
@@ -12627,12 +12627,12 @@
       </c>
       <c r="BY29" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ29" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA29" t="inlineStr">
@@ -12652,22 +12652,22 @@
       </c>
       <c r="CD29" t="inlineStr">
         <is>
+          <t>610.0</t>
+        </is>
+      </c>
+      <c r="CE29" t="inlineStr">
+        <is>
+          <t>622.0</t>
+        </is>
+      </c>
+      <c r="CF29" t="inlineStr">
+        <is>
           <t>607.0</t>
         </is>
       </c>
-      <c r="CE29" t="inlineStr">
-        <is>
-          <t>608.0</t>
-        </is>
-      </c>
-      <c r="CF29" t="inlineStr">
-        <is>
-          <t>601.0</t>
-        </is>
-      </c>
       <c r="CG29" t="inlineStr">
         <is>
-          <t>607.0</t>
+          <t>616.0</t>
         </is>
       </c>
       <c r="CH29" t="inlineStr">
@@ -12699,12 +12699,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2335.806</t>
+          <t>2028.846</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -12714,7 +12714,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>603.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -12724,17 +12724,17 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-2.02</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-30.86</t>
+          <t>-24.92</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -12799,7 +12799,7 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>-12.74</t>
+          <t>-12.16</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
@@ -12809,17 +12809,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>9.38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
@@ -12830,66 +12830,66 @@
       <c r="AC30" t="inlineStr"/>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>80.43</t>
+          <t>87.18</t>
         </is>
       </c>
       <c r="AG30" t="inlineStr">
         <is>
-          <t>85.31</t>
+          <t>81.72</t>
         </is>
       </c>
       <c r="AH30" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="AI30" t="n">
-        <v>-2.97</v>
+        <v>-1.79</v>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-6.47</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>603.4</t>
+          <t>606.8</t>
         </is>
       </c>
       <c r="AM30" t="n">
-        <v>621.9</v>
+        <v>617.85</v>
       </c>
       <c r="AN30" t="n">
-        <v>661.92</v>
+        <v>660.6</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>657.1</t>
+          <t>656.19</t>
         </is>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>10.64</t>
         </is>
       </c>
       <c r="AQ30" t="n">
-        <v>-21.23</v>
+        <v>-19.58</v>
       </c>
       <c r="AR30" t="n">
-        <v>-22.5</v>
+        <v>-21.91</v>
       </c>
       <c r="AS30" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
       </c>
       <c r="AT30" t="inlineStr">
         <is>
-          <t>-196.97</t>
+          <t>-194.46</t>
         </is>
       </c>
       <c r="AU30" t="inlineStr">
@@ -12908,43 +12908,43 @@
       </c>
       <c r="AV30" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>1415940028.0</t>
+          <t>1228596935.0</t>
         </is>
       </c>
       <c r="AX30" t="n">
-        <v>1955657888.8</v>
+        <v>1740579212.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
-          <t>2828486800.4</t>
+          <t>2318255340.3</t>
         </is>
       </c>
       <c r="AZ30" t="n">
-        <v>2204685972.04</v>
+        <v>2189722054.78</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
-          <t>-872828911</t>
+          <t>-577676127</t>
         </is>
       </c>
       <c r="BB30" t="inlineStr">
         <is>
-          <t>83077517.50306264</t>
+          <t>37745455.84402931</t>
         </is>
       </c>
       <c r="BC30" t="inlineStr">
         <is>
-          <t>-145712547.2404709</t>
+          <t>-211580883.280654</t>
         </is>
       </c>
       <c r="BD30" t="inlineStr">
         <is>
-          <t>1415940028.0</t>
+          <t>1228596935.0</t>
         </is>
       </c>
       <c r="BE30" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="BI30" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="BQ30" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR30" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="BS30" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="BT30" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU30" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="BV30" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW30" t="inlineStr">
@@ -13049,12 +13049,12 @@
       </c>
       <c r="BY30" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ30" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA30" t="inlineStr">
@@ -13074,22 +13074,22 @@
       </c>
       <c r="CD30" t="inlineStr">
         <is>
-          <t>602.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="CE30" t="inlineStr">
         <is>
-          <t>614.0</t>
+          <t>608.0</t>
         </is>
       </c>
       <c r="CF30" t="inlineStr">
         <is>
-          <t>602.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CG30" t="inlineStr">
         <is>
-          <t>603.0</t>
+          <t>607.0</t>
         </is>
       </c>
       <c r="CH30" t="inlineStr">
@@ -13121,12 +13121,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3405.189</t>
+          <t>2335.806</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -13136,7 +13136,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>603.0</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -13146,17 +13146,17 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-0.84</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-18.00</t>
+          <t>-30.86</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -13221,7 +13221,7 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>-13.02</t>
+          <t>-12.74</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
@@ -13231,17 +13231,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15.74</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
@@ -13252,66 +13252,66 @@
       <c r="AC31" t="inlineStr"/>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>77.55</t>
+          <t>80.43</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
         <is>
-          <t>81.84</t>
+          <t>85.31</t>
         </is>
       </c>
       <c r="AH31" t="n">
-        <v>0.2</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AI31" t="n">
-        <v>-4.23</v>
+        <v>-2.97</v>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-6.05</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL31" t="inlineStr">
         <is>
-          <t>599.8</t>
+          <t>603.4</t>
         </is>
       </c>
       <c r="AM31" t="n">
-        <v>626.3</v>
+        <v>621.9</v>
       </c>
       <c r="AN31" t="n">
-        <v>663.5599999999999</v>
+        <v>661.92</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>658.01</t>
+          <t>657.1</t>
         </is>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>0.83</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AQ31" t="n">
-        <v>-22.62</v>
+        <v>-21.23</v>
       </c>
       <c r="AR31" t="n">
-        <v>-22.81</v>
+        <v>-22.5</v>
       </c>
       <c r="AS31" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
-          <t>-198.33</t>
+          <t>-196.97</t>
         </is>
       </c>
       <c r="AU31" t="inlineStr">
@@ -13330,43 +13330,43 @@
       </c>
       <c r="AV31" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>2057143055.0</t>
+          <t>1415940028.0</t>
         </is>
       </c>
       <c r="AX31" t="n">
-        <v>2528952699.4</v>
+        <v>1955657888.8</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
-          <t>3084050533.3</t>
+          <t>2828486800.4</t>
         </is>
       </c>
       <c r="AZ31" t="n">
-        <v>2214399585.16</v>
+        <v>2204685972.04</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
-          <t>-555097833</t>
+          <t>-872828911</t>
         </is>
       </c>
       <c r="BB31" t="inlineStr">
         <is>
-          <t>124675711.092796</t>
+          <t>83077517.50306264</t>
         </is>
       </c>
       <c r="BC31" t="inlineStr">
         <is>
-          <t>-66483379.03162146</t>
+          <t>-145712547.2404709</t>
         </is>
       </c>
       <c r="BD31" t="inlineStr">
         <is>
-          <t>2057143055.0</t>
+          <t>1415940028.0</t>
         </is>
       </c>
       <c r="BE31" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>-10.70</t>
+          <t>-10.40</t>
         </is>
       </c>
       <c r="BI31" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="BQ31" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR31" t="inlineStr">
@@ -13441,12 +13441,12 @@
       </c>
       <c r="BS31" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="BT31" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU31" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="BV31" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW31" t="inlineStr">
@@ -13471,12 +13471,12 @@
       </c>
       <c r="BY31" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ31" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA31" t="inlineStr">
@@ -13496,22 +13496,22 @@
       </c>
       <c r="CD31" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="CE31" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>614.0</t>
         </is>
       </c>
       <c r="CF31" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>602.0</t>
         </is>
       </c>
       <c r="CG31" t="inlineStr">
         <is>
-          <t>601.0</t>
+          <t>603.0</t>
         </is>
       </c>
       <c r="CH31" t="inlineStr">
@@ -13533,7 +13533,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2851.548</t>
+          <t>3405.189</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -13568,17 +13568,17 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-2.52</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-10.66</t>
+          <t>-18.00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -13643,7 +13643,7 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-13.02</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
@@ -13653,17 +13653,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13.18</t>
+          <t>15.74</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-1.83</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
@@ -13674,66 +13674,66 @@
       <c r="AC32" t="inlineStr"/>
       <c r="AD32" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>97.96</t>
+          <t>77.55</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>68.84</t>
+          <t>81.84</t>
         </is>
       </c>
       <c r="AH32" t="n">
-        <v>2.83</v>
+        <v>0.2</v>
       </c>
       <c r="AI32" t="n">
-        <v>-5.85</v>
+        <v>-4.23</v>
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>-5.15</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL32" t="inlineStr">
         <is>
-          <t>594.2</t>
+          <t>599.8</t>
         </is>
       </c>
       <c r="AM32" t="n">
-        <v>631.1</v>
+        <v>626.3</v>
       </c>
       <c r="AN32" t="n">
-        <v>665.38</v>
+        <v>663.5599999999999</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
-          <t>658.81</t>
+          <t>658.01</t>
         </is>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>0.83</t>
         </is>
       </c>
       <c r="AQ32" t="n">
-        <v>-23.86</v>
+        <v>-22.62</v>
       </c>
       <c r="AR32" t="n">
-        <v>-22.86</v>
+        <v>-22.81</v>
       </c>
       <c r="AS32" t="inlineStr">
         <is>
@@ -13742,7 +13742,7 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
-          <t>-198.54</t>
+          <t>-198.33</t>
         </is>
       </c>
       <c r="AU32" t="inlineStr">
@@ -13752,43 +13752,43 @@
       </c>
       <c r="AV32" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>1749409365.0</t>
+          <t>2057143055.0</t>
         </is>
       </c>
       <c r="AX32" t="n">
-        <v>2772989177.6</v>
+        <v>2528952699.4</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
-          <t>3103713833.7</t>
+          <t>3084050533.3</t>
         </is>
       </c>
       <c r="AZ32" t="n">
-        <v>2209332488.54</v>
+        <v>2214399585.16</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
-          <t>-330724656</t>
+          <t>-555097833</t>
         </is>
       </c>
       <c r="BB32" t="inlineStr">
         <is>
-          <t>159431909.2972355</t>
+          <t>124675711.092796</t>
         </is>
       </c>
       <c r="BC32" t="inlineStr">
         <is>
-          <t>-19624770.94642115</t>
+          <t>-66483379.03162146</t>
         </is>
       </c>
       <c r="BD32" t="inlineStr">
         <is>
-          <t>1749409365.0</t>
+          <t>2057143055.0</t>
         </is>
       </c>
       <c r="BE32" t="inlineStr">
@@ -13808,7 +13808,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>-9.21</t>
+          <t>-10.70</t>
         </is>
       </c>
       <c r="BI32" t="inlineStr">
@@ -13858,17 +13858,17 @@
       </c>
       <c r="BR32" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS32" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="BT32" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU32" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="BV32" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW32" t="inlineStr">
@@ -13893,12 +13893,12 @@
       </c>
       <c r="BY32" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ32" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA32" t="inlineStr">
@@ -13918,22 +13918,22 @@
       </c>
       <c r="CD32" t="inlineStr">
         <is>
+          <t>611.0</t>
+        </is>
+      </c>
+      <c r="CE32" t="inlineStr">
+        <is>
           <t>612.0</t>
         </is>
       </c>
-      <c r="CE32" t="inlineStr">
-        <is>
-          <t>619.0</t>
-        </is>
-      </c>
       <c r="CF32" t="inlineStr">
         <is>
-          <t>610.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CG32" t="inlineStr">
         <is>
-          <t>611.0</t>
+          <t>601.0</t>
         </is>
       </c>
       <c r="CH32" t="inlineStr">
@@ -13965,12 +13965,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>3697.739</t>
+          <t>2851.548</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -13980,7 +13980,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -13990,17 +13990,17 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-2.69</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-12.55</t>
+          <t>-10.66</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -14065,7 +14065,7 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
@@ -14075,17 +14075,17 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17.09</t>
+          <t>13.18</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
@@ -14096,66 +14096,66 @@
       <c r="AC33" t="inlineStr"/>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>97.96</t>
         </is>
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>44.92</t>
+          <t>68.84</t>
         </is>
       </c>
       <c r="AH33" t="n">
-        <v>4.33</v>
+        <v>2.83</v>
       </c>
       <c r="AI33" t="n">
-        <v>-7.77</v>
+        <v>-5.85</v>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-5.15</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AL33" t="inlineStr">
         <is>
-          <t>586.6</t>
+          <t>594.2</t>
         </is>
       </c>
       <c r="AM33" t="n">
-        <v>636</v>
+        <v>631.1</v>
       </c>
       <c r="AN33" t="n">
-        <v>667.3</v>
+        <v>665.38</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>659.49</t>
+          <t>658.81</t>
         </is>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>-15.53</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AQ33" t="n">
-        <v>-26.12</v>
+        <v>-23.86</v>
       </c>
       <c r="AR33" t="n">
-        <v>-22.61</v>
+        <v>-22.86</v>
       </c>
       <c r="AS33" t="inlineStr">
         <is>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
-          <t>-197.45</t>
+          <t>-198.54</t>
         </is>
       </c>
       <c r="AU33" t="inlineStr">
@@ -14174,43 +14174,43 @@
       </c>
       <c r="AV33" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="AX33" t="n">
-        <v>2845492684.8</v>
+        <v>2772989177.6</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
-          <t>3254023064.0</t>
+          <t>3103713833.7</t>
         </is>
       </c>
       <c r="AZ33" t="n">
-        <v>2250939639.92</v>
+        <v>2209332488.54</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
-          <t>-408530379</t>
+          <t>-330724656</t>
         </is>
       </c>
       <c r="BB33" t="inlineStr">
         <is>
-          <t>191987669.3415367</t>
+          <t>159431909.2972355</t>
         </is>
       </c>
       <c r="BC33" t="inlineStr">
         <is>
-          <t>80988449.20909452</t>
+          <t>-19624770.94642115</t>
         </is>
       </c>
       <c r="BD33" t="inlineStr">
         <is>
-          <t>2251806679.0</t>
+          <t>1749409365.0</t>
         </is>
       </c>
       <c r="BE33" t="inlineStr">
@@ -14230,7 +14230,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>-9.06</t>
+          <t>-9.21</t>
         </is>
       </c>
       <c r="BI33" t="inlineStr">
@@ -14275,7 +14275,7 @@
       </c>
       <c r="BQ33" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR33" t="inlineStr">
@@ -14285,12 +14285,12 @@
       </c>
       <c r="BS33" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="BT33" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU33" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="BV33" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW33" t="inlineStr">
@@ -14315,12 +14315,12 @@
       </c>
       <c r="BY33" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ33" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA33" t="inlineStr">
@@ -14340,22 +14340,22 @@
       </c>
       <c r="CD33" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CE33" t="inlineStr">
         <is>
-          <t>616.0</t>
+          <t>619.0</t>
         </is>
       </c>
       <c r="CF33" t="inlineStr">
         <is>
-          <t>594.0</t>
+          <t>610.0</t>
         </is>
       </c>
       <c r="CG33" t="inlineStr">
         <is>
-          <t>612.0</t>
+          <t>611.0</t>
         </is>
       </c>
       <c r="CH33" t="inlineStr">
@@ -14387,12 +14387,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3906.167</t>
+          <t>3697.739</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -14402,7 +14402,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -14412,17 +14412,17 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>-2.86</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>-15.42</t>
+          <t>-12.55</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -14487,7 +14487,7 @@
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>-14.62</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
@@ -14497,17 +14497,17 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18.05</t>
+          <t>17.09</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
@@ -14518,66 +14518,66 @@
       <c r="AC34" t="inlineStr"/>
       <c r="AD34" t="inlineStr">
         <is>
-          <t>104</t>
+          <t>71</t>
         </is>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>2662</t>
+          <t>1888</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AG34" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>44.92</t>
         </is>
       </c>
       <c r="AH34" t="n">
-        <v>2.18</v>
+        <v>4.33</v>
       </c>
       <c r="AI34" t="n">
-        <v>-9.9</v>
+        <v>-7.77</v>
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>-4.19</t>
+          <t>-4.69</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>577.4</t>
+          <t>586.6</t>
         </is>
       </c>
       <c r="AM34" t="n">
-        <v>640.85</v>
+        <v>636</v>
       </c>
       <c r="AN34" t="n">
-        <v>668.88</v>
+        <v>667.3</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>660.11</t>
+          <t>659.49</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>-32.16</t>
+          <t>-15.53</t>
         </is>
       </c>
       <c r="AQ34" t="n">
-        <v>-28.72</v>
+        <v>-26.12</v>
       </c>
       <c r="AR34" t="n">
-        <v>-21.73</v>
+        <v>-22.61</v>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>-193.67</t>
+          <t>-197.45</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
@@ -14596,43 +14596,43 @@
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>3304007589.182203</t>
+          <t>3301738399.176305</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="AX34" t="n">
-        <v>2895931468.2</v>
+        <v>2845492684.8</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>3423927956.4</t>
+          <t>3254023064.0</t>
         </is>
       </c>
       <c r="AZ34" t="n">
-        <v>2313304958.2</v>
+        <v>2250939639.92</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>-527996488</t>
+          <t>-408530379</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>212169345.7292535</t>
+          <t>191987669.3415367</t>
         </is>
       </c>
       <c r="BC34" t="inlineStr">
         <is>
-          <t>168000892.6023631</t>
+          <t>80988449.20909452</t>
         </is>
       </c>
       <c r="BD34" t="inlineStr">
         <is>
-          <t>2303990317.0</t>
+          <t>2251806679.0</t>
         </is>
       </c>
       <c r="BE34" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>-12.33</t>
+          <t>-9.06</t>
         </is>
       </c>
       <c r="BI34" t="inlineStr">
@@ -14697,7 +14697,7 @@
       </c>
       <c r="BQ34" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR34" t="inlineStr">
@@ -14707,12 +14707,12 @@
       </c>
       <c r="BS34" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="BT34" t="inlineStr">
         <is>
-          <t>5.7</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="BU34" t="inlineStr">
@@ -14722,7 +14722,7 @@
       </c>
       <c r="BV34" t="inlineStr">
         <is>
-          <t>12.72</t>
+          <t>12.7</t>
         </is>
       </c>
       <c r="BW34" t="inlineStr">
@@ -14737,12 +14737,12 @@
       </c>
       <c r="BY34" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>26.77</t>
         </is>
       </c>
       <c r="BZ34" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>441942</t>
         </is>
       </c>
       <c r="CA34" t="inlineStr">
@@ -14762,22 +14762,22 @@
       </c>
       <c r="CD34" t="inlineStr">
         <is>
-          <t>589.0</t>
+          <t>594.0</t>
         </is>
       </c>
       <c r="CE34" t="inlineStr">
         <is>
+          <t>616.0</t>
+        </is>
+      </c>
+      <c r="CF34" t="inlineStr">
+        <is>
           <t>594.0</t>
         </is>
       </c>
-      <c r="CF34" t="inlineStr">
-        <is>
-          <t>584.0</t>
-        </is>
-      </c>
       <c r="CG34" t="inlineStr">
         <is>
-          <t>590.0</t>
+          <t>612.0</t>
         </is>
       </c>
       <c r="CH34" t="inlineStr">

--- a/Result/checksun_type/BIOS(嵌入式軟體).xlsx
+++ b/Result/checksun_type/BIOS(嵌入式軟體).xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【x】看好</t>
+          <t>價_量;【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>294.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -993,7 +993,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>-14.31</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,17 +1123,17 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1144,75 +1144,75 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>745</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-0.5600000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>215.2</t>
+          <t>216.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>214.9</v>
+        <v>215.45</v>
       </c>
       <c r="BA2" t="n">
-        <v>215.99</v>
+        <v>215.68</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>230.66</t>
+          <t>230.15</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>193.33</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>-0.26</v>
+        <v>0.26</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.42</v>
+        <v>-0.28</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-101.17</t>
+          <t>-100.79</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>644425.1053719008</t>
+          <t>651449.8032786886</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>62940.0</t>
+          <t>164555.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>63670.8</v>
+        <v>88104.39999999999</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>68084.7</t>
+          <t>78176.1</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>79080.74000000001</v>
+        <v>80684.12</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-4413</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-1494.795145381775</t>
+          <t>-210.6709799189155</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-469.6106846753682</t>
+          <t>6852.011930126813</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>62940.0</t>
+          <t>164555.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>-14.31</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1383,27 +1383,27 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>225.5</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
           <t>213.0</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
-        <is>
-          <t>216.0</t>
-        </is>
-      </c>
-      <c r="CS2" t="inlineStr">
-        <is>
-          <t>212.0</t>
-        </is>
-      </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>439.0</t>
+          <t>294.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1480,7 +1480,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-17.21</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,75 +1631,75 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>745</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-1.16</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>215.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>214.7</v>
+        <v>214.9</v>
       </c>
       <c r="BA3" t="n">
-        <v>216.46</v>
+        <v>215.99</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>231.2</t>
+          <t>230.66</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>65.90</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.16</v>
+        <v>-0.26</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.46</v>
+        <v>-0.42</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-101.28</t>
+          <t>-101.17</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>644425.1053719008</t>
+          <t>651449.8032786886</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>93569.0</t>
+          <t>62940.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>61556.2</v>
+        <v>63670.8</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>66771.8</t>
+          <t>68084.7</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>80046.16</v>
+        <v>79080.74000000001</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-5215</t>
+          <t>-4413</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1681.192320055668</t>
+          <t>-1494.795145381775</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-24.97832422579813</t>
+          <t>-469.6106846753682</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>93569.0</t>
+          <t>62940.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-17.21</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1815,17 +1815,17 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CR3" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CS3" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>439.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,159 +1937,159 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>213.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>3.84</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-7.81</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2024-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2024-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>253.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>258.5</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>565.0</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>543.0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>-17.60</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>-53.41</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025/06/30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>257.5</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>234.0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>217.5</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2025/09/25</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>258.5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
           <t>218.5</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-12.87</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2024-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>253.0</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>258.5</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>565.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>543.0</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>-15.47</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>-53.41</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>257.5</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>234.0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>2025/07/30</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>217.5</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2025/09/25</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>258.5</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>2025/08/19</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>218.5</t>
-        </is>
-      </c>
       <c r="AK4" t="inlineStr">
         <is>
           <t>2025-09-18 00:00:00</t>
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,75 +2118,75 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>745</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>1.25</v>
+        <v>-1.16</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>215.8</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>214.65</v>
+        <v>214.7</v>
       </c>
       <c r="BA4" t="n">
-        <v>217.09</v>
+        <v>216.46</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>231.59</t>
+          <t>231.2</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>114.72</t>
+          <t>65.90</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>0.08</v>
+        <v>-0.16</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.53</v>
+        <v>-0.46</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-101.28</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>644425.1053719008</t>
+          <t>651449.8032786886</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>72952.0</t>
+          <t>93569.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>55536.6</v>
+        <v>61556.2</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>63736.3</t>
+          <t>66771.8</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>81247.39999999999</v>
+        <v>80046.16</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-8199</t>
+          <t>-5215</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-1982.32213747928</t>
+          <t>-1681.192320055668</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-2670.575726289782</t>
+          <t>-24.97832422579813</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>72952.0</t>
+          <t>93569.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-15.47</t>
+          <t>-17.60</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2277,7 +2277,7 @@
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2297,22 +2297,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2357,27 +2357,27 @@
       </c>
       <c r="CP4" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>220.5</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>220.5</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>218.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>218.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2434,17 +2434,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.44</t>
+          <t>-12.87</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>-15.47</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,38 +2605,38 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>745</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -2645,35 +2645,35 @@
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>214.4</v>
+        <v>214.65</v>
       </c>
       <c r="BA5" t="n">
-        <v>217.53</v>
+        <v>217.09</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>231.98</t>
+          <t>231.59</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>73.27</t>
+          <t>114.72</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>-0.18</v>
+        <v>0.08</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.53</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-101.91</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>644425.1053719008</t>
+          <t>651449.8032786886</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>46506.0</t>
+          <t>72952.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>51780.6</v>
+        <v>55536.6</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>62716.7</t>
+          <t>63736.3</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>84433.48</v>
+        <v>81247.39999999999</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-10936</t>
+          <t>-8199</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1857.185121331916</t>
+          <t>-1982.32213747928</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-4145.658596156543</t>
+          <t>-2670.575726289782</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>46506.0</t>
+          <t>72952.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2739,7 +2739,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>-15.47</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2844,27 +2844,27 @@
       </c>
       <c r="CP5" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>218.5</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>3.39</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-17.44</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-16.25</t>
+          <t>-17.21</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,75 +3092,75 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>745</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.23</v>
+        <v>-0.83</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.21</v>
+        <v>0.65</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.8</t>
         </is>
       </c>
       <c r="AZ6" t="n">
         <v>214.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>217.82</v>
+        <v>217.53</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>232.36</t>
+          <t>231.98</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>93.03</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.06</v>
+        <v>-0.18</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-102.26</t>
+          <t>-101.91</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>644425.1053719008</t>
+          <t>651449.8032786886</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>42387.0</t>
+          <t>46506.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>68247.8</v>
+        <v>51780.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>76005.1</t>
+          <t>62716.7</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>84793.44</v>
+        <v>84433.48</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-7757</t>
+          <t>-10936</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1441.099035000165</t>
+          <t>-1857.185121331916</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-3271.360603246329</t>
+          <t>-4145.658596156543</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>42387.0</t>
+          <t>46506.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-16.25</t>
+          <t>-17.21</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3428,7 +3428,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-16.63</t>
+          <t>-16.25</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,33 +3579,33 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>745</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
+          <t>46.15</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
           <t>30.77</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>43.16</t>
-        </is>
-      </c>
       <c r="AU7" t="n">
-        <v>-0.87</v>
+        <v>-0.23</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
@@ -3615,39 +3615,39 @@
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>217.4</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>214.38</v>
+        <v>214.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>218.08</v>
+        <v>217.82</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>232.64</t>
+          <t>232.36</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>93.03</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="BE7" t="n">
-        <v>-1</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-102.79</t>
+          <t>-102.26</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>644425.1053719008</t>
+          <t>651449.8032786886</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>52367.0</t>
+          <t>42387.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>72498.60000000001</v>
+        <v>68247.8</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>77751.7</t>
+          <t>76005.1</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>85915.12</v>
+        <v>84793.44</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-5253</t>
+          <t>-7757</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1108.324204409954</t>
+          <t>-1441.099035000165</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-1464.20773468721</t>
+          <t>-3271.360603246329</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>52367.0</t>
+          <t>42387.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-16.63</t>
+          <t>-16.25</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3818,27 +3818,27 @@
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>296.0</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>2.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-16.63</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,75 +4066,75 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>745</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-1.15</v>
+        <v>-0.87</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>217.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>214.25</v>
+        <v>214.38</v>
       </c>
       <c r="BA8" t="n">
-        <v>218.5</v>
+        <v>218.08</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>232.79</t>
+          <t>232.64</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>86.65</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="BE8" t="n">
-        <v>-1.21</v>
+        <v>-1</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-103.38</t>
+          <t>-102.79</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>644425.1053719008</t>
+          <t>651449.8032786886</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>63471.0</t>
+          <t>52367.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>71987.39999999999</v>
+        <v>72498.60000000001</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>75957.1</t>
+          <t>77751.7</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>86877.86</v>
+        <v>85915.12</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-3969</t>
+          <t>-5253</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1043.618107995907</t>
+          <t>-1108.324204409954</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>100.4466394932097</t>
+          <t>-1464.20773468721</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>63471.0</t>
+          <t>52367.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-16.63</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4225,7 +4225,7 @@
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4305,27 +4305,27 @@
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr">
+        <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>296.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,159 +4372,159 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>214.5</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3.16</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.08</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-5.23</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2024-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2024-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>253.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>258.5</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>565.0</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>543.0</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>-17.02</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>-53.41</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025/06/30</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>257.5</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>234.0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>217.5</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>2025/09/25</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>258.5</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
           <t>218.5</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-2.1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-4.60</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>-40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2024-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>253.0</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>258.5</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>565.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>543.0</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-15.47</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>-53.41</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>257.5</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>234.0</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>2025/07/30</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>217.5</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2025/09/25</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>258.5</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>2025/08/19</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>218.5</t>
-        </is>
-      </c>
       <c r="AK9" t="inlineStr">
         <is>
           <t>2025-09-18 00:00:00</t>
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,75 +4553,75 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>745</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>0.78</v>
+        <v>-1.15</v>
       </c>
       <c r="AV9" t="n">
         <v>1.28</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>216.8</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>214.05</v>
+        <v>214.25</v>
       </c>
       <c r="BA9" t="n">
-        <v>218.89</v>
+        <v>218.5</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>233.05</t>
+          <t>232.79</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>94.92</t>
+          <t>86.65</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="BE9" t="n">
-        <v>-1.48</v>
+        <v>-1.21</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-103.39</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>644425.1053719008</t>
+          <t>651449.8032786886</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>54172.0</t>
+          <t>63471.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>71936</v>
+        <v>71987.39999999999</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>75405.1</t>
+          <t>75957.1</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>87614.14</v>
+        <v>86877.86</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3469</t>
+          <t>-3969</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-1251.629880266656</t>
+          <t>-1043.618107995907</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>1142.365508340474</t>
+          <t>100.4466394932097</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>54172.0</t>
+          <t>63471.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4687,7 +4687,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-15.47</t>
+          <t>-17.02</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4792,27 +4792,27 @@
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>218.5</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>578.0</t>
+          <t>248.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,7 +4859,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>218.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4869,17 +4869,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-2.8</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-4.60</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-40.0</t>
+          <t>-90.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-14.89</t>
+          <t>-15.47</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>7.52</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,75 +5040,75 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>745</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>83.33</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>80.56</t>
+          <t>94.44</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>1.71</v>
+        <v>0.78</v>
       </c>
       <c r="AV10" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.47</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-6.09</t>
+          <t>-6.08</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>216.3</t>
+          <t>216.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>213.68</v>
+        <v>214.05</v>
       </c>
       <c r="BA10" t="n">
-        <v>219.08</v>
+        <v>218.89</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>233.29</t>
+          <t>233.05</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>79.74</t>
+          <t>94.92</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.37</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="BE10" t="n">
-        <v>-1.83</v>
+        <v>-1.48</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-105.09</t>
+          <t>-104.12</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>644425.1053719008</t>
+          <t>651449.8032786886</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>128842.0</t>
+          <t>54172.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>73652.8</v>
+        <v>71936</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>74641.5</t>
+          <t>75405.1</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>90654.2</v>
+        <v>87614.14</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-988</t>
+          <t>-3469</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-1686.901769104316</t>
+          <t>-1251.629880266656</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>3586.343695681542</t>
+          <t>1142.365508340474</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>128842.0</t>
+          <t>54172.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-14.89</t>
+          <t>-15.47</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5199,7 +5199,7 @@
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.52</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>3.04</t>
+          <t>2.93</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>33.51</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>21.08</t>
+          <t>21.29</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10112</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5279,27 +5279,27 @@
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>資訊服務業平上櫃</t>
+          <t>資訊服務業右下上櫃</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>222.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>227.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>219.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>218.5</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2429.0</t>
+          <t>10905.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,74 +5346,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>61.2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>65.04</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>47.37</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>57.4</t>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5546,47 +5546,47 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>6.32</v>
+        <v>10.09</v>
       </c>
       <c r="AV11" t="n">
-        <v>2.28</v>
+        <v>6</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>52.14</v>
+        <v>52.45</v>
       </c>
       <c r="BA11" t="n">
-        <v>52.79</v>
+        <v>52.98</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>110.61</t>
+          <t>313.22</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.63</v>
+        <v>-0.35</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-116.64</t>
+          <t>-109.33</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>136615.0</t>
+          <t>662931.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>205743</v>
+        <v>329375.2</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>139611.1</t>
+          <t>199569.7</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>222614.5</v>
+        <v>233511.96</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>66131</t>
+          <t>129805</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-9020.19988810568</t>
+          <t>-394.1269517676747</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>12815.11317058292</t>
+          <t>47049.27419809136</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>136615.0</t>
+          <t>662931.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>46.70</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5808,7 +5808,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>8118.0</t>
+          <t>2429.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5843,22 +5843,22 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>7.35</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -5873,7 +5873,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5913,7 +5913,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6029,51 +6029,51 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>7.72</v>
+        <v>6.32</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.4</v>
+        <v>2.28</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>52.01</v>
+        <v>52.14</v>
       </c>
       <c r="BA12" t="n">
-        <v>52.66</v>
+        <v>52.79</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>110.61</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>-0.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.63</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-116.64</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>453696.0</t>
+          <t>136615.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>189517.4</v>
+        <v>205743</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>133155.2</t>
+          <t>139611.1</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>221511.36</v>
+        <v>222614.5</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>56362</t>
+          <t>66131</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-12990.25680786724</t>
+          <t>-9020.19988810568</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>19842.4862323358</t>
+          <t>12815.11317058292</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>453696.0</t>
+          <t>136615.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>44.37</t>
+          <t>46.70</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>5690.0</t>
+          <t>8118.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,17 +6330,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>8.82</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>42.33</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6516,51 +6516,51 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>8.029999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="AV13" t="n">
-        <v>-2.94</v>
+        <v>-0.4</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>50.54</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>52.07</v>
+        <v>52.01</v>
       </c>
       <c r="BA13" t="n">
-        <v>52.54</v>
+        <v>52.66</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.8</v>
+        <v>-0.35</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.92</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-124.22</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,43 +6579,43 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>303392.0</t>
+          <t>453696.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>123618.4</v>
+        <v>189517.4</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>92094.8</t>
+          <t>133155.2</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>213489.6</v>
+        <v>221511.36</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>31523</t>
+          <t>56362</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-18959.84645154052</t>
+          <t>-12990.25680786724</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>-4800.033902029216</t>
+          <t>19842.4862323358</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>303392.0</t>
+          <t>453696.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>44.37</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6685,17 +6685,17 @@
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6782,7 +6782,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1799.0</t>
+          <t>5690.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>10.78</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,66 +6988,66 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>64.75</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>0.02</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AV14" t="n">
-        <v>-4.74</v>
+        <v>-2.94</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>50.54</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>52.11</v>
+        <v>52.07</v>
       </c>
       <c r="BA14" t="n">
-        <v>52.44</v>
+        <v>52.54</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-29.04</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-1.23</v>
+        <v>-0.8</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.95</v>
+        <v>-0.92</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-125.03</t>
+          <t>-124.22</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>90242.0</t>
+          <t>303392.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>80214.39999999999</v>
+        <v>123618.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>70704.0</t>
+          <t>92094.8</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>209175.5</v>
+        <v>213489.6</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>31523</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-21534.35782417894</t>
+          <t>-18959.84645154052</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-23728.20431176394</t>
+          <t>-4800.033902029216</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>90242.0</t>
+          <t>303392.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7167,22 +7167,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7237,17 +7237,17 @@
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>1799.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,149 +7294,149 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>49.65</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>18.87</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-01-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>56.7</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025/03/14</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>32.85</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>11.99</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>-11.61</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2026-01-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
         <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>5.59</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025/03/14</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>32.85</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="AI15" t="inlineStr">
         <is>
           <t>2025/10/20</t>
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>64.75</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.67</v>
+        <v>0.02</v>
       </c>
       <c r="AV15" t="n">
-        <v>-5.36</v>
+        <v>-4.74</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>52.38</v>
+        <v>52.11</v>
       </c>
       <c r="BA15" t="n">
-        <v>52.46</v>
+        <v>52.44</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.54</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-42.21</t>
+          <t>-29.04</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-1.25</v>
+        <v>-1.23</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.88</v>
+        <v>-0.95</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-123.21</t>
+          <t>-125.03</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>44770.0</t>
+          <t>90242.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>69764.2</v>
+        <v>80214.39999999999</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>78924.9</t>
+          <t>70704.0</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>210122.46</v>
+        <v>209175.5</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>-9160</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-21135.47664461804</t>
+          <t>-21534.35782417894</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-27083.51188596481</t>
+          <t>-23728.20431176394</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>44770.0</t>
+          <t>90242.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7654,7 +7654,7 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
@@ -7664,12 +7664,12 @@
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7719,22 +7719,22 @@
       </c>
       <c r="CQ15" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7756,7 +7756,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1120.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7791,17 +7791,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>13.49</t>
+          <t>18.46</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -7886,12 +7886,12 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>-0.85</v>
+        <v>0.67</v>
       </c>
       <c r="AV16" t="n">
-        <v>-5.92</v>
+        <v>-5.36</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>52.58</v>
+        <v>52.38</v>
       </c>
       <c r="BA16" t="n">
         <v>52.46</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-64.29</t>
+          <t>-42.21</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-1.3</v>
+        <v>-1.25</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.79</v>
+        <v>-0.88</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-123.21</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>55487.0</t>
+          <t>44770.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>73479.2</v>
+        <v>69764.2</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>119450.5</t>
+          <t>78924.9</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>212397.56</v>
+        <v>210122.46</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-45971</t>
+          <t>-9160</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-20054.0156916459</t>
+          <t>-21135.47664461804</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-26037.54013889589</t>
+          <t>-27083.51188596481</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>55487.0</t>
+          <t>44770.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2486.0</t>
+          <t>1120.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>12.7</t>
+          <t>19.85</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-38.18</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.02</v>
+        <v>-0.85</v>
       </c>
       <c r="AV17" t="n">
-        <v>-6.34</v>
+        <v>-5.92</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>49.51000000000001</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>52.86</v>
+        <v>52.58</v>
       </c>
       <c r="BA17" t="n">
-        <v>52.54</v>
+        <v>52.46</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>49.23</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-87.87</t>
+          <t>-64.29</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-1.24</v>
+        <v>-1.3</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.66</v>
+        <v>-0.79</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-117.42</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>124201.0</t>
+          <t>55487.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>76793</v>
+        <v>73479.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>124218.1</t>
+          <t>119450.5</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>213523.76</v>
+        <v>212397.56</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-47425</t>
+          <t>-45971</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-18966.10215578226</t>
+          <t>-20054.0156916459</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-24761.63263812255</t>
+          <t>-26037.54013889589</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>124201.0</t>
+          <t>55487.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,42 +8740,42 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
+          <t>-1.19</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2486.0</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>49.5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>19.12</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>1.6</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1713.0</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>50.1</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>11.64</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-56.32</t>
+          <t>-38.18</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>1.56</v>
+        <v>-0.02</v>
       </c>
       <c r="AV18" t="n">
-        <v>-7.14</v>
+        <v>-6.34</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.51000000000001</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>53.12</v>
+        <v>52.86</v>
       </c>
       <c r="BA18" t="n">
-        <v>52.62</v>
+        <v>52.54</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>48.94</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-133.25</t>
+          <t>-87.87</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-1.2</v>
+        <v>-1.24</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.52</v>
+        <v>-0.66</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-113.60</t>
+          <t>-117.42</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>86372.0</t>
+          <t>124201.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>60571.2</v>
+        <v>76793</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>138654.5</t>
+          <t>124218.1</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>215595.82</v>
+        <v>213523.76</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-78083</t>
+          <t>-47425</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-17912.3693408113</t>
+          <t>-18966.10215578226</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-29416.77789994201</t>
+          <t>-24761.63263812255</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>86372.0</t>
+          <t>124201.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>767.0</t>
+          <t>1713.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>18.14</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-66.67</t>
+          <t>-56.32</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-01-07 00:00:00</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-1.83</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>9.78</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>0.61</v>
+        <v>1.56</v>
       </c>
       <c r="AV19" t="n">
-        <v>-7.97</v>
+        <v>-7.14</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>49.33</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>53.24</v>
+        <v>53.12</v>
       </c>
       <c r="BA19" t="n">
-        <v>52.78</v>
+        <v>52.62</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>48.82</t>
+          <t>48.94</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-248.04</t>
+          <t>-133.25</t>
         </is>
       </c>
       <c r="BD19" t="n">
         <v>-1.2</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.34</v>
+        <v>-0.52</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-109.07</t>
+          <t>-113.60</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>85243.1673553719</t>
+          <t>121248.0614754098</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>37991.0</t>
+          <t>86372.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>61193.6</v>
+        <v>60571.2</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>183607.2</t>
+          <t>138654.5</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>217110.84</v>
+        <v>215595.82</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-122413</t>
+          <t>-78083</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-15820.65869369663</t>
+          <t>-17912.3693408113</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-30963.27906325758</t>
+          <t>-29416.77789994201</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>37991.0</t>
+          <t>86372.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>29.62</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9602,7 +9602,7 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>13.16</t>
+          <t>14.2</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>50.79</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>7120</t>
+          <t>7685</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9672,17 +9672,17 @@
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>51.1</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>49.2</t>
+          <t>49.6</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>50.1</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4610.828</t>
+          <t>4753.977</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>539.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9749,7 +9749,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-32.47</t>
+          <t>-23.18</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-22.00</t>
+          <t>-21.42</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,75 +9910,75 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-1.21</v>
+        <v>-0.59</v>
       </c>
       <c r="AV20" t="n">
-        <v>-3.31</v>
+        <v>-2.7</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>545.6</t>
+          <t>546.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>564.3</v>
+        <v>561.35</v>
       </c>
       <c r="BA20" t="n">
-        <v>607.84</v>
+        <v>604.42</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>636.56</t>
+          <t>635.09</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-18.27</v>
+        <v>-17.66</v>
       </c>
       <c r="BE20" t="n">
-        <v>-19.04</v>
+        <v>-18.76</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-182.05</t>
+          <t>-183.54</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>3357815157.047521</t>
+          <t>3785820750.891393</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>2493007382.0</t>
+          <t>2576882341.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>2277544053.4</v>
+        <v>2399229287.8</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>3372583140.2</t>
+          <t>3123362656.5</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>2805787563.28</v>
+        <v>2807247067.2</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-1095039086</t>
+          <t>-724133368</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>93624751.32030897</t>
+          <t>47815936.12187205</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-195905446.9469471</t>
+          <t>-204132547.4695311</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>2493007382.0</t>
+          <t>2576882341.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>400348</t>
+          <t>403319</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>545.0</t>
+          <t>539.0</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>548.0</t>
+          <t>547.0</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>538.0</t>
+          <t>535.0</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>539.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>5388.987</t>
+          <t>4610.828</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>546.0</t>
+          <t>539.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-32.47</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10246,7 +10246,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-20.98</t>
+          <t>-22.00</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,75 +10397,75 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>65.71</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.21</v>
       </c>
       <c r="AV21" t="n">
-        <v>-3.77</v>
+        <v>-3.31</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>546.4</t>
+          <t>545.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>567.8</v>
+        <v>564.3</v>
       </c>
       <c r="BA21" t="n">
-        <v>611.02</v>
+        <v>607.84</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>637.89</t>
+          <t>636.56</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-18.37</v>
+        <v>-18.27</v>
       </c>
       <c r="BE21" t="n">
-        <v>-19.23</v>
+        <v>-19.04</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-182.88</t>
+          <t>-184.77</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>3357815157.047521</t>
+          <t>3785820750.891393</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>2971429132.0</t>
+          <t>2493007382.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>2179064559.4</v>
+        <v>2277544053.4</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>3856732354.3</t>
+          <t>3372583140.2</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>2779834991.66</v>
+        <v>2805787563.28</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-1677667794</t>
+          <t>-1095039086</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>146266605.5507192</t>
+          <t>93624751.32030897</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-168169220.3451495</t>
+          <t>-195905446.9469471</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>2971429132.0</t>
+          <t>2493007382.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10556,7 +10556,7 @@
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
@@ -10586,12 +10586,12 @@
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>400348</t>
+          <t>403319</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>555.0</t>
+          <t>545.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>548.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>546.0</t>
+          <t>538.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>546.0</t>
+          <t>539.0</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4418.986</t>
+          <t>5388.987</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>555.0</t>
+          <t>546.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,7 +10713,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-2.97</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-40.78</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10733,7 +10733,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-19.68</t>
+          <t>-20.98</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,75 +10884,75 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>65.71</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>1.39</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AV22" t="n">
-        <v>-4.11</v>
+        <v>-3.77</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>547.4</t>
+          <t>546.4</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>570.85</v>
+        <v>567.8</v>
       </c>
       <c r="BA22" t="n">
-        <v>614.08</v>
+        <v>611.02</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>639.12</t>
+          <t>637.89</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-18.94</v>
+        <v>-18.37</v>
       </c>
       <c r="BE22" t="n">
-        <v>-19.44</v>
+        <v>-19.23</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-183.81</t>
+          <t>-185.63</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>3357815157.047521</t>
+          <t>3785820750.891393</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>2465699962.0</t>
+          <t>2971429132.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>2526011013.6</v>
+        <v>2179064559.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>4265162260.7</t>
+          <t>3856732354.3</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>2736629025.76</v>
+        <v>2779834991.66</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-1739151247</t>
+          <t>-1677667794</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>203436755.7136044</t>
+          <t>146266605.5507192</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-173799469.1159687</t>
+          <t>-168169220.3451495</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>2465699962.0</t>
+          <t>2971429132.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-17.53</t>
+          <t>-18.87</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11043,7 +11043,7 @@
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>400348</t>
+          <t>403319</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>554.0</t>
+          <t>555.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>552.0</t>
+          <t>546.0</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>555.0</t>
+          <t>546.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11165,7 +11165,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2714.103</t>
+          <t>4418.986</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>548.0</t>
+          <t>555.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,7 +11200,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-2.21</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-31.76</t>
+          <t>-40.78</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-19.68</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,75 +11371,75 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>0.51</v>
+        <v>1.39</v>
       </c>
       <c r="AV23" t="n">
-        <v>-5</v>
+        <v>-4.11</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>545.2</t>
+          <t>547.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>573.9</v>
+        <v>570.85</v>
       </c>
       <c r="BA23" t="n">
-        <v>616.8</v>
+        <v>614.08</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>640.12</t>
+          <t>639.12</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-20.32</v>
+        <v>-18.94</v>
       </c>
       <c r="BE23" t="n">
-        <v>-19.57</v>
+        <v>-19.44</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-184.35</t>
+          <t>-186.59</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>3357815157.047521</t>
+          <t>3785820750.891393</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>1489127622.0</t>
+          <t>2465699962.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>3131804564.8</v>
+        <v>2526011013.6</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>4589353287.0</t>
+          <t>4265162260.7</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>2708576977.62</v>
+        <v>2736629025.76</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-1457548722</t>
+          <t>-1739151247</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>272025160.2280722</t>
+          <t>203436755.7136044</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-121450289.5344262</t>
+          <t>-173799469.1159687</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>1489127622.0</t>
+          <t>2465699962.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-18.57</t>
+          <t>-17.53</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11530,7 +11530,7 @@
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -11550,22 +11550,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>400348</t>
+          <t>403319</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>542.0</t>
+          <t>554.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>553.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>541.0</t>
+          <t>552.0</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>548.0</t>
+          <t>555.0</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3645.565</t>
+          <t>2714.103</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>540.0</t>
+          <t>548.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-0.19</t>
+          <t>-0.92</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -11697,7 +11697,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-24.04</t>
+          <t>-31.76</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11707,7 +11707,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-21.85</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,75 +11858,75 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>-0.88</v>
+        <v>0.51</v>
       </c>
       <c r="AV24" t="n">
-        <v>-5.56</v>
+        <v>-5</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>544.8</t>
+          <t>545.2</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>576.85</v>
+        <v>573.9</v>
       </c>
       <c r="BA24" t="n">
-        <v>619.5599999999999</v>
+        <v>616.8</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>641.09</t>
+          <t>640.12</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-21.06</v>
+        <v>-20.32</v>
       </c>
       <c r="BE24" t="n">
-        <v>-19.38</v>
+        <v>-19.57</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-183.55</t>
+          <t>-187.15</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>3357815157.047521</t>
+          <t>3785820750.891393</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>1968456169.0</t>
+          <t>1489127622.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>3847496025.2</v>
+        <v>3131804564.8</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>5065100698.0</t>
+          <t>4589353287.0</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>2710153011.62</v>
+        <v>2708576977.62</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-1217604672</t>
+          <t>-1457548722</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>343566151.093981</t>
+          <t>272025160.2280722</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>62304513.77972078</t>
+          <t>-121450289.5344262</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>1968456169.0</t>
+          <t>1489127622.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-19.76</t>
+          <t>-18.57</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="BZ24" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CA24" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
@@ -12047,12 +12047,12 @@
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>400348</t>
+          <t>403319</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>545.0</t>
+          <t>542.0</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
+          <t>553.0</t>
+        </is>
+      </c>
+      <c r="CS24" t="inlineStr">
+        <is>
+          <t>541.0</t>
+        </is>
+      </c>
+      <c r="CT24" t="inlineStr">
+        <is>
           <t>548.0</t>
-        </is>
-      </c>
-      <c r="CS24" t="inlineStr">
-        <is>
-          <t>535.0</t>
-        </is>
-      </c>
-      <c r="CT24" t="inlineStr">
-        <is>
-          <t>540.0</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3643.793</t>
+          <t>3645.565</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>540.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,7 +12174,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-10.97</t>
+          <t>-24.04</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-21.42</t>
+          <t>-21.85</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,12 +12345,12 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
@@ -12364,56 +12364,56 @@
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.88</v>
       </c>
       <c r="AV25" t="n">
-        <v>-5.72</v>
+        <v>-5.56</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>546.8</t>
+          <t>544.8</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>580</v>
+        <v>576.85</v>
       </c>
       <c r="BA25" t="n">
-        <v>622.46</v>
+        <v>619.5599999999999</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>642.08</t>
+          <t>641.09</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-10.19</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-20.89</v>
+        <v>-21.06</v>
       </c>
       <c r="BE25" t="n">
-        <v>-18.96</v>
+        <v>-19.38</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-181.74</t>
+          <t>-186.31</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>3357815157.047521</t>
+          <t>3785820750.891393</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>2000609912.0</t>
+          <t>1968456169.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>4467622227</v>
+        <v>3847496025.2</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>5018129405.0</t>
+          <t>5065100698.0</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>2695477171.12</v>
+        <v>2710153011.62</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-550507178</t>
+          <t>-1217604672</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>394704630.6056647</t>
+          <t>343566151.093981</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>271229584.4149408</t>
+          <t>62304513.77972078</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>2000609912.0</t>
+          <t>1968456169.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-19.76</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12504,7 +12504,7 @@
       </c>
       <c r="BZ25" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CA25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>400348</t>
+          <t>403319</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>554.0</t>
+          <t>545.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
-          <t>557.0</t>
+          <t>548.0</t>
         </is>
       </c>
       <c r="CS25" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>535.0</t>
         </is>
       </c>
       <c r="CT25" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>540.0</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>8521.76</t>
+          <t>3643.793</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>551.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,7 +12661,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>-2.23</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>-10.97</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>-21.42</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,17 +12832,17 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr">
@@ -12851,56 +12851,56 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>0.51</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AV26" t="n">
-        <v>-5.95</v>
+        <v>-5.72</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>548.2</t>
+          <t>546.8</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>582.9</v>
+        <v>580</v>
       </c>
       <c r="BA26" t="n">
-        <v>625.3</v>
+        <v>622.46</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>643.02</t>
+          <t>642.08</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-10.19</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-20.68</v>
+        <v>-20.89</v>
       </c>
       <c r="BE26" t="n">
-        <v>-18.48</v>
+        <v>-18.96</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-179.65</t>
+          <t>-184.44</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>3357815157.047521</t>
+          <t>3785820750.891393</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>4706161403.0</t>
+          <t>2000609912.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>5534400149.2</v>
+        <v>4467622227</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>4956648855.5</t>
+          <t>5018129405.0</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>2681952710.56</v>
+        <v>2695477171.12</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>577751293</t>
+          <t>-550507178</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>417154639.0039782</t>
+          <t>394704630.6056647</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>556562156.2718658</t>
+          <t>271229584.4149408</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>4706161403.0</t>
+          <t>2000609912.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -12991,7 +12991,7 @@
       </c>
       <c r="BZ26" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CA26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>400348</t>
+          <t>403319</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>548.0</t>
+          <t>554.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>556.0</t>
+          <t>557.0</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>545.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>551.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10056.098</t>
+          <t>8521.76</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>551.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,7 +13148,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-1.47</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13168,7 +13168,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>-20.26</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>46.48</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,75 +13319,75 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>-0.87</v>
+        <v>0.51</v>
       </c>
       <c r="AV27" t="n">
-        <v>-6.33</v>
+        <v>-5.95</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>548.8</t>
+          <t>548.2</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>585.9</v>
+        <v>582.9</v>
       </c>
       <c r="BA27" t="n">
-        <v>627.96</v>
+        <v>625.3</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>644.04</t>
+          <t>643.02</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-20.92</v>
+        <v>-20.68</v>
       </c>
       <c r="BE27" t="n">
-        <v>-17.93</v>
+        <v>-18.48</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-177.28</t>
+          <t>-182.29</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>3357815157.047521</t>
+          <t>3785820750.891393</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>5494667718.0</t>
+          <t>4706161403.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>6004313507.8</v>
+        <v>5534400149.2</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>4646636108.5</t>
+          <t>4956648855.5</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>2640209392.16</v>
+        <v>2681952710.56</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>1357677399</t>
+          <t>577751293</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>391807817.6825441</t>
+          <t>417154639.0039782</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>654422379.3077617</t>
+          <t>556562156.2718658</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>5494667718.0</t>
+          <t>4706161403.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-19.17</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="BZ27" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CA27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>400348</t>
+          <t>403319</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>547.0</t>
+          <t>548.0</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
+          <t>556.0</t>
+        </is>
+      </c>
+      <c r="CS27" t="inlineStr">
+        <is>
+          <t>545.0</t>
+        </is>
+      </c>
+      <c r="CT27" t="inlineStr">
+        <is>
           <t>551.0</t>
-        </is>
-      </c>
-      <c r="CS27" t="inlineStr">
-        <is>
-          <t>540.0</t>
-        </is>
-      </c>
-      <c r="CT27" t="inlineStr">
-        <is>
-          <t>544.0</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9190.451</t>
+          <t>10056.098</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>546.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,7 +13635,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-1.3</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -13645,7 +13645,7 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>43.63</t>
+          <t>29.22</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13655,7 +13655,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>-40.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-20.98</t>
+          <t>-21.27</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>46.48</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-1.65</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,12 +13806,12 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>173</t>
+          <t>148</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
@@ -13825,56 +13825,56 @@
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-1.69</v>
+        <v>-0.87</v>
       </c>
       <c r="AV28" t="n">
-        <v>-5.75</v>
+        <v>-6.33</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-6.58</t>
+          <t>-6.7</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-2.22</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>555.4</t>
+          <t>548.8</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>589.3</v>
+        <v>585.9</v>
       </c>
       <c r="BA28" t="n">
-        <v>630.8200000000001</v>
+        <v>627.96</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>645.16</t>
+          <t>644.04</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-17.66</t>
+          <t>-16.70</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-20.21</v>
+        <v>-20.92</v>
       </c>
       <c r="BE28" t="n">
-        <v>-17.18</v>
+        <v>-17.93</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>23.2</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-174.06</t>
+          <t>-179.84</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>3357815157.047521</t>
+          <t>3785820750.891393</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>5067584924.0</t>
+          <t>5494667718.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>6046902009.2</v>
+        <v>6004313507.8</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>4210179461.7</t>
+          <t>4646636108.5</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>2592540360.14</v>
+        <v>2640209392.16</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>1836722547</t>
+          <t>1357677399</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>344059715.5688681</t>
+          <t>391807817.6825441</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>686367650.6337652</t>
+          <t>654422379.3077617</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>5067584924.0</t>
+          <t>5494667718.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>-19.17</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13965,7 +13965,7 @@
       </c>
       <c r="BZ28" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="CA28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>6.31</t>
+          <t>6.26</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>11.51</t>
+          <t>11.59</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>27.75</t>
+          <t>27.65</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>400348</t>
+          <t>403319</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>552.0</t>
+          <t>547.0</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
-          <t>555.0</t>
+          <t>551.0</t>
         </is>
       </c>
       <c r="CS28" t="inlineStr">
         <is>
-          <t>546.0</t>
+          <t>540.0</t>
         </is>
       </c>
       <c r="CT28" t="inlineStr">
         <is>
-          <t>546.0</t>
+          <t>544.0</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/BIOS(嵌入式軟體).xlsx
+++ b/Result/checksun_type/BIOS(嵌入式軟體).xlsx
@@ -938,7 +938,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>價_量;【d1】;【x】看好</t>
+          <t>價_量;【b1】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.49</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>745.0</t>
+          <t>422.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,12 +978,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.70</t>
+          <t>30.59</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-14.31</t>
+          <t>-14.89</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025/06/30</t>
+          <t>2025/09/10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>258.5</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1123,87 +1123,87 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>9.70</t>
+          <t>5.49</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>422</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>82.35</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>65.55</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>2.45</v>
+        <v>1.2</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.35</v>
+        <v>0.78</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-6.29</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>216.2</t>
+          <t>217.4</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>215.45</v>
+        <v>215.72</v>
       </c>
       <c r="BA2" t="n">
-        <v>215.68</v>
+        <v>215.3</v>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>230.15</t>
+          <t>229.67</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>193.33</t>
+          <t>574.40</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>0.26</v>
+        <v>0.55</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0.28</v>
+        <v>-0.12</v>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-100.79</t>
+          <t>-100.32</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1222,43 +1222,43 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>651449.8032786886</t>
+          <t>650403.1503067485</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>164555.0</t>
+          <t>93091.0</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>88104.39999999999</v>
+        <v>97421.39999999999</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>78176.1</t>
+          <t>74601.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>80684.12</v>
+        <v>79258.38</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-210.6709799189155</t>
+          <t>813.4395496432526</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>6852.011930126813</t>
+          <t>6446.047462235176</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>164555.0</t>
+          <t>93091.0</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1268,17 +1268,17 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-14.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1323,22 +1323,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>9.59</t>
+          <t>9.52</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1363,12 +1363,12 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
@@ -1388,22 +1388,22 @@
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>215.0</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>225.5</t>
+          <t>224.0</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>221.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>3.49</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>294.0</t>
+          <t>745.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.48</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1535,7 +1535,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>-14.31</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025/06/30</t>
+          <t>2025/09/10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>258.5</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1610,17 +1610,17 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>3.83</t>
+          <t>9.70</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1631,66 +1631,66 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>422</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>14.29</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>30.4</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-0.5600000000000001</v>
+        <v>2.45</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-6.36</t>
+          <t>-6.29</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>215.2</t>
+          <t>216.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>214.9</v>
+        <v>215.45</v>
       </c>
       <c r="BA3" t="n">
-        <v>215.99</v>
+        <v>215.68</v>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>230.66</t>
+          <t>230.15</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>38.18</t>
+          <t>193.33</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>-0.26</v>
+        <v>0.26</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.42</v>
+        <v>-0.28</v>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-101.17</t>
+          <t>-100.79</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1709,43 +1709,43 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>651449.8032786886</t>
+          <t>650403.1503067485</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>62940.0</t>
+          <t>164555.0</t>
         </is>
       </c>
       <c r="BK3" t="n">
-        <v>63670.8</v>
+        <v>88104.39999999999</v>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>68084.7</t>
+          <t>78176.1</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>79080.74000000001</v>
+        <v>80684.12</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-4413</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-1494.795145381775</t>
+          <t>-210.6709799189155</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>-469.6106846753682</t>
+          <t>6852.011930126813</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>62940.0</t>
+          <t>164555.0</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.59</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
@@ -1875,22 +1875,22 @@
       </c>
       <c r="CQ3" t="inlineStr">
         <is>
+          <t>215.0</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr">
+        <is>
+          <t>225.5</t>
+        </is>
+      </c>
+      <c r="CS3" t="inlineStr">
+        <is>
           <t>213.0</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
-        <is>
-          <t>216.0</t>
-        </is>
-      </c>
-      <c r="CS3" t="inlineStr">
-        <is>
-          <t>212.0</t>
-        </is>
-      </c>
       <c r="CT3" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>221.5</t>
         </is>
       </c>
       <c r="CU3" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>439.0</t>
+          <t>294.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1937,7 +1937,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1947,17 +1947,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.84</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-7.81</t>
+          <t>-6.48</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-17.21</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025/06/30</t>
+          <t>2025/09/10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>258.5</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.14</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2097,17 +2097,17 @@
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>3.83</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2118,66 +2118,66 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>422</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.29</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>30.4</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-1.16</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.37</v>
+        <v>0.14</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-0.81</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-6.38</t>
+          <t>-6.36</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>215.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>214.7</v>
+        <v>214.9</v>
       </c>
       <c r="BA4" t="n">
-        <v>216.46</v>
+        <v>215.99</v>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>231.2</t>
+          <t>230.66</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>65.90</t>
+          <t>38.18</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>-0.16</v>
+        <v>-0.26</v>
       </c>
       <c r="BE4" t="n">
-        <v>-0.46</v>
+        <v>-0.42</v>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-101.28</t>
+          <t>-101.17</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2196,43 +2196,43 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>651449.8032786886</t>
+          <t>650403.1503067485</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>93569.0</t>
+          <t>62940.0</t>
         </is>
       </c>
       <c r="BK4" t="n">
-        <v>61556.2</v>
+        <v>63670.8</v>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>66771.8</t>
+          <t>68084.7</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>80046.16</v>
+        <v>79080.74000000001</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-5215</t>
+          <t>-4413</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-1681.192320055668</t>
+          <t>-1494.795145381775</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-24.97832422579813</t>
+          <t>-469.6106846753682</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>93569.0</t>
+          <t>62940.0</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>-17.60</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2302,17 +2302,17 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="CQ4" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CR4" t="inlineStr">
         <is>
-          <t>220.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>210.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>334.0</t>
+          <t>439.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2424,159 +2424,159 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>213.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-7.81</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2024-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2024-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>253.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>258.5</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>565.0</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>543.0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-17.60</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>-53.41</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>258.5</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>-0.31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>234.0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>217.5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>2025/09/25</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>258.5</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
           <t>218.5</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-12.87</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2024-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>253.0</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>258.5</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>565.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>543.0</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-15.47</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>-53.41</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>257.5</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>0.11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>234.0</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>2025/07/30</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>217.5</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>2025/09/25</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>258.5</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>2025/08/19</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>218.5</t>
-        </is>
-      </c>
       <c r="AK5" t="inlineStr">
         <is>
           <t>2025-09-18 00:00:00</t>
@@ -2584,17 +2584,17 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2605,66 +2605,66 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>422</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>76.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>43.59</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>1.25</v>
+        <v>-1.16</v>
       </c>
       <c r="AV5" t="n">
-        <v>0.54</v>
+        <v>0.37</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-0.81</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.38</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>215.8</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>214.65</v>
+        <v>214.7</v>
       </c>
       <c r="BA5" t="n">
-        <v>217.09</v>
+        <v>216.46</v>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>231.59</t>
+          <t>231.2</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>114.72</t>
+          <t>65.90</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>0.08</v>
+        <v>-0.16</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.53</v>
+        <v>-0.46</v>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
@@ -2673,7 +2673,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-101.49</t>
+          <t>-101.28</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2683,43 +2683,43 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>651449.8032786886</t>
+          <t>650403.1503067485</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>72952.0</t>
+          <t>93569.0</t>
         </is>
       </c>
       <c r="BK5" t="n">
-        <v>55536.6</v>
+        <v>61556.2</v>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>63736.3</t>
+          <t>66771.8</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>81247.39999999999</v>
+        <v>80046.16</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-8199</t>
+          <t>-5215</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-1982.32213747928</t>
+          <t>-1681.192320055668</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>-2670.575726289782</t>
+          <t>-24.97832422579813</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>72952.0</t>
+          <t>93569.0</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2729,17 +2729,17 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>-15.47</t>
+          <t>-3.18</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2784,22 +2784,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2824,12 +2824,12 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
@@ -2849,22 +2849,22 @@
       </c>
       <c r="CQ5" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>220.5</t>
         </is>
       </c>
       <c r="CR5" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>220.5</t>
         </is>
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>210.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>218.5</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
@@ -2896,12 +2896,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.16</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>218.0</t>
+          <t>334.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>218.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.44</t>
+          <t>-12.87</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>-15.47</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -3006,12 +3006,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025/06/30</t>
+          <t>2025/09/10</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>258.5</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.25</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -3071,17 +3071,17 @@
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>4.35</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3092,38 +3092,38 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>422</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>76.92</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>43.59</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>-0.83</v>
+        <v>1.25</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.65</v>
+        <v>0.54</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-6.23</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -3132,26 +3132,26 @@
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>214.4</v>
+        <v>214.65</v>
       </c>
       <c r="BA6" t="n">
-        <v>217.53</v>
+        <v>217.09</v>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>231.98</t>
+          <t>231.59</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>73.27</t>
+          <t>114.72</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>-0.18</v>
+        <v>0.08</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.53</v>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-101.91</t>
+          <t>-101.49</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -3170,43 +3170,43 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>651449.8032786886</t>
+          <t>650403.1503067485</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>46506.0</t>
+          <t>72952.0</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>51780.6</v>
+        <v>55536.6</v>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>62716.7</t>
+          <t>63736.3</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>84433.48</v>
+        <v>81247.39999999999</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-10936</t>
+          <t>-8199</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-1857.185121331916</t>
+          <t>-1982.32213747928</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-4145.658596156543</t>
+          <t>-2670.575726289782</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>46506.0</t>
+          <t>72952.0</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>-17.21</t>
+          <t>-0.68</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>9.46</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
@@ -3311,12 +3311,12 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
@@ -3336,22 +3336,22 @@
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>218.5</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>-1.16</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>218.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3408,17 +3408,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-17.44</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-16.25</t>
+          <t>-17.21</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025/06/30</t>
+          <t>2025/09/10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>258.5</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3508,7 +3508,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.56</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3579,66 +3579,66 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>422</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>46.15</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>-0.23</v>
+        <v>-0.83</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.21</v>
+        <v>0.65</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-6.23</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>215.8</t>
         </is>
       </c>
       <c r="AZ7" t="n">
         <v>214.4</v>
       </c>
       <c r="BA7" t="n">
-        <v>217.82</v>
+        <v>217.53</v>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>232.36</t>
+          <t>231.98</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>93.03</t>
+          <t>73.27</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>-0.06</v>
+        <v>-0.18</v>
       </c>
       <c r="BE7" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-102.26</t>
+          <t>-101.91</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3657,43 +3657,43 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>651449.8032786886</t>
+          <t>650403.1503067485</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>42387.0</t>
+          <t>46506.0</t>
         </is>
       </c>
       <c r="BK7" t="n">
-        <v>68247.8</v>
+        <v>51780.6</v>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>76005.1</t>
+          <t>62716.7</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>84793.44</v>
+        <v>84433.48</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-7757</t>
+          <t>-10936</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-1441.099035000165</t>
+          <t>-1857.185121331916</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-3271.360603246329</t>
+          <t>-4145.658596156543</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>42387.0</t>
+          <t>46506.0</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3703,17 +3703,17 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-16.25</t>
+          <t>-2.73</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3768,12 +3768,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
@@ -3798,12 +3798,12 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>213.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>241.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3895,17 +3895,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-6.76</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-16.63</t>
+          <t>-16.25</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025/06/30</t>
+          <t>2025/09/10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>258.5</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>3.14</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4066,33 +4066,33 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>422</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
+          <t>46.15</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
           <t>30.77</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>43.16</t>
-        </is>
-      </c>
       <c r="AU8" t="n">
-        <v>-0.87</v>
+        <v>-0.23</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.41</v>
+        <v>1.21</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
@@ -4102,30 +4102,30 @@
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>217.4</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>214.38</v>
+        <v>214.4</v>
       </c>
       <c r="BA8" t="n">
-        <v>218.08</v>
+        <v>217.82</v>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>232.64</t>
+          <t>232.36</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>85.15</t>
+          <t>93.03</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="BE8" t="n">
-        <v>-1</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
@@ -4134,7 +4134,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-102.79</t>
+          <t>-102.26</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -4144,43 +4144,43 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>651449.8032786886</t>
+          <t>650403.1503067485</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>52367.0</t>
+          <t>42387.0</t>
         </is>
       </c>
       <c r="BK8" t="n">
-        <v>72498.60000000001</v>
+        <v>68247.8</v>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>77751.7</t>
+          <t>76005.1</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>85915.12</v>
+        <v>84793.44</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-5253</t>
+          <t>-7757</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-1108.324204409954</t>
+          <t>-1441.099035000165</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-1464.20773468721</t>
+          <t>-3271.360603246329</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>52367.0</t>
+          <t>42387.0</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -4190,17 +4190,17 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>-16.63</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -4245,7 +4245,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>9.33</t>
+          <t>9.37</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
@@ -4310,22 +4310,22 @@
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>216.0</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>214.0</t>
+          <t>213.0</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>215.5</t>
+          <t>216.5</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
@@ -4357,12 +4357,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>296.0</t>
+          <t>241.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.16</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-5.23</t>
+          <t>-6.76</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-16.63</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025/06/30</t>
+          <t>2025/09/10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>257.5</t>
+          <t>258.5</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4482,7 +4482,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.35</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>3.85</t>
+          <t>3.14</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4553,66 +4553,66 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>422</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>15.38</t>
+          <t>30.77</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>66.24</t>
+          <t>43.16</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-1.15</v>
+        <v>-0.87</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>217.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>214.25</v>
+        <v>214.38</v>
       </c>
       <c r="BA9" t="n">
-        <v>218.5</v>
+        <v>218.08</v>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>232.79</t>
+          <t>232.64</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>86.65</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>-0.16</v>
+        <v>-0.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>-1.21</v>
+        <v>-1</v>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>-103.39</t>
+          <t>-102.79</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4631,43 +4631,43 @@
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>651449.8032786886</t>
+          <t>650403.1503067485</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>63471.0</t>
+          <t>52367.0</t>
         </is>
       </c>
       <c r="BK9" t="n">
-        <v>71987.39999999999</v>
+        <v>72498.60000000001</v>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>75957.1</t>
+          <t>77751.7</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>86877.86</v>
+        <v>85915.12</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-3969</t>
+          <t>-5253</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-1043.618107995907</t>
+          <t>-1108.324204409954</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>100.4466394932097</t>
+          <t>-1464.20773468721</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>63471.0</t>
+          <t>52367.0</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4677,17 +4677,17 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-17.02</t>
+          <t>-2.05</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4742,12 +4742,12 @@
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>9.29</t>
+          <t>9.33</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4757,7 +4757,7 @@
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
@@ -4797,22 +4797,22 @@
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
+          <t>215.5</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr">
+        <is>
           <t>220.0</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
-        <is>
-          <t>220.0</t>
-        </is>
-      </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>212.0</t>
+          <t>214.0</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>214.5</t>
+          <t>215.5</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
@@ -4844,12 +4844,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-1.82</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>248.0</t>
+          <t>296.0</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4859,159 +4859,159 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>214.5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>-0.1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-5.23</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>-90.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-09-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2024-10-17 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2024-10-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>253.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>258.5</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>565.0</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>543.0</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>-17.02</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>-53.41</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025/09/10</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>258.5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>234.0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>2025/07/30</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>217.5</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2025/09/25</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>258.5</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/08/19</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
           <t>218.5</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.08</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-4.60</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>-90.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-09-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-09-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2024-10-17 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2024-10-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>253.0</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>258.5</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>565.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>543.0</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-15.47</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>-53.41</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2025/06/30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>257.5</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>234.0</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>2025/07/30</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>217.5</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>2025/09/25</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>258.5</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>2025/08/19</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>218.5</t>
-        </is>
-      </c>
       <c r="AK10" t="inlineStr">
         <is>
           <t>2025-09-18 00:00:00</t>
@@ -5019,17 +5019,17 @@
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>3.23</t>
+          <t>3.85</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-1.36</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5040,66 +5040,66 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>422</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>83.33</t>
+          <t>15.38</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>94.44</t>
+          <t>66.24</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>0.78</v>
+        <v>-1.15</v>
       </c>
       <c r="AV10" t="n">
         <v>1.28</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-6.08</t>
+          <t>-6.14</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>216.8</t>
+          <t>217.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>214.05</v>
+        <v>214.25</v>
       </c>
       <c r="BA10" t="n">
-        <v>218.89</v>
+        <v>218.5</v>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>233.05</t>
+          <t>232.79</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>94.92</t>
+          <t>86.65</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.16</v>
       </c>
       <c r="BE10" t="n">
-        <v>-1.48</v>
+        <v>-1.21</v>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-104.12</t>
+          <t>-103.39</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -5118,43 +5118,43 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>651449.8032786886</t>
+          <t>650403.1503067485</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>54172.0</t>
+          <t>63471.0</t>
         </is>
       </c>
       <c r="BK10" t="n">
-        <v>71936</v>
+        <v>71987.39999999999</v>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>75405.1</t>
+          <t>75957.1</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>87614.14</v>
+        <v>86877.86</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-3469</t>
+          <t>-3969</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-1251.629880266656</t>
+          <t>-1043.618107995907</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>1142.365508340474</t>
+          <t>100.4466394932097</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>54172.0</t>
+          <t>63471.0</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -5164,17 +5164,17 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2026/01/08</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>-15.47</t>
+          <t>-2.50</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5229,12 +5229,12 @@
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>9.46</t>
+          <t>9.29</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>2.93</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>33.51</t>
+          <t>33.28</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>21.29</t>
+          <t>21.18</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10043</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>224.0</t>
+          <t>220.0</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>212.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>218.5</t>
+          <t>214.5</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10905.0</t>
+          <t>5322.0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5346,7 +5346,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>65.04</t>
+          <t>64.91</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -5426,7 +5426,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>12.70</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>0.41</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -5506,17 +5506,17 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>13.60</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5527,12 +5527,12 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5546,47 +5546,47 @@
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>10.09</v>
+        <v>9.34</v>
       </c>
       <c r="AV11" t="n">
-        <v>6</v>
+        <v>10.78</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5.07</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>58.44</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>52.45</v>
+        <v>52.76</v>
       </c>
       <c r="BA11" t="n">
-        <v>52.98</v>
+        <v>53.27</v>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>50.75</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>313.22</t>
+          <t>8807.60</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>0.76</v>
+        <v>1.5</v>
       </c>
       <c r="BE11" t="n">
-        <v>-0.35</v>
+        <v>0.02</v>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-109.33</t>
+          <t>-99.56</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5605,48 +5605,48 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>662931.0</t>
+          <t>327958.0</t>
         </is>
       </c>
       <c r="BK11" t="n">
-        <v>329375.2</v>
+        <v>376918.4</v>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>199569.7</t>
+          <t>228566.4</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>233511.96</v>
+        <v>237746.18</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>129805</t>
+          <t>148352</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-394.1269517676747</t>
+          <t>6545.581819641966</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>47049.27419809136</t>
+          <t>44713.98006239498</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>662931.0</t>
+          <t>327958.0</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>65.33</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5706,22 +5706,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
@@ -5746,12 +5746,12 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
@@ -5771,22 +5771,22 @@
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>62.3</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>56.5</t>
+          <t>59.4</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>61.2</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
@@ -5818,12 +5818,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2429.0</t>
+          <t>10905.0</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5833,74 +5833,74 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>61.2</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>4.23</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>65.04</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>7.35</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>47.37</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2026-01-06</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>56.7</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
       <c r="T12" t="inlineStr">
         <is>
           <t>57.4</t>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>7.94</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5943,7 +5943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -5993,17 +5993,17 @@
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>6.21</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6014,12 +6014,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6033,47 +6033,47 @@
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>6.32</v>
+        <v>10.09</v>
       </c>
       <c r="AV12" t="n">
-        <v>2.28</v>
+        <v>6</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>-1.23</t>
+          <t>-1.02</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5.24</t>
+          <t>5.07</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>53.33</t>
+          <t>55.59</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>52.14</v>
+        <v>52.45</v>
       </c>
       <c r="BA12" t="n">
-        <v>52.79</v>
+        <v>52.98</v>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>50.16</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>110.61</t>
+          <t>313.22</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BE12" t="n">
-        <v>-0.63</v>
+        <v>-0.35</v>
       </c>
       <c r="BF12" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-116.64</t>
+          <t>-109.33</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -6092,48 +6092,48 @@
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>136615.0</t>
+          <t>662931.0</t>
         </is>
       </c>
       <c r="BK12" t="n">
-        <v>205743</v>
+        <v>329375.2</v>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>139611.1</t>
+          <t>199569.7</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>222614.5</v>
+        <v>233511.96</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>66131</t>
+          <t>129805</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-9020.19988810568</t>
+          <t>-394.1269517676747</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>12815.11317058292</t>
+          <t>47049.27419809136</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>136615.0</t>
+          <t>662931.0</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -6148,7 +6148,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>46.70</t>
+          <t>58.34</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
@@ -6233,12 +6233,12 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
@@ -6258,22 +6258,22 @@
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>55.9</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>57.1</t>
+          <t>62.3</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>55.1</t>
+          <t>56.5</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>56.7</t>
+          <t>61.2</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
@@ -6295,7 +6295,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>8118.0</t>
+          <t>2429.0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6320,7 +6320,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6330,22 +6330,22 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>8.82</t>
+          <t>11.27</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>42.33</t>
+          <t>47.37</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -6360,7 +6360,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
@@ -6430,7 +6430,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
@@ -6480,17 +6480,17 @@
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>6.21</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
@@ -6501,12 +6501,12 @@
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -6516,51 +6516,51 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>7.72</v>
+        <v>6.32</v>
       </c>
       <c r="AV13" t="n">
-        <v>-0.4</v>
+        <v>2.28</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>-1.24</t>
+          <t>-1.23</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>5.45</t>
+          <t>5.24</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>51.8</t>
+          <t>53.33</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>52.01</v>
+        <v>52.14</v>
       </c>
       <c r="BA13" t="n">
-        <v>52.66</v>
+        <v>52.79</v>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>49.94</t>
+          <t>50.16</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>110.61</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>-0.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BE13" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.63</v>
       </c>
       <c r="BF13" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>-121.24</t>
+          <t>-116.64</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -6579,48 +6579,48 @@
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>453696.0</t>
+          <t>136615.0</t>
         </is>
       </c>
       <c r="BK13" t="n">
-        <v>189517.4</v>
+        <v>205743</v>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>133155.2</t>
+          <t>139611.1</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>221511.36</v>
+        <v>222614.5</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>56362</t>
+          <t>66131</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>-12990.25680786724</t>
+          <t>-9020.19988810568</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>19842.4862323358</t>
+          <t>12815.11317058292</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>453696.0</t>
+          <t>136615.0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-09</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>44.37</t>
+          <t>46.70</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6680,22 +6680,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6705,7 +6705,7 @@
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM13" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN13" t="inlineStr">
@@ -6745,22 +6745,22 @@
       </c>
       <c r="CQ13" t="inlineStr">
         <is>
-          <t>57.0</t>
+          <t>55.9</t>
         </is>
       </c>
       <c r="CR13" t="inlineStr">
         <is>
-          <t>57.8</t>
+          <t>57.1</t>
         </is>
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>53.9</t>
+          <t>55.1</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>56.7</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
@@ -6792,12 +6792,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>9.86</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5690.0</t>
+          <t>8118.0</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6807,7 +6807,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6817,17 +6817,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10.78</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>34.23</t>
+          <t>42.33</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6847,7 +6847,7 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -6967,17 +6967,17 @@
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>14.54</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>8.76</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
@@ -6988,12 +6988,12 @@
       <c r="AP14" t="inlineStr"/>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -7003,51 +7003,51 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>85.96</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AU14" t="n">
-        <v>8.029999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="AV14" t="n">
-        <v>-2.94</v>
+        <v>-0.4</v>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>-0.9</t>
+          <t>-1.24</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>5.65</t>
+          <t>5.45</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>50.54</t>
+          <t>51.8</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>52.07</v>
+        <v>52.01</v>
       </c>
       <c r="BA14" t="n">
-        <v>52.54</v>
+        <v>52.66</v>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>49.73</t>
+          <t>49.94</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>56.01</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>-0.8</v>
+        <v>-0.35</v>
       </c>
       <c r="BE14" t="n">
-        <v>-0.92</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>-124.22</t>
+          <t>-121.24</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -7066,43 +7066,43 @@
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
         <is>
-          <t>303392.0</t>
+          <t>453696.0</t>
         </is>
       </c>
       <c r="BK14" t="n">
-        <v>123618.4</v>
+        <v>189517.4</v>
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>92094.8</t>
+          <t>133155.2</t>
         </is>
       </c>
       <c r="BM14" t="n">
-        <v>213489.6</v>
+        <v>221511.36</v>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>31523</t>
+          <t>56362</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>-18959.84645154052</t>
+          <t>-12990.25680786724</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>-4800.033902029216</t>
+          <t>19842.4862323358</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>303392.0</t>
+          <t>453696.0</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -7122,7 +7122,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>41.27</t>
+          <t>44.37</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -7147,7 +7147,7 @@
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>2.23</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="CI14" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ14" t="inlineStr">
@@ -7207,12 +7207,12 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM14" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN14" t="inlineStr">
@@ -7232,22 +7232,22 @@
       </c>
       <c r="CQ14" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>57.0</t>
         </is>
       </c>
       <c r="CR14" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>57.8</t>
         </is>
       </c>
       <c r="CS14" t="inlineStr">
         <is>
-          <t>50.2</t>
+          <t>53.9</t>
         </is>
       </c>
       <c r="CT14" t="inlineStr">
         <is>
-          <t>54.6</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="CU14" t="inlineStr">
@@ -7269,7 +7269,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>9.86</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1799.0</t>
+          <t>5690.0</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7304,17 +7304,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>18.87</t>
+          <t>14.55</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>13.45</t>
+          <t>34.23</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -7334,7 +7334,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -7404,7 +7404,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -7454,17 +7454,17 @@
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>4.60</t>
+          <t>14.54</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>-2.72</t>
+          <t>8.76</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
@@ -7475,66 +7475,66 @@
       <c r="AP15" t="inlineStr"/>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>70.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>64.75</t>
+          <t>85.96</t>
         </is>
       </c>
       <c r="AU15" t="n">
-        <v>0.02</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="AV15" t="n">
-        <v>-4.74</v>
+        <v>-2.94</v>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.9</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>5.85</t>
+          <t>5.65</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>49.64</t>
+          <t>50.54</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>52.11</v>
+        <v>52.07</v>
       </c>
       <c r="BA15" t="n">
-        <v>52.44</v>
+        <v>52.54</v>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>49.54</t>
+          <t>49.73</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-29.04</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>-1.23</v>
+        <v>-0.8</v>
       </c>
       <c r="BE15" t="n">
-        <v>-0.95</v>
+        <v>-0.92</v>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>-125.03</t>
+          <t>-124.22</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -7553,43 +7553,43 @@
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
         <is>
-          <t>90242.0</t>
+          <t>303392.0</t>
         </is>
       </c>
       <c r="BK15" t="n">
-        <v>80214.39999999999</v>
+        <v>123618.4</v>
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>70704.0</t>
+          <t>92094.8</t>
         </is>
       </c>
       <c r="BM15" t="n">
-        <v>209175.5</v>
+        <v>213489.6</v>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>9510</t>
+          <t>31523</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>-21534.35782417894</t>
+          <t>-18959.84645154052</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>-23728.20431176394</t>
+          <t>-4800.033902029216</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>90242.0</t>
+          <t>303392.0</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>41.27</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -7654,22 +7654,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="CI15" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ15" t="inlineStr">
@@ -7694,12 +7694,12 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM15" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN15" t="inlineStr">
@@ -7724,17 +7724,17 @@
       </c>
       <c r="CR15" t="inlineStr">
         <is>
-          <t>51.2</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CS15" t="inlineStr">
         <is>
-          <t>49.45</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CT15" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>54.6</t>
         </is>
       </c>
       <c r="CU15" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>1799.0</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7781,149 +7781,149 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>49.65</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>22.3</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>13.45</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2026-01-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-01-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-11-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-11-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>56.7</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>57.4</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>53.7</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>5.59</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025/03/14</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>32.85</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2025/12/30</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
           <t>49.9</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>18.46</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>-11.61</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2026-01-06 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2026-01-08 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-11-12 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-11-24 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>56.7</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>57.4</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>2025/06/19</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>38.1</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>2025/11/24</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
         <is>
           <t>53.7</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>5.59</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025/03/14</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>32.85</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>0.13</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>2025/12/30</t>
-        </is>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>49.9</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>2025/06/19</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>38.1</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>2025/11/24</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>53.7</t>
-        </is>
-      </c>
       <c r="AI16" t="inlineStr">
         <is>
           <t>2025/10/20</t>
@@ -7941,17 +7941,17 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>4.60</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>-2.72</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
@@ -7962,66 +7962,66 @@
       <c r="AP16" t="inlineStr"/>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>70.0</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>64.75</t>
         </is>
       </c>
       <c r="AU16" t="n">
-        <v>0.67</v>
+        <v>0.02</v>
       </c>
       <c r="AV16" t="n">
-        <v>-5.36</v>
+        <v>-4.74</v>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>6.18</t>
+          <t>5.85</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>49.57</t>
+          <t>49.64</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>52.38</v>
+        <v>52.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>52.46</v>
+        <v>52.44</v>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>49.4</t>
+          <t>49.54</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-42.21</t>
+          <t>-29.04</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>-1.25</v>
+        <v>-1.23</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.88</v>
+        <v>-0.95</v>
       </c>
       <c r="BF16" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>-123.21</t>
+          <t>-125.03</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -8040,43 +8040,43 @@
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
         <is>
-          <t>44770.0</t>
+          <t>90242.0</t>
         </is>
       </c>
       <c r="BK16" t="n">
-        <v>69764.2</v>
+        <v>80214.39999999999</v>
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>78924.9</t>
+          <t>70704.0</t>
         </is>
       </c>
       <c r="BM16" t="n">
-        <v>210122.46</v>
+        <v>209175.5</v>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>-9160</t>
+          <t>9510</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>-21135.47664461804</t>
+          <t>-21534.35782417894</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>-27083.51188596481</t>
+          <t>-23728.20431176394</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>44770.0</t>
+          <t>90242.0</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>29.11</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -8141,7 +8141,7 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -8151,12 +8151,12 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="CI16" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ16" t="inlineStr">
@@ -8181,12 +8181,12 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM16" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN16" t="inlineStr">
@@ -8206,22 +8206,22 @@
       </c>
       <c r="CQ16" t="inlineStr">
         <is>
-          <t>49.15</t>
+          <t>50.2</t>
         </is>
       </c>
       <c r="CR16" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>51.2</t>
         </is>
       </c>
       <c r="CS16" t="inlineStr">
         <is>
-          <t>48.65</t>
+          <t>49.45</t>
         </is>
       </c>
       <c r="CT16" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>49.65</t>
         </is>
       </c>
       <c r="CU16" t="inlineStr">
@@ -8243,7 +8243,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -8253,12 +8253,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1120.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8278,17 +8278,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>21.91</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-38.49</t>
+          <t>-11.61</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8308,7 +8308,7 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -8373,12 +8373,12 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -8428,17 +8428,17 @@
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
@@ -8449,66 +8449,66 @@
       <c r="AP17" t="inlineStr"/>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>87.88</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>55.14</t>
         </is>
       </c>
       <c r="AU17" t="n">
-        <v>-0.85</v>
+        <v>0.67</v>
       </c>
       <c r="AV17" t="n">
-        <v>-5.92</v>
+        <v>-5.36</v>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>6.55</t>
+          <t>6.18</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>49.47</t>
+          <t>49.57</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>52.58</v>
+        <v>52.38</v>
       </c>
       <c r="BA17" t="n">
         <v>52.46</v>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>49.23</t>
+          <t>49.4</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-64.29</t>
+          <t>-42.21</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>-1.3</v>
+        <v>-1.25</v>
       </c>
       <c r="BE17" t="n">
-        <v>-0.79</v>
+        <v>-0.88</v>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
@@ -8517,7 +8517,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>-120.76</t>
+          <t>-123.21</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -8527,43 +8527,43 @@
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
         <is>
-          <t>55487.0</t>
+          <t>44770.0</t>
         </is>
       </c>
       <c r="BK17" t="n">
-        <v>73479.2</v>
+        <v>69764.2</v>
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>119450.5</t>
+          <t>78924.9</t>
         </is>
       </c>
       <c r="BM17" t="n">
-        <v>212397.56</v>
+        <v>210122.46</v>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>-45971</t>
+          <t>-9160</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>-20054.0156916459</t>
+          <t>-21135.47664461804</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>-26037.54013889589</t>
+          <t>-27083.51188596481</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>55487.0</t>
+          <t>44770.0</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>26.91</t>
+          <t>29.11</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -8628,7 +8628,7 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="CI17" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ17" t="inlineStr">
@@ -8668,12 +8668,12 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM17" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN17" t="inlineStr">
@@ -8693,22 +8693,22 @@
       </c>
       <c r="CQ17" t="inlineStr">
         <is>
-          <t>49.7</t>
+          <t>49.15</t>
         </is>
       </c>
       <c r="CR17" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="CS17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>48.65</t>
         </is>
       </c>
       <c r="CT17" t="inlineStr">
         <is>
-          <t>49.05</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="CU17" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.19</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2486.0</t>
+          <t>1120.0</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8755,7 +8755,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>19.12</t>
+          <t>23.24</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-38.18</t>
+          <t>-38.49</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8795,7 +8795,7 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -8915,17 +8915,17 @@
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>6.35</t>
+          <t>2.86</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>-3.23</t>
+          <t>-2.55</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
@@ -8936,66 +8936,66 @@
       <c r="AP18" t="inlineStr"/>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>41.18</t>
+          <t>36.36</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>23.95</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="AU18" t="n">
-        <v>-0.02</v>
+        <v>-0.85</v>
       </c>
       <c r="AV18" t="n">
-        <v>-6.34</v>
+        <v>-5.92</v>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>7.06</t>
+          <t>6.55</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>49.51000000000001</t>
+          <t>49.47</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>52.86</v>
+        <v>52.58</v>
       </c>
       <c r="BA18" t="n">
-        <v>52.54</v>
+        <v>52.46</v>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>49.08</t>
+          <t>49.23</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-87.87</t>
+          <t>-64.29</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>-1.24</v>
+        <v>-1.3</v>
       </c>
       <c r="BE18" t="n">
-        <v>-0.66</v>
+        <v>-0.79</v>
       </c>
       <c r="BF18" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>-117.42</t>
+          <t>-120.76</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -9014,43 +9014,43 @@
       </c>
       <c r="BI18" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ18" t="inlineStr">
         <is>
-          <t>124201.0</t>
+          <t>55487.0</t>
         </is>
       </c>
       <c r="BK18" t="n">
-        <v>76793</v>
+        <v>73479.2</v>
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>124218.1</t>
+          <t>119450.5</t>
         </is>
       </c>
       <c r="BM18" t="n">
-        <v>213523.76</v>
+        <v>212397.56</v>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>-47425</t>
+          <t>-45971</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>-18966.10215578226</t>
+          <t>-20054.0156916459</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>-24761.63263812255</t>
+          <t>-26037.54013889589</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>124201.0</t>
+          <t>55487.0</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>28.07</t>
+          <t>26.91</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -9115,7 +9115,7 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -9125,12 +9125,12 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -9140,7 +9140,7 @@
       </c>
       <c r="CI18" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ18" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM18" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN18" t="inlineStr">
@@ -9180,22 +9180,22 @@
       </c>
       <c r="CQ18" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>49.7</t>
         </is>
       </c>
       <c r="CR18" t="inlineStr">
         <is>
-          <t>51.3</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="CS18" t="inlineStr">
         <is>
-          <t>49.3</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CT18" t="inlineStr">
         <is>
-          <t>49.5</t>
+          <t>49.05</t>
         </is>
       </c>
       <c r="CU18" t="inlineStr">
@@ -9227,12 +9227,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-1.19</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1713.0</t>
+          <t>2486.0</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -9242,7 +9242,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9252,17 +9252,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>18.14</t>
+          <t>22.54</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-56.32</t>
+          <t>-38.18</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -9282,7 +9282,7 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-01-08 00:00:00</t>
+          <t>2026-01-09 00:00:00</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -9352,7 +9352,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -9402,17 +9402,17 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>6.35</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-3.23</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
@@ -9423,66 +9423,66 @@
       <c r="AP19" t="inlineStr"/>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>47</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>10905</t>
+          <t>5322</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>41.18</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>23.95</t>
         </is>
       </c>
       <c r="AU19" t="n">
-        <v>1.56</v>
+        <v>-0.02</v>
       </c>
       <c r="AV19" t="n">
-        <v>-7.14</v>
+        <v>-6.34</v>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.06</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>49.33</t>
+          <t>49.51000000000001</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>53.12</v>
+        <v>52.86</v>
       </c>
       <c r="BA19" t="n">
-        <v>52.62</v>
+        <v>52.54</v>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>48.94</t>
+          <t>49.08</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-133.25</t>
+          <t>-87.87</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>-1.2</v>
+        <v>-1.24</v>
       </c>
       <c r="BE19" t="n">
-        <v>-0.52</v>
+        <v>-0.66</v>
       </c>
       <c r="BF19" t="inlineStr">
         <is>
@@ -9491,7 +9491,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>-113.60</t>
+          <t>-117.42</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -9501,43 +9501,43 @@
       </c>
       <c r="BI19" t="inlineStr">
         <is>
-          <t>121248.0614754098</t>
+          <t>122006.1165644172</t>
         </is>
       </c>
       <c r="BJ19" t="inlineStr">
         <is>
-          <t>86372.0</t>
+          <t>124201.0</t>
         </is>
       </c>
       <c r="BK19" t="n">
-        <v>60571.2</v>
+        <v>76793</v>
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>138654.5</t>
+          <t>124218.1</t>
         </is>
       </c>
       <c r="BM19" t="n">
-        <v>215595.82</v>
+        <v>213523.76</v>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>-78083</t>
+          <t>-47425</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>-17912.3693408113</t>
+          <t>-18966.10215578226</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>-29416.77789994201</t>
+          <t>-24761.63263812255</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>86372.0</t>
+          <t>124201.0</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>29.62</t>
+          <t>28.07</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -9582,7 +9582,7 @@
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -9612,12 +9612,12 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -9627,7 +9627,7 @@
       </c>
       <c r="CI19" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="CJ19" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>50.79</t>
+          <t>51.03</t>
         </is>
       </c>
       <c r="CM19" t="inlineStr">
         <is>
-          <t>7685</t>
+          <t>8024</t>
         </is>
       </c>
       <c r="CN19" t="inlineStr">
@@ -9667,22 +9667,22 @@
       </c>
       <c r="CQ19" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="CR19" t="inlineStr">
         <is>
-          <t>51.1</t>
+          <t>51.3</t>
         </is>
       </c>
       <c r="CS19" t="inlineStr">
         <is>
-          <t>49.6</t>
+          <t>49.3</t>
         </is>
       </c>
       <c r="CT19" t="inlineStr">
         <is>
-          <t>50.1</t>
+          <t>49.5</t>
         </is>
       </c>
       <c r="CU19" t="inlineStr">
@@ -9714,12 +9714,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-2.41</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4753.977</t>
+          <t>6823.126</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -9729,7 +9729,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>530.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-23.18</t>
+          <t>-5.04</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-21.42</t>
+          <t>-23.30</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -9839,7 +9839,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -9889,17 +9889,17 @@
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>21.97</t>
+          <t>31.54</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-2.26</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
@@ -9910,66 +9910,66 @@
       <c r="AP20" t="inlineStr"/>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>537</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>21.67</t>
+          <t>8.33</t>
         </is>
       </c>
       <c r="AU20" t="n">
-        <v>-0.59</v>
+        <v>-2.32</v>
       </c>
       <c r="AV20" t="n">
-        <v>-2.7</v>
+        <v>-2.77</v>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>-7.13</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>-4.83</t>
+          <t>-5.13</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>546.2</t>
+          <t>542.6</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>561.35</v>
+        <v>558.05</v>
       </c>
       <c r="BA20" t="n">
-        <v>604.42</v>
+        <v>600.84</v>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>635.09</t>
+          <t>633.36</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>5.87</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>-17.66</v>
+        <v>-18.02</v>
       </c>
       <c r="BE20" t="n">
-        <v>-18.76</v>
+        <v>-18.61</v>
       </c>
       <c r="BF20" t="inlineStr">
         <is>
@@ -9978,7 +9978,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>-183.54</t>
+          <t>-182.88</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -9988,43 +9988,43 @@
       </c>
       <c r="BI20" t="inlineStr">
         <is>
-          <t>3785820750.891393</t>
+          <t>3789276272.539877</t>
         </is>
       </c>
       <c r="BJ20" t="inlineStr">
         <is>
-          <t>2576882341.0</t>
+          <t>3650380558.0</t>
         </is>
       </c>
       <c r="BK20" t="n">
-        <v>2399229287.8</v>
+        <v>2831479875</v>
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>3123362656.5</t>
+          <t>2981642219.9</t>
         </is>
       </c>
       <c r="BM20" t="n">
-        <v>2807247067.2</v>
+        <v>2853231372.9</v>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>-724133368</t>
+          <t>-150162344</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>47815936.12187205</t>
+          <t>21340278.58410675</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>-204132547.4695311</t>
+          <t>-124275837.8736024</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>2576882341.0</t>
+          <t>3650380558.0</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
@@ -10044,7 +10044,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-21.25</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -10089,22 +10089,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="CI20" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="CJ20" t="inlineStr">
@@ -10129,12 +10129,12 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM20" t="inlineStr">
         <is>
-          <t>403319</t>
+          <t>393663</t>
         </is>
       </c>
       <c r="CN20" t="inlineStr">
@@ -10154,22 +10154,22 @@
       </c>
       <c r="CQ20" t="inlineStr">
         <is>
-          <t>539.0</t>
+          <t>540.0</t>
         </is>
       </c>
       <c r="CR20" t="inlineStr">
         <is>
-          <t>547.0</t>
+          <t>542.0</t>
         </is>
       </c>
       <c r="CS20" t="inlineStr">
         <is>
-          <t>535.0</t>
+          <t>530.0</t>
         </is>
       </c>
       <c r="CT20" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>530.0</t>
         </is>
       </c>
       <c r="CU20" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4610.828</t>
+          <t>4753.977</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>539.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10226,17 +10226,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-32.47</t>
+          <t>-23.18</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -10301,7 +10301,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-22.00</t>
+          <t>-21.42</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -10376,17 +10376,17 @@
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>21.31</t>
+          <t>21.97</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
@@ -10397,66 +10397,66 @@
       <c r="AP21" t="inlineStr"/>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>537</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>46.67</t>
+          <t>21.67</t>
         </is>
       </c>
       <c r="AU21" t="n">
-        <v>-1.21</v>
+        <v>-0.59</v>
       </c>
       <c r="AV21" t="n">
-        <v>-3.31</v>
+        <v>-2.7</v>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>-7.13</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-4.83</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>545.6</t>
+          <t>546.2</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>564.3</v>
+        <v>561.35</v>
       </c>
       <c r="BA21" t="n">
-        <v>607.84</v>
+        <v>604.42</v>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>636.56</t>
+          <t>635.09</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>-18.27</v>
+        <v>-17.66</v>
       </c>
       <c r="BE21" t="n">
-        <v>-19.04</v>
+        <v>-18.76</v>
       </c>
       <c r="BF21" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>-184.77</t>
+          <t>-183.54</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -10475,43 +10475,43 @@
       </c>
       <c r="BI21" t="inlineStr">
         <is>
-          <t>3785820750.891393</t>
+          <t>3789276272.539877</t>
         </is>
       </c>
       <c r="BJ21" t="inlineStr">
         <is>
-          <t>2493007382.0</t>
+          <t>2576882341.0</t>
         </is>
       </c>
       <c r="BK21" t="n">
-        <v>2277544053.4</v>
+        <v>2399229287.8</v>
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>3372583140.2</t>
+          <t>3123362656.5</t>
         </is>
       </c>
       <c r="BM21" t="n">
-        <v>2805787563.28</v>
+        <v>2807247067.2</v>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>-1095039086</t>
+          <t>-724133368</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>93624751.32030897</t>
+          <t>47815936.12187205</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>-195905446.9469471</t>
+          <t>-204132547.4695311</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>2493007382.0</t>
+          <t>2576882341.0</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -10531,7 +10531,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>-19.91</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -10576,22 +10576,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -10601,7 +10601,7 @@
       </c>
       <c r="CI21" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="CJ21" t="inlineStr">
@@ -10616,12 +10616,12 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM21" t="inlineStr">
         <is>
-          <t>403319</t>
+          <t>393663</t>
         </is>
       </c>
       <c r="CN21" t="inlineStr">
@@ -10641,22 +10641,22 @@
       </c>
       <c r="CQ21" t="inlineStr">
         <is>
-          <t>545.0</t>
+          <t>539.0</t>
         </is>
       </c>
       <c r="CR21" t="inlineStr">
         <is>
-          <t>548.0</t>
+          <t>547.0</t>
         </is>
       </c>
       <c r="CS21" t="inlineStr">
         <is>
-          <t>538.0</t>
+          <t>535.0</t>
         </is>
       </c>
       <c r="CT21" t="inlineStr">
         <is>
-          <t>539.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="CU21" t="inlineStr">
@@ -10688,12 +10688,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.62</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5388.987</t>
+          <t>4610.828</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -10703,7 +10703,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>546.0</t>
+          <t>539.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10713,17 +10713,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-43.50</t>
+          <t>-32.47</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-20.98</t>
+          <t>-22.00</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -10863,17 +10863,17 @@
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>21.31</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>-2.20</t>
+          <t>-1.48</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
@@ -10884,66 +10884,66 @@
       <c r="AP22" t="inlineStr"/>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>537</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>65.71</t>
+          <t>46.67</t>
         </is>
       </c>
       <c r="AU22" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.21</v>
       </c>
       <c r="AV22" t="n">
-        <v>-3.77</v>
+        <v>-3.31</v>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>-7.07</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>-4.21</t>
+          <t>-4.51</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>546.4</t>
+          <t>545.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>567.8</v>
+        <v>564.3</v>
       </c>
       <c r="BA22" t="n">
-        <v>611.02</v>
+        <v>607.84</v>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>637.89</t>
+          <t>636.56</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>4.48</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>-18.37</v>
+        <v>-18.27</v>
       </c>
       <c r="BE22" t="n">
-        <v>-19.23</v>
+        <v>-19.04</v>
       </c>
       <c r="BF22" t="inlineStr">
         <is>
@@ -10952,7 +10952,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>-185.63</t>
+          <t>-184.77</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -10962,43 +10962,43 @@
       </c>
       <c r="BI22" t="inlineStr">
         <is>
-          <t>3785820750.891393</t>
+          <t>3789276272.539877</t>
         </is>
       </c>
       <c r="BJ22" t="inlineStr">
         <is>
-          <t>2971429132.0</t>
+          <t>2493007382.0</t>
         </is>
       </c>
       <c r="BK22" t="n">
-        <v>2179064559.4</v>
+        <v>2277544053.4</v>
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>3856732354.3</t>
+          <t>3372583140.2</t>
         </is>
       </c>
       <c r="BM22" t="n">
-        <v>2779834991.66</v>
+        <v>2805787563.28</v>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>-1677667794</t>
+          <t>-1095039086</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>146266605.5507192</t>
+          <t>93624751.32030897</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>-168169220.3451495</t>
+          <t>-195905446.9469471</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>2971429132.0</t>
+          <t>2493007382.0</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>-18.87</t>
+          <t>-19.91</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -11063,7 +11063,7 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
@@ -11073,12 +11073,12 @@
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="CI22" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="CJ22" t="inlineStr">
@@ -11103,12 +11103,12 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM22" t="inlineStr">
         <is>
-          <t>403319</t>
+          <t>393663</t>
         </is>
       </c>
       <c r="CN22" t="inlineStr">
@@ -11128,22 +11128,22 @@
       </c>
       <c r="CQ22" t="inlineStr">
         <is>
-          <t>555.0</t>
+          <t>545.0</t>
         </is>
       </c>
       <c r="CR22" t="inlineStr">
         <is>
-          <t>558.0</t>
+          <t>548.0</t>
         </is>
       </c>
       <c r="CS22" t="inlineStr">
         <is>
-          <t>546.0</t>
+          <t>538.0</t>
         </is>
       </c>
       <c r="CT22" t="inlineStr">
         <is>
-          <t>546.0</t>
+          <t>539.0</t>
         </is>
       </c>
       <c r="CU22" t="inlineStr">
@@ -11175,12 +11175,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4418.986</t>
+          <t>5388.987</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11190,7 +11190,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>555.0</t>
+          <t>546.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11200,17 +11200,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-40.78</t>
+          <t>-43.50</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>-19.68</t>
+          <t>-20.98</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -11300,7 +11300,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
@@ -11350,17 +11350,17 @@
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>20.42</t>
+          <t>24.91</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-2.20</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
@@ -11371,66 +11371,66 @@
       <c r="AP23" t="inlineStr"/>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>537</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>52.38</t>
+          <t>65.71</t>
         </is>
       </c>
       <c r="AU23" t="n">
-        <v>1.39</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="AV23" t="n">
-        <v>-4.11</v>
+        <v>-3.77</v>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-7.07</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>-3.92</t>
+          <t>-4.21</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>547.4</t>
+          <t>546.4</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>570.85</v>
+        <v>567.8</v>
       </c>
       <c r="BA23" t="n">
-        <v>614.08</v>
+        <v>611.02</v>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>639.12</t>
+          <t>637.89</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>4.48</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>-18.94</v>
+        <v>-18.37</v>
       </c>
       <c r="BE23" t="n">
-        <v>-19.44</v>
+        <v>-19.23</v>
       </c>
       <c r="BF23" t="inlineStr">
         <is>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>-186.59</t>
+          <t>-185.63</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -11449,43 +11449,43 @@
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>3785820750.891393</t>
+          <t>3789276272.539877</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>2465699962.0</t>
+          <t>2971429132.0</t>
         </is>
       </c>
       <c r="BK23" t="n">
-        <v>2526011013.6</v>
+        <v>2179064559.4</v>
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>4265162260.7</t>
+          <t>3856732354.3</t>
         </is>
       </c>
       <c r="BM23" t="n">
-        <v>2736629025.76</v>
+        <v>2779834991.66</v>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>-1739151247</t>
+          <t>-1677667794</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>203436755.7136044</t>
+          <t>146266605.5507192</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>-173799469.1159687</t>
+          <t>-168169220.3451495</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>2465699962.0</t>
+          <t>2971429132.0</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -11505,7 +11505,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>-17.53</t>
+          <t>-18.87</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -11550,7 +11550,7 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
@@ -11560,12 +11560,12 @@
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">
@@ -11575,7 +11575,7 @@
       </c>
       <c r="CI23" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="CJ23" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM23" t="inlineStr">
         <is>
-          <t>403319</t>
+          <t>393663</t>
         </is>
       </c>
       <c r="CN23" t="inlineStr">
@@ -11615,22 +11615,22 @@
       </c>
       <c r="CQ23" t="inlineStr">
         <is>
-          <t>554.0</t>
+          <t>555.0</t>
         </is>
       </c>
       <c r="CR23" t="inlineStr">
         <is>
-          <t>563.0</t>
+          <t>558.0</t>
         </is>
       </c>
       <c r="CS23" t="inlineStr">
         <is>
-          <t>552.0</t>
+          <t>546.0</t>
         </is>
       </c>
       <c r="CT23" t="inlineStr">
         <is>
-          <t>555.0</t>
+          <t>546.0</t>
         </is>
       </c>
       <c r="CU23" t="inlineStr">
@@ -11652,7 +11652,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -11662,12 +11662,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2714.103</t>
+          <t>4418.986</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11677,7 +11677,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>548.0</t>
+          <t>555.0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11687,17 +11687,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-0.92</t>
+          <t>-4.72</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-31.76</t>
+          <t>-40.78</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -11762,7 +11762,7 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>-20.69</t>
+          <t>-19.68</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -11837,17 +11837,17 @@
       </c>
       <c r="AL24" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>20.42</t>
         </is>
       </c>
       <c r="AN24" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
@@ -11858,66 +11858,66 @@
       <c r="AP24" t="inlineStr"/>
       <c r="AQ24" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>537</t>
         </is>
       </c>
       <c r="AR24" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr">
         <is>
-          <t>19.05</t>
+          <t>52.38</t>
         </is>
       </c>
       <c r="AU24" t="n">
-        <v>0.51</v>
+        <v>1.39</v>
       </c>
       <c r="AV24" t="n">
-        <v>-5</v>
+        <v>-4.11</v>
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>-6.96</t>
+          <t>-7.04</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>-3.64</t>
+          <t>-3.92</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
-          <t>545.2</t>
+          <t>547.4</t>
         </is>
       </c>
       <c r="AZ24" t="n">
-        <v>573.9</v>
+        <v>570.85</v>
       </c>
       <c r="BA24" t="n">
-        <v>616.8</v>
+        <v>614.08</v>
       </c>
       <c r="BB24" t="inlineStr">
         <is>
-          <t>640.12</t>
+          <t>639.12</t>
         </is>
       </c>
       <c r="BC24" t="inlineStr">
         <is>
-          <t>-3.82</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BD24" t="n">
-        <v>-20.32</v>
+        <v>-18.94</v>
       </c>
       <c r="BE24" t="n">
-        <v>-19.57</v>
+        <v>-19.44</v>
       </c>
       <c r="BF24" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="BG24" t="inlineStr">
         <is>
-          <t>-187.15</t>
+          <t>-186.59</t>
         </is>
       </c>
       <c r="BH24" t="inlineStr">
@@ -11936,43 +11936,43 @@
       </c>
       <c r="BI24" t="inlineStr">
         <is>
-          <t>3785820750.891393</t>
+          <t>3789276272.539877</t>
         </is>
       </c>
       <c r="BJ24" t="inlineStr">
         <is>
-          <t>1489127622.0</t>
+          <t>2465699962.0</t>
         </is>
       </c>
       <c r="BK24" t="n">
-        <v>3131804564.8</v>
+        <v>2526011013.6</v>
       </c>
       <c r="BL24" t="inlineStr">
         <is>
-          <t>4589353287.0</t>
+          <t>4265162260.7</t>
         </is>
       </c>
       <c r="BM24" t="n">
-        <v>2708576977.62</v>
+        <v>2736629025.76</v>
       </c>
       <c r="BN24" t="inlineStr">
         <is>
-          <t>-1457548722</t>
+          <t>-1739151247</t>
         </is>
       </c>
       <c r="BO24" t="inlineStr">
         <is>
-          <t>272025160.2280722</t>
+          <t>203436755.7136044</t>
         </is>
       </c>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>-121450289.5344262</t>
+          <t>-173799469.1159687</t>
         </is>
       </c>
       <c r="BQ24" t="inlineStr">
         <is>
-          <t>1489127622.0</t>
+          <t>2465699962.0</t>
         </is>
       </c>
       <c r="BR24" t="inlineStr">
@@ -11992,7 +11992,7 @@
       </c>
       <c r="BU24" t="inlineStr">
         <is>
-          <t>-18.57</t>
+          <t>-17.53</t>
         </is>
       </c>
       <c r="BV24" t="inlineStr">
@@ -12037,22 +12037,22 @@
       </c>
       <c r="CD24" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE24" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CF24" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="CG24" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="CH24" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="CI24" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="CJ24" t="inlineStr">
@@ -12077,12 +12077,12 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM24" t="inlineStr">
         <is>
-          <t>403319</t>
+          <t>393663</t>
         </is>
       </c>
       <c r="CN24" t="inlineStr">
@@ -12102,22 +12102,22 @@
       </c>
       <c r="CQ24" t="inlineStr">
         <is>
-          <t>542.0</t>
+          <t>554.0</t>
         </is>
       </c>
       <c r="CR24" t="inlineStr">
         <is>
-          <t>553.0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="CS24" t="inlineStr">
         <is>
-          <t>541.0</t>
+          <t>552.0</t>
         </is>
       </c>
       <c r="CT24" t="inlineStr">
         <is>
-          <t>548.0</t>
+          <t>555.0</t>
         </is>
       </c>
       <c r="CU24" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>3645.565</t>
+          <t>2714.103</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>540.0</t>
+          <t>548.0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -12174,17 +12174,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-3.4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-24.04</t>
+          <t>-31.76</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -12249,7 +12249,7 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>-21.85</t>
+          <t>-20.69</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
@@ -12324,17 +12324,17 @@
       </c>
       <c r="AL25" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>16.85</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AN25" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
@@ -12345,66 +12345,66 @@
       <c r="AP25" t="inlineStr"/>
       <c r="AQ25" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>537</t>
         </is>
       </c>
       <c r="AR25" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>57.14</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr">
         <is>
-          <t>5.56</t>
+          <t>19.05</t>
         </is>
       </c>
       <c r="AU25" t="n">
-        <v>-0.88</v>
+        <v>0.51</v>
       </c>
       <c r="AV25" t="n">
-        <v>-5.56</v>
+        <v>-5</v>
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>-6.89</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>-3.36</t>
+          <t>-3.64</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>544.8</t>
+          <t>545.2</t>
         </is>
       </c>
       <c r="AZ25" t="n">
-        <v>576.85</v>
+        <v>573.9</v>
       </c>
       <c r="BA25" t="n">
-        <v>619.5599999999999</v>
+        <v>616.8</v>
       </c>
       <c r="BB25" t="inlineStr">
         <is>
-          <t>641.09</t>
+          <t>640.12</t>
         </is>
       </c>
       <c r="BC25" t="inlineStr">
         <is>
-          <t>-8.67</t>
+          <t>-3.82</t>
         </is>
       </c>
       <c r="BD25" t="n">
-        <v>-21.06</v>
+        <v>-20.32</v>
       </c>
       <c r="BE25" t="n">
-        <v>-19.38</v>
+        <v>-19.57</v>
       </c>
       <c r="BF25" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
       </c>
       <c r="BG25" t="inlineStr">
         <is>
-          <t>-186.31</t>
+          <t>-187.15</t>
         </is>
       </c>
       <c r="BH25" t="inlineStr">
@@ -12423,43 +12423,43 @@
       </c>
       <c r="BI25" t="inlineStr">
         <is>
-          <t>3785820750.891393</t>
+          <t>3789276272.539877</t>
         </is>
       </c>
       <c r="BJ25" t="inlineStr">
         <is>
-          <t>1968456169.0</t>
+          <t>1489127622.0</t>
         </is>
       </c>
       <c r="BK25" t="n">
-        <v>3847496025.2</v>
+        <v>3131804564.8</v>
       </c>
       <c r="BL25" t="inlineStr">
         <is>
-          <t>5065100698.0</t>
+          <t>4589353287.0</t>
         </is>
       </c>
       <c r="BM25" t="n">
-        <v>2710153011.62</v>
+        <v>2708576977.62</v>
       </c>
       <c r="BN25" t="inlineStr">
         <is>
-          <t>-1217604672</t>
+          <t>-1457548722</t>
         </is>
       </c>
       <c r="BO25" t="inlineStr">
         <is>
-          <t>343566151.093981</t>
+          <t>272025160.2280722</t>
         </is>
       </c>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>62304513.77972078</t>
+          <t>-121450289.5344262</t>
         </is>
       </c>
       <c r="BQ25" t="inlineStr">
         <is>
-          <t>1968456169.0</t>
+          <t>1489127622.0</t>
         </is>
       </c>
       <c r="BR25" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="BU25" t="inlineStr">
         <is>
-          <t>-19.76</t>
+          <t>-18.57</t>
         </is>
       </c>
       <c r="BV25" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="CD25" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE25" t="inlineStr">
@@ -12534,12 +12534,12 @@
       </c>
       <c r="CF25" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="CG25" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="CH25" t="inlineStr">
@@ -12549,7 +12549,7 @@
       </c>
       <c r="CI25" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="CJ25" t="inlineStr">
@@ -12564,12 +12564,12 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM25" t="inlineStr">
         <is>
-          <t>403319</t>
+          <t>393663</t>
         </is>
       </c>
       <c r="CN25" t="inlineStr">
@@ -12589,22 +12589,22 @@
       </c>
       <c r="CQ25" t="inlineStr">
         <is>
-          <t>545.0</t>
+          <t>542.0</t>
         </is>
       </c>
       <c r="CR25" t="inlineStr">
         <is>
+          <t>553.0</t>
+        </is>
+      </c>
+      <c r="CS25" t="inlineStr">
+        <is>
+          <t>541.0</t>
+        </is>
+      </c>
+      <c r="CT25" t="inlineStr">
+        <is>
           <t>548.0</t>
-        </is>
-      </c>
-      <c r="CS25" t="inlineStr">
-        <is>
-          <t>535.0</t>
-        </is>
-      </c>
-      <c r="CT25" t="inlineStr">
-        <is>
-          <t>540.0</t>
         </is>
       </c>
       <c r="CU25" t="inlineStr">
@@ -12636,12 +12636,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3643.793</t>
+          <t>3645.565</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -12651,7 +12651,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>540.0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -12661,17 +12661,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-10.97</t>
+          <t>-24.04</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>-21.42</t>
+          <t>-21.85</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
@@ -12811,17 +12811,17 @@
       </c>
       <c r="AL26" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>16.84</t>
+          <t>16.85</t>
         </is>
       </c>
       <c r="AN26" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
@@ -12832,12 +12832,12 @@
       <c r="AP26" t="inlineStr"/>
       <c r="AQ26" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>537</t>
         </is>
       </c>
       <c r="AR26" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr">
@@ -12851,47 +12851,47 @@
         </is>
       </c>
       <c r="AU26" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.88</v>
       </c>
       <c r="AV26" t="n">
-        <v>-5.72</v>
+        <v>-5.56</v>
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>-6.82</t>
+          <t>-6.89</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>-3.05</t>
+          <t>-3.36</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>546.8</t>
+          <t>544.8</t>
         </is>
       </c>
       <c r="AZ26" t="n">
-        <v>580</v>
+        <v>576.85</v>
       </c>
       <c r="BA26" t="n">
-        <v>622.46</v>
+        <v>619.5599999999999</v>
       </c>
       <c r="BB26" t="inlineStr">
         <is>
-          <t>642.08</t>
+          <t>641.09</t>
         </is>
       </c>
       <c r="BC26" t="inlineStr">
         <is>
-          <t>-10.19</t>
+          <t>-8.67</t>
         </is>
       </c>
       <c r="BD26" t="n">
-        <v>-20.89</v>
+        <v>-21.06</v>
       </c>
       <c r="BE26" t="n">
-        <v>-18.96</v>
+        <v>-19.38</v>
       </c>
       <c r="BF26" t="inlineStr">
         <is>
@@ -12900,7 +12900,7 @@
       </c>
       <c r="BG26" t="inlineStr">
         <is>
-          <t>-184.44</t>
+          <t>-186.31</t>
         </is>
       </c>
       <c r="BH26" t="inlineStr">
@@ -12910,43 +12910,43 @@
       </c>
       <c r="BI26" t="inlineStr">
         <is>
-          <t>3785820750.891393</t>
+          <t>3789276272.539877</t>
         </is>
       </c>
       <c r="BJ26" t="inlineStr">
         <is>
-          <t>2000609912.0</t>
+          <t>1968456169.0</t>
         </is>
       </c>
       <c r="BK26" t="n">
-        <v>4467622227</v>
+        <v>3847496025.2</v>
       </c>
       <c r="BL26" t="inlineStr">
         <is>
-          <t>5018129405.0</t>
+          <t>5065100698.0</t>
         </is>
       </c>
       <c r="BM26" t="n">
-        <v>2695477171.12</v>
+        <v>2710153011.62</v>
       </c>
       <c r="BN26" t="inlineStr">
         <is>
-          <t>-550507178</t>
+          <t>-1217604672</t>
         </is>
       </c>
       <c r="BO26" t="inlineStr">
         <is>
-          <t>394704630.6056647</t>
+          <t>343566151.093981</t>
         </is>
       </c>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>271229584.4149408</t>
+          <t>62304513.77972078</t>
         </is>
       </c>
       <c r="BQ26" t="inlineStr">
         <is>
-          <t>2000609912.0</t>
+          <t>1968456169.0</t>
         </is>
       </c>
       <c r="BR26" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="BU26" t="inlineStr">
         <is>
-          <t>-19.32</t>
+          <t>-19.76</t>
         </is>
       </c>
       <c r="BV26" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="CD26" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE26" t="inlineStr">
@@ -13021,12 +13021,12 @@
       </c>
       <c r="CF26" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="CG26" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="CH26" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="CI26" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="CJ26" t="inlineStr">
@@ -13051,12 +13051,12 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM26" t="inlineStr">
         <is>
-          <t>403319</t>
+          <t>393663</t>
         </is>
       </c>
       <c r="CN26" t="inlineStr">
@@ -13076,22 +13076,22 @@
       </c>
       <c r="CQ26" t="inlineStr">
         <is>
-          <t>554.0</t>
+          <t>545.0</t>
         </is>
       </c>
       <c r="CR26" t="inlineStr">
         <is>
-          <t>557.0</t>
+          <t>548.0</t>
         </is>
       </c>
       <c r="CS26" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>535.0</t>
         </is>
       </c>
       <c r="CT26" t="inlineStr">
         <is>
-          <t>543.0</t>
+          <t>540.0</t>
         </is>
       </c>
       <c r="CU26" t="inlineStr">
@@ -13123,12 +13123,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>8521.76</t>
+          <t>3643.793</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -13138,7 +13138,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>551.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -13148,17 +13148,17 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-1.47</t>
+          <t>-2.45</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>11.66</t>
+          <t>-10.97</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -13223,7 +13223,7 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>-20.26</t>
+          <t>-21.42</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -13298,17 +13298,17 @@
       </c>
       <c r="AL27" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>39.39</t>
+          <t>16.84</t>
         </is>
       </c>
       <c r="AN27" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
@@ -13319,17 +13319,17 @@
       <c r="AP27" t="inlineStr"/>
       <c r="AQ27" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>537</t>
         </is>
       </c>
       <c r="AR27" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr">
         <is>
-          <t>16.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr">
@@ -13338,47 +13338,47 @@
         </is>
       </c>
       <c r="AU27" t="n">
-        <v>0.51</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="AV27" t="n">
-        <v>-5.95</v>
+        <v>-5.72</v>
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>-6.78</t>
+          <t>-6.82</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-3.05</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>548.2</t>
+          <t>546.8</t>
         </is>
       </c>
       <c r="AZ27" t="n">
-        <v>582.9</v>
+        <v>580</v>
       </c>
       <c r="BA27" t="n">
-        <v>625.3</v>
+        <v>622.46</v>
       </c>
       <c r="BB27" t="inlineStr">
         <is>
-          <t>643.02</t>
+          <t>642.08</t>
         </is>
       </c>
       <c r="BC27" t="inlineStr">
         <is>
-          <t>-11.91</t>
+          <t>-10.19</t>
         </is>
       </c>
       <c r="BD27" t="n">
-        <v>-20.68</v>
+        <v>-20.89</v>
       </c>
       <c r="BE27" t="n">
-        <v>-18.48</v>
+        <v>-18.96</v>
       </c>
       <c r="BF27" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
       </c>
       <c r="BG27" t="inlineStr">
         <is>
-          <t>-182.29</t>
+          <t>-184.44</t>
         </is>
       </c>
       <c r="BH27" t="inlineStr">
@@ -13397,43 +13397,43 @@
       </c>
       <c r="BI27" t="inlineStr">
         <is>
-          <t>3785820750.891393</t>
+          <t>3789276272.539877</t>
         </is>
       </c>
       <c r="BJ27" t="inlineStr">
         <is>
-          <t>4706161403.0</t>
+          <t>2000609912.0</t>
         </is>
       </c>
       <c r="BK27" t="n">
-        <v>5534400149.2</v>
+        <v>4467622227</v>
       </c>
       <c r="BL27" t="inlineStr">
         <is>
-          <t>4956648855.5</t>
+          <t>5018129405.0</t>
         </is>
       </c>
       <c r="BM27" t="n">
-        <v>2681952710.56</v>
+        <v>2695477171.12</v>
       </c>
       <c r="BN27" t="inlineStr">
         <is>
-          <t>577751293</t>
+          <t>-550507178</t>
         </is>
       </c>
       <c r="BO27" t="inlineStr">
         <is>
-          <t>417154639.0039782</t>
+          <t>394704630.6056647</t>
         </is>
       </c>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>556562156.2718658</t>
+          <t>271229584.4149408</t>
         </is>
       </c>
       <c r="BQ27" t="inlineStr">
         <is>
-          <t>4706161403.0</t>
+          <t>2000609912.0</t>
         </is>
       </c>
       <c r="BR27" t="inlineStr">
@@ -13453,7 +13453,7 @@
       </c>
       <c r="BU27" t="inlineStr">
         <is>
-          <t>-18.13</t>
+          <t>-19.32</t>
         </is>
       </c>
       <c r="BV27" t="inlineStr">
@@ -13498,7 +13498,7 @@
       </c>
       <c r="CD27" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE27" t="inlineStr">
@@ -13508,12 +13508,12 @@
       </c>
       <c r="CF27" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CG27" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="CH27" t="inlineStr">
@@ -13523,7 +13523,7 @@
       </c>
       <c r="CI27" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="CJ27" t="inlineStr">
@@ -13538,12 +13538,12 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM27" t="inlineStr">
         <is>
-          <t>403319</t>
+          <t>393663</t>
         </is>
       </c>
       <c r="CN27" t="inlineStr">
@@ -13563,22 +13563,22 @@
       </c>
       <c r="CQ27" t="inlineStr">
         <is>
-          <t>548.0</t>
+          <t>554.0</t>
         </is>
       </c>
       <c r="CR27" t="inlineStr">
         <is>
-          <t>556.0</t>
+          <t>557.0</t>
         </is>
       </c>
       <c r="CS27" t="inlineStr">
         <is>
-          <t>545.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="CT27" t="inlineStr">
         <is>
-          <t>551.0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="CU27" t="inlineStr">
@@ -13610,12 +13610,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10056.098</t>
+          <t>8521.76</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>544.0</t>
+          <t>551.0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -13635,17 +13635,17 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-3.96</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>29.22</t>
+          <t>11.66</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>-21.27</t>
+          <t>-20.26</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -13735,7 +13735,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -13785,17 +13785,17 @@
       </c>
       <c r="AL28" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AM28" t="inlineStr">
         <is>
-          <t>46.48</t>
+          <t>39.39</t>
         </is>
       </c>
       <c r="AN28" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="AO28" t="inlineStr">
@@ -13806,66 +13806,66 @@
       <c r="AP28" t="inlineStr"/>
       <c r="AQ28" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>537</t>
         </is>
       </c>
       <c r="AR28" t="inlineStr">
         <is>
-          <t>4754</t>
+          <t>6823</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>16.67</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.56</t>
         </is>
       </c>
       <c r="AU28" t="n">
-        <v>-0.87</v>
+        <v>0.51</v>
       </c>
       <c r="AV28" t="n">
-        <v>-6.33</v>
+        <v>-5.95</v>
       </c>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>-6.7</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
-          <t>548.8</t>
+          <t>548.2</t>
         </is>
       </c>
       <c r="AZ28" t="n">
-        <v>585.9</v>
+        <v>582.9</v>
       </c>
       <c r="BA28" t="n">
-        <v>627.96</v>
+        <v>625.3</v>
       </c>
       <c r="BB28" t="inlineStr">
         <is>
-          <t>644.04</t>
+          <t>643.02</t>
         </is>
       </c>
       <c r="BC28" t="inlineStr">
         <is>
-          <t>-16.70</t>
+          <t>-11.91</t>
         </is>
       </c>
       <c r="BD28" t="n">
-        <v>-20.92</v>
+        <v>-20.68</v>
       </c>
       <c r="BE28" t="n">
-        <v>-17.93</v>
+        <v>-18.48</v>
       </c>
       <c r="BF28" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
       </c>
       <c r="BG28" t="inlineStr">
         <is>
-          <t>-179.84</t>
+          <t>-182.29</t>
         </is>
       </c>
       <c r="BH28" t="inlineStr">
@@ -13884,43 +13884,43 @@
       </c>
       <c r="BI28" t="inlineStr">
         <is>
-          <t>3785820750.891393</t>
+          <t>3789276272.539877</t>
         </is>
       </c>
       <c r="BJ28" t="inlineStr">
         <is>
-          <t>5494667718.0</t>
+          <t>4706161403.0</t>
         </is>
       </c>
       <c r="BK28" t="n">
-        <v>6004313507.8</v>
+        <v>5534400149.2</v>
       </c>
       <c r="BL28" t="inlineStr">
         <is>
-          <t>4646636108.5</t>
+          <t>4956648855.5</t>
         </is>
       </c>
       <c r="BM28" t="n">
-        <v>2640209392.16</v>
+        <v>2681952710.56</v>
       </c>
       <c r="BN28" t="inlineStr">
         <is>
-          <t>1357677399</t>
+          <t>577751293</t>
         </is>
       </c>
       <c r="BO28" t="inlineStr">
         <is>
-          <t>391807817.6825441</t>
+          <t>417154639.0039782</t>
         </is>
       </c>
       <c r="BP28" t="inlineStr">
         <is>
-          <t>654422379.3077617</t>
+          <t>556562156.2718658</t>
         </is>
       </c>
       <c r="BQ28" t="inlineStr">
         <is>
-          <t>5494667718.0</t>
+          <t>4706161403.0</t>
         </is>
       </c>
       <c r="BR28" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="BU28" t="inlineStr">
         <is>
-          <t>-19.17</t>
+          <t>-18.13</t>
         </is>
       </c>
       <c r="BV28" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="CD28" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;可能出現反轉訊號&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;3&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CE28" t="inlineStr">
@@ -13995,12 +13995,12 @@
       </c>
       <c r="CF28" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="CG28" t="inlineStr">
         <is>
-          <t>6.26</t>
+          <t>6.42</t>
         </is>
       </c>
       <c r="CH28" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="CI28" t="inlineStr">
         <is>
-          <t>11.59</t>
+          <t>11.32</t>
         </is>
       </c>
       <c r="CJ28" t="inlineStr">
@@ -14025,12 +14025,12 @@
       </c>
       <c r="CL28" t="inlineStr">
         <is>
-          <t>27.65</t>
+          <t>27.18</t>
         </is>
       </c>
       <c r="CM28" t="inlineStr">
         <is>
-          <t>403319</t>
+          <t>393663</t>
         </is>
       </c>
       <c r="CN28" t="inlineStr">
@@ -14050,22 +14050,22 @@
       </c>
       <c r="CQ28" t="inlineStr">
         <is>
-          <t>547.0</t>
+          <t>548.0</t>
         </is>
       </c>
       <c r="CR28" t="inlineStr">
         <is>
+          <t>556.0</t>
+        </is>
+      </c>
+      <c r="CS28" t="inlineStr">
+        <is>
+          <t>545.0</t>
+        </is>
+      </c>
+      <c r="CT28" t="inlineStr">
+        <is>
           <t>551.0</t>
-        </is>
-      </c>
-      <c r="CS28" t="inlineStr">
-        <is>
-          <t>540.0</t>
-        </is>
-      </c>
-      <c r="CT28" t="inlineStr">
-        <is>
-          <t>544.0</t>
         </is>
       </c>
       <c r="CU28" t="inlineStr">

--- a/Result/checksun_type/BIOS(嵌入式軟體).xlsx
+++ b/Result/checksun_type/BIOS(嵌入式軟體).xlsx
@@ -973,12 +973,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>275.0</t>
+          <t>382.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1003,12 +1003,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.12385807023159169</t>
+          <t>-0.025427551899598517</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-27.27</t>
+          <t>-23.79</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-48.71</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1143,22 +1143,22 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-09-18 00:00:00</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>3.58</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-1.33</t>
+          <t>5.09</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
@@ -1169,85 +1169,85 @@
       <c r="AP2" t="inlineStr"/>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>38.3</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.77</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>-3.98</v>
+        <v>2.13</v>
       </c>
       <c r="AV2" t="n">
-        <v>-4.44</v>
+        <v>-5.48</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>-2.84</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-1.61</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>195.8</t>
+          <t>192.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>200.1</t>
+          <t>198.75</t>
         </is>
       </c>
       <c r="BA2" t="n">
-        <v>204.9</v>
+        <v>204.08</v>
       </c>
       <c r="BB2" t="n">
-        <v>210.89</v>
+        <v>210.55</v>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>214.34</t>
+          <t>213.95</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>212.66</t>
+          <t>212.42</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>-58.73</t>
+          <t>-38.74</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>-5.38</v>
+        <v>-5.2</v>
       </c>
       <c r="BG2" t="n">
-        <v>-3.39</v>
+        <v>-3.75</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-133.36</t>
+          <t>-110.47</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
@@ -1257,43 +1257,43 @@
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>626978.0165369649</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>51890.0</t>
+          <t>74023.0</t>
         </is>
       </c>
       <c r="BM2" t="n">
-        <v>113413.8</v>
+        <v>95918.2</v>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>100914.7</t>
+          <t>98420.8</t>
         </is>
       </c>
       <c r="BO2" t="n">
-        <v>91316.48</v>
+        <v>91804.12</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>-2502</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>-213.6640266173075</t>
+          <t>-910.3307307874132</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>-3441.335387722051</t>
+          <t>-4741.997603863623</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>51890.0</t>
+          <t>74023.0</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-14.55</t>
+          <t>-10.45</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>8.14</t>
+          <t>8.53</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
@@ -1398,12 +1398,12 @@
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>190.5</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>197.5</t>
         </is>
       </c>
       <c r="CU2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="CV2" t="inlineStr">
         <is>
-          <t>188.0</t>
+          <t>197.0</t>
         </is>
       </c>
       <c r="CW2" t="inlineStr">
@@ -1458,17 +1458,17 @@
       </c>
       <c r="CZ2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1485,12 +1485,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.31</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>459.0</t>
+          <t>275.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1510,17 +1510,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.061980254487441246</t>
+          <t>0.12385807023159169</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1545,12 +1545,12 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-26.89</t>
+          <t>-27.27</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-48.71</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -1655,22 +1655,22 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-09-18 00:00:00</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>5.97</t>
+          <t>3.58</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-2.11</t>
+          <t>-1.33</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1681,12 +1681,12 @@
       <c r="AP3" t="inlineStr"/>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1696,70 +1696,70 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>-5.26</v>
+        <v>-3.98</v>
       </c>
       <c r="AV3" t="n">
-        <v>-3.38</v>
+        <v>-4.44</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.84</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>199.5</t>
+          <t>195.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>202.95</t>
+          <t>200.1</t>
         </is>
       </c>
       <c r="BA3" t="n">
-        <v>206.48</v>
+        <v>204.9</v>
       </c>
       <c r="BB3" t="n">
-        <v>211.45</v>
+        <v>210.89</v>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>214.86</t>
+          <t>214.34</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>212.99</t>
+          <t>212.66</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-59.27</t>
+          <t>-58.73</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>-4.6</v>
+        <v>-5.38</v>
       </c>
       <c r="BG3" t="n">
-        <v>-2.89</v>
+        <v>-3.39</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-128.46</t>
+          <t>-109.45</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
@@ -1769,43 +1769,43 @@
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>626978.0165369649</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>87239.0</t>
+          <t>51890.0</t>
         </is>
       </c>
       <c r="BM3" t="n">
-        <v>110234.4</v>
+        <v>113413.8</v>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>103800.8</t>
+          <t>100914.7</t>
         </is>
       </c>
       <c r="BO3" t="n">
-        <v>93547.3</v>
+        <v>91316.48</v>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>6433</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>373.1853117653732</t>
+          <t>-213.6640265917386</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>911.0511849056784</t>
+          <t>-3441.335387716579</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>87239.0</t>
+          <t>51890.0</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>-14.09</t>
+          <t>-14.55</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1875,17 +1875,17 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>8.18</t>
+          <t>8.14</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1935,14 +1935,14 @@
       </c>
       <c r="CS3" t="inlineStr">
         <is>
+          <t>189.0</t>
+        </is>
+      </c>
+      <c r="CT3" t="inlineStr">
+        <is>
           <t>191.5</t>
         </is>
       </c>
-      <c r="CT3" t="inlineStr">
-        <is>
-          <t>195.0</t>
-        </is>
-      </c>
       <c r="CU3" t="inlineStr">
         <is>
           <t>187.0</t>
@@ -1950,7 +1950,7 @@
       </c>
       <c r="CV3" t="inlineStr">
         <is>
-          <t>189.0</t>
+          <t>188.0</t>
         </is>
       </c>
       <c r="CW3" t="inlineStr">
@@ -1970,17 +1970,17 @@
       </c>
       <c r="CZ3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="DA3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DB3" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1997,12 +1997,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.75</t>
+          <t>-1.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>689.0</t>
+          <t>459.0</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.86</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.03416690059873792</t>
+          <t>0.061980254487441246</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -2057,12 +2057,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -2082,12 +2082,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -2097,12 +2097,12 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-25.92</t>
+          <t>-26.89</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-48.71</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -2167,22 +2167,22 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-09-18 00:00:00</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>8.97</t>
+          <t>5.97</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-4.70</t>
+          <t>-2.11</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
@@ -2193,12 +2193,12 @@
       <c r="AP4" t="inlineStr"/>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -2208,70 +2208,70 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>3.42</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>-5.48</v>
+        <v>-5.26</v>
       </c>
       <c r="AV4" t="n">
-        <v>-2.36</v>
+        <v>-3.38</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-1.64</t>
+          <t>-1.59</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>202.6</t>
+          <t>199.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>205.4</t>
+          <t>202.95</t>
         </is>
       </c>
       <c r="BA4" t="n">
-        <v>207.5</v>
+        <v>206.48</v>
       </c>
       <c r="BB4" t="n">
-        <v>211.93</v>
+        <v>211.45</v>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>215.46</t>
+          <t>214.86</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>213.47</t>
+          <t>212.99</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>-48.28</t>
+          <t>-59.27</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>-3.65</v>
+        <v>-4.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>-2.46</v>
+        <v>-2.89</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-124.24</t>
+          <t>-108.07</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
@@ -2281,43 +2281,43 @@
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>626978.0165369649</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>133941.0</t>
+          <t>87239.0</t>
         </is>
       </c>
       <c r="BM4" t="n">
-        <v>107572.8</v>
+        <v>110234.4</v>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>104018.8</t>
+          <t>103800.8</t>
         </is>
       </c>
       <c r="BO4" t="n">
-        <v>92696.24000000001</v>
+        <v>93547.3</v>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>6433</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>275.391516648954</t>
+          <t>373.1853117945961</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>3308.815889198639</t>
+          <t>911.0511849119357</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>133941.0</t>
+          <t>87239.0</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>-12.95</t>
+          <t>-14.09</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2382,22 +2382,22 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>8.29</t>
+          <t>8.18</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
@@ -2407,7 +2407,7 @@
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2447,22 +2447,22 @@
       </c>
       <c r="CS4" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CT4" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>195.0</t>
         </is>
       </c>
       <c r="CU4" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="CV4" t="inlineStr">
         <is>
-          <t>191.5</t>
+          <t>189.0</t>
         </is>
       </c>
       <c r="CW4" t="inlineStr">
@@ -2482,17 +2482,17 @@
       </c>
       <c r="CZ4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="DA4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DB4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -2509,12 +2509,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-3.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>663.0</t>
+          <t>689.0</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2534,17 +2534,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.85</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.10430266748674008</t>
+          <t>0.03416690059873792</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-10-17 00:00:00</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2024-10-28 00:00:00</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -2594,12 +2594,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>565.0</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>543.0</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2609,12 +2609,12 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-23.02</t>
+          <t>-25.92</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-48.71</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -2634,7 +2634,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -2679,22 +2679,22 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-09-18 00:00:00</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>8.97</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-4.70</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
@@ -2705,85 +2705,85 @@
       <c r="AP5" t="inlineStr"/>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>382</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>10.26</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>44.44</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>-2.31</v>
+        <v>-5.48</v>
       </c>
       <c r="AV5" t="n">
-        <v>-2.31</v>
+        <v>-2.36</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-1.70</t>
+          <t>-1.64</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>203.7</t>
+          <t>202.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>207.45</t>
+          <t>205.4</t>
         </is>
       </c>
       <c r="BA5" t="n">
-        <v>208.52</v>
+        <v>207.5</v>
       </c>
       <c r="BB5" t="n">
-        <v>212.31</v>
+        <v>211.93</v>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>215.99</t>
+          <t>215.46</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>213.86</t>
+          <t>213.47</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-21.77</t>
+          <t>-48.28</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>-2.64</v>
+        <v>-3.65</v>
       </c>
       <c r="BG5" t="n">
-        <v>-2.16</v>
+        <v>-2.46</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>35.84</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-121.32</t>
+          <t>-106.87</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
@@ -2793,43 +2793,43 @@
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>626978.0165369649</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>132498.0</t>
+          <t>133941.0</t>
         </is>
       </c>
       <c r="BM5" t="n">
-        <v>109702.2</v>
+        <v>107572.8</v>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>99340.7</t>
+          <t>104018.8</t>
         </is>
       </c>
       <c r="BO5" t="n">
-        <v>90783.34</v>
+        <v>92696.24000000001</v>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>3554</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>-276.1401874509887</t>
+          <t>275.3915166823525</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1612.236327860068</t>
+          <t>3308.815889205798</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>132498.0</t>
+          <t>133941.0</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>-9.55</t>
+          <t>-12.95</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2899,17 +2899,17 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>8.61</t>
+          <t>8.29</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.3</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>29.8</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>20.33</t>
         </is>
       </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8993</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2959,22 +2959,22 @@
       </c>
       <c r="CS5" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>200.0</t>
         </is>
       </c>
       <c r="CT5" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>200.5</t>
         </is>
       </c>
       <c r="CU5" t="inlineStr">
         <is>
-          <t>196.5</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CV5" t="inlineStr">
         <is>
-          <t>199.0</t>
+          <t>191.5</t>
         </is>
       </c>
       <c r="CW5" t="inlineStr">
@@ -2994,39 +2994,39 @@
       </c>
       <c r="CZ5" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="DA5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DB5" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>759.0</t>
+          <t>2611.0</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3046,17 +3046,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-12.5</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.009451031971873894</t>
+          <t>-0.08565899577684101</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -3066,37 +3066,37 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-21 00:00:00</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>278.5</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -3121,22 +3121,22 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-18.18</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2025/08/08</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -3146,67 +3146,67 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2025/12/30</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/06/19</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2026/02/06</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2026/01/21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
@@ -3217,131 +3217,131 @@
       <c r="AP6" t="inlineStr"/>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>74.36</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>53.85</t>
+          <t>34.92</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>3.37</v>
+        <v>2.05</v>
       </c>
       <c r="AV6" t="n">
-        <v>-2.29</v>
+        <v>0.68</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-1.48</t>
+          <t>7.49</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-1.76</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>204.6</t>
+          <t>62.42</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>208.5</t>
+          <t>62.83000000000001</t>
         </is>
       </c>
       <c r="BA6" t="n">
-        <v>209.4</v>
+        <v>62</v>
       </c>
       <c r="BB6" t="n">
-        <v>212.55</v>
+        <v>57.68</v>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>216.35</t>
+          <t>55.8</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>214.03</t>
+          <t>56.018</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-14.89</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>-2.07</v>
+        <v>1.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>-2.05</v>
+        <v>1.64</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-120.16</t>
+          <t>-56.82</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>2026/01/28</t>
+          <t>2026/02/04</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>131080.8005836576</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>161501.0</t>
+          <t>166936.0</t>
         </is>
       </c>
       <c r="BM6" t="n">
-        <v>100923.4</v>
+        <v>195895</v>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>99978.5</t>
+          <t>214247.2</t>
         </is>
       </c>
       <c r="BO6" t="n">
-        <v>89322.67999999999</v>
+        <v>199167.84</v>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>-18352</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>-619.481372052999</t>
+          <t>357.8197232057402</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>-714.4214857614716</t>
+          <t>1709.09570053083</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>161501.0</t>
+          <t>166936.0</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -3351,32 +3351,32 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>2026/01/08</t>
+          <t>2026/01/16</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-3.86</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3386,117 +3386,117 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>-45.46523659305993</t>
+          <t>37.85536797433306</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>132.6621367133306</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>132.6621367133306</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>9.16</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>77.26</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>73.42%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>24.70%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>基本輸出入軟體(Insyde H2O)86.26%、基板管理控制器(BMC)韌體13.74% (2024年)</t>
+          <t>電腦,零組件及週邊設備99.30%、其他勞務0.70% (2024年)</t>
         </is>
       </c>
       <c r="CQ6" t="inlineStr">
         <is>
-          <t>系微-資訊服務業-上櫃</t>
+          <t>鑫聯大投控-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
       <c r="CR6" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CS6" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>63.6</t>
         </is>
       </c>
       <c r="CT6" t="inlineStr">
         <is>
-          <t>217.0</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CU6" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CV6" t="inlineStr">
         <is>
-          <t>211.5</t>
+          <t>63.7</t>
         </is>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - BIOS(嵌入式軟體)</t>
+          <t>** 電腦及週邊設備 - 中央處理器、晶片組、面板、顯示器模組、記憶體、主機板、機殼、電源供應器、網路卡、電池、散熱片、風扇馬達、散熱模組、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機、多功能視訊卡、光學鏡片、鏡頭、光碟片、連接線、機構樞紐、金屬、塑膠模具、印表機、傳真機、掃瞄器、多功能事務機、投影機、安全監控系統、其他電腦及週邊設備之零組件</t>
         </is>
       </c>
       <c r="CY6" t="inlineStr">
@@ -3506,39 +3506,39 @@
       </c>
       <c r="CZ6" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="DA6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="DB6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>175.0</t>
+          <t>1901.0</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3558,17 +3558,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.0189267132187396</t>
+          <t>0.07388003004283376</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3578,37 +3578,37 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-21 00:00:00</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>278.5</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3618,12 +3618,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -3633,22 +3633,22 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-20.12</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2025/08/08</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3658,67 +3658,67 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2025/12/30</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/06/19</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2026/02/06</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2026/01/21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>-2.40</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
@@ -3729,131 +3729,131 @@
       <c r="AP7" t="inlineStr"/>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>29.06</t>
+          <t>32.28</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>-0.42</v>
       </c>
       <c r="AV7" t="n">
-        <v>-2.59</v>
+        <v>0.68</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-1.25</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>204.4</t>
+          <t>62.26000000000001</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>207.6</t>
+          <t>62.67</t>
         </is>
       </c>
       <c r="BA7" t="n">
-        <v>209.82</v>
+        <v>61.84</v>
       </c>
       <c r="BB7" t="n">
-        <v>212.48</v>
+        <v>57.51</v>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>216.71</t>
+          <t>55.63</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>214.17</t>
+          <t>55.852</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>-26.43</t>
+          <t>-18.87</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>-2.58</v>
+        <v>1.38</v>
       </c>
       <c r="BG7" t="n">
-        <v>-2.04</v>
+        <v>1.7</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-120.11</t>
+          <t>-55.21</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>2026/01/28</t>
+          <t>2026/02/04</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>131080.8005836576</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>35993.0</t>
+          <t>119213.0</t>
         </is>
       </c>
       <c r="BM7" t="n">
-        <v>88415.60000000001</v>
+        <v>222905.6</v>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>90121.3</t>
+          <t>207570.3</t>
         </is>
       </c>
       <c r="BO7" t="n">
-        <v>86864.48</v>
+        <v>197315.12</v>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-1705</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-602.2195331969131</t>
+          <t>112.1331818739056</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-7120.167595015024</t>
+          <t>5778.226423105458</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>35993.0</t>
+          <t>119213.0</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3863,32 +3863,32 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>2026/01/08</t>
+          <t>2026/01/16</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-6.14</t>
+          <t>-2.97</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3898,117 +3898,117 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>-45.46523659305993</t>
+          <t>37.85536797433306</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>132.6621367133306</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>132.6621367133306</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>8.94</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>77.26</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>73.42%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>24.70%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
         <is>
-          <t>基本輸出入軟體(Insyde H2O)86.26%、基板管理控制器(BMC)韌體13.74% (2024年)</t>
+          <t>電腦,零組件及週邊設備99.30%、其他勞務0.70% (2024年)</t>
         </is>
       </c>
       <c r="CQ7" t="inlineStr">
         <is>
-          <t>系微-資訊服務業-上櫃</t>
+          <t>鑫聯大投控-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
       <c r="CR7" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CS7" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>61.6</t>
         </is>
       </c>
       <c r="CT7" t="inlineStr">
         <is>
-          <t>208.0</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="CU7" t="inlineStr">
         <is>
-          <t>200.5</t>
+          <t>61.1</t>
         </is>
       </c>
       <c r="CV7" t="inlineStr">
         <is>
-          <t>206.5</t>
+          <t>62.0</t>
         </is>
       </c>
       <c r="CW7" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CX7" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - BIOS(嵌入式軟體)</t>
+          <t>** 電腦及週邊設備 - 中央處理器、晶片組、面板、顯示器模組、記憶體、主機板、機殼、電源供應器、網路卡、電池、散熱片、風扇馬達、散熱模組、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機、多功能視訊卡、光學鏡片、鏡頭、光碟片、連接線、機構樞紐、金屬、塑膠模具、印表機、傳真機、掃瞄器、多功能事務機、投影機、安全監控系統、其他電腦及週邊設備之零組件</t>
         </is>
       </c>
       <c r="CY7" t="inlineStr">
@@ -4018,39 +4018,39 @@
       </c>
       <c r="CZ7" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="DA7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="DB7" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>370.0</t>
+          <t>6280.0</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -4070,17 +4070,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.78</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.004265958149052652</t>
+          <t>0.37289616467510384</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -4090,37 +4090,37 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-21 00:00:00</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>278.5</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -4130,12 +4130,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -4145,22 +4145,22 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-20.89</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2025/08/08</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -4170,67 +4170,67 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2025/12/30</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/06/19</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2026/02/06</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2026/01/21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>16.05</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>-10.07</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
@@ -4241,131 +4241,131 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>20.63</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>15.2</t>
+          <t>30.69</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>-0.92</v>
+        <v>-2.63</v>
       </c>
       <c r="AV8" t="n">
-        <v>-1.98</v>
+        <v>2.23</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>7.74</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-2.17</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>206.4</t>
+          <t>63.16</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>207.35</t>
+          <t>62.63</t>
         </is>
       </c>
       <c r="BA8" t="n">
-        <v>210.58</v>
+        <v>61.78</v>
       </c>
       <c r="BB8" t="n">
-        <v>212.51</v>
+        <v>57.35</v>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>217.23</t>
+          <t>55.48</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>214.33</t>
+          <t>55.654</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>-41.22</t>
+          <t>-15.07</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>-2.69</v>
+        <v>1.51</v>
       </c>
       <c r="BG8" t="n">
-        <v>-1.91</v>
+        <v>1.78</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-118.78</t>
+          <t>-53.10</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>2026/01/28</t>
+          <t>2026/02/04</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>131080.8005836576</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>73931.0</t>
+          <t>401415.0</t>
         </is>
       </c>
       <c r="BM8" t="n">
-        <v>97367.2</v>
+        <v>276868.4</v>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>96953.6</t>
+          <t>201667.4</t>
         </is>
       </c>
       <c r="BO8" t="n">
-        <v>87094.67999999999</v>
+        <v>196168.7</v>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>413</t>
+          <t>75201</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>582.861932588198</t>
+          <t>-918.065589259104</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-2569.656051269558</t>
+          <t>16498.08365452974</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>73931.0</t>
+          <t>401415.0</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -4375,32 +4375,32 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>2026/01/08</t>
+          <t>2026/01/16</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-7.05</t>
+          <t>-3.76</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4410,117 +4410,117 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-45.46523659305993</t>
+          <t>37.85536797433306</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>132.6621367133306</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>132.6621367133306</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>8.85</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>77.26</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>73.42%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>24.70%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
         <is>
-          <t>基本輸出入軟體(Insyde H2O)86.26%、基板管理控制器(BMC)韌體13.74% (2024年)</t>
+          <t>電腦,零組件及週邊設備99.30%、其他勞務0.70% (2024年)</t>
         </is>
       </c>
       <c r="CQ8" t="inlineStr">
         <is>
-          <t>系微-資訊服務業-上櫃</t>
+          <t>鑫聯大投控-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
       <c r="CR8" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CS8" t="inlineStr">
         <is>
-          <t>200.0</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CT8" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>68.2</t>
         </is>
       </c>
       <c r="CU8" t="inlineStr">
         <is>
-          <t>194.0</t>
+          <t>61.0</t>
         </is>
       </c>
       <c r="CV8" t="inlineStr">
         <is>
-          <t>204.5</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="CW8" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CX8" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - BIOS(嵌入式軟體)</t>
+          <t>** 電腦及週邊設備 - 中央處理器、晶片組、面板、顯示器模組、記憶體、主機板、機殼、電源供應器、網路卡、電池、散熱片、風扇馬達、散熱模組、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機、多功能視訊卡、光學鏡片、鏡頭、光碟片、連接線、機構樞紐、金屬、塑膠模具、印表機、傳真機、掃瞄器、多功能事務機、投影機、安全監控系統、其他電腦及週邊設備之零組件</t>
         </is>
       </c>
       <c r="CY8" t="inlineStr">
@@ -4530,39 +4530,39 @@
       </c>
       <c r="CZ8" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="DA8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="DB8" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>3709</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.16</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>739.0</t>
+          <t>1919.0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4582,17 +4582,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.79</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.01342629859845986</t>
+          <t>0.4267002393777195</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4602,37 +4602,37 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2026-02-06 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-08 00:00:00</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-21 00:00:00</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>278.5</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -4657,22 +4657,22 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-23.79</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.46</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2025/08/08</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>38.65</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4682,67 +4682,67 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2025/12/30</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>49.9</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/06/19</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2026/02/06</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>61.7</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2026/01/21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>58.1</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-02-04 00:00:00</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>4.91</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-1.71</t>
+          <t>-1.25</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
@@ -4753,131 +4753,131 @@
       <c r="AP9" t="inlineStr"/>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>2611</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>47.62</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>21.43</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>-5.38</v>
+        <v>-1</v>
       </c>
       <c r="AV9" t="n">
-        <v>-1.35</v>
+        <v>3.4</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>7.92</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-2.50</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>208.2</t>
+          <t>63.84000000000001</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>207.55</t>
+          <t>62.56999999999999</t>
         </is>
       </c>
       <c r="BA9" t="n">
-        <v>211.05</v>
+        <v>61.74</v>
       </c>
       <c r="BB9" t="n">
-        <v>212.45</v>
+        <v>57.21</v>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>217.89</t>
+          <t>55.38</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>214.7</t>
+          <t>55.39400000000001</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>-51.56</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>-2.59</v>
+        <v>1.71</v>
       </c>
       <c r="BG9" t="n">
-        <v>-1.71</v>
+        <v>1.85</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>3.8</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-116.84</t>
+          <t>-51.33</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>2026/01/28</t>
+          <t>2026/02/04</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>131080.8005836576</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>144588.0</t>
+          <t>121650.0</t>
         </is>
       </c>
       <c r="BM9" t="n">
-        <v>100464.8</v>
+        <v>252765.2</v>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>99133.8</t>
+          <t>177167.7</t>
         </is>
       </c>
       <c r="BO9" t="n">
-        <v>86851.22</v>
+        <v>190093.06</v>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>75597</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>1156.047020562335</t>
+          <t>-4084.638179038893</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-41.93755837355275</t>
+          <t>987.0195689026441</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>144588.0</t>
+          <t>121650.0</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>2026/01/08</t>
+          <t>2026/01/16</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-10.45</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4922,117 +4922,117 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.03</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-45.46523659305993</t>
+          <t>37.85536797433306</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>132.6621367133306</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>132.6621367133306</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>8.53</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>77.26</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>14.78</t>
         </is>
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>73.42%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>24.70%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>49.79</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>7999</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
         <is>
-          <t>基本輸出入軟體(Insyde H2O)86.26%、基板管理控制器(BMC)韌體13.74% (2024年)</t>
+          <t>電腦,零組件及週邊設備99.30%、其他勞務0.70% (2024年)</t>
         </is>
       </c>
       <c r="CQ9" t="inlineStr">
         <is>
-          <t>系微-資訊服務業-上櫃</t>
+          <t>鑫聯大投控-電腦及週邊設備業-上櫃</t>
         </is>
       </c>
       <c r="CR9" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
+          <t>電腦及週邊設備業右上上櫃</t>
         </is>
       </c>
       <c r="CS9" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CT9" t="inlineStr">
         <is>
-          <t>205.5</t>
+          <t>64.7</t>
         </is>
       </c>
       <c r="CU9" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>62.5</t>
         </is>
       </c>
       <c r="CV9" t="inlineStr">
         <is>
-          <t>197.0</t>
+          <t>63.2</t>
         </is>
       </c>
       <c r="CW9" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>25.05</t>
         </is>
       </c>
       <c r="CX9" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - BIOS(嵌入式軟體)</t>
+          <t>** 電腦及週邊設備 - 中央處理器、晶片組、面板、顯示器模組、記憶體、主機板、機殼、電源供應器、網路卡、電池、散熱片、風扇馬達、散熱模組、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、工業電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機、多功能視訊卡、光學鏡片、鏡頭、光碟片、連接線、機構樞紐、金屬、塑膠模具、印表機、傳真機、掃瞄器、多功能事務機、投影機、安全監控系統、其他電腦及週邊設備之零組件</t>
         </is>
       </c>
       <c r="CY9" t="inlineStr">
@@ -5042,39 +5042,39 @@
       </c>
       <c r="CZ9" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="DA9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5</t>
         </is>
       </c>
       <c r="DB9" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-2.7</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>433.0</t>
+          <t>6095.678</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>509.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5094,17 +5094,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-0.045206621591315235</t>
+          <t>0.11136116639555242</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -5114,37 +5114,37 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-10-27 00:00:00</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-11-03 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04 00:00:00</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-13 00:00:00</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>278.5</t>
+          <t>714.0</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665.0</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -5169,92 +5169,92 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-21.28</t>
+          <t>-26.34</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2025/05/21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>628.0</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/07/22</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2026/01/16</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>510.0</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2025/12/18</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>554.0</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>28.17</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-2.21</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
@@ -5265,131 +5265,131 @@
       <c r="AP10" t="inlineStr"/>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>7.14</t>
+          <t>35.85</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>54.76</t>
+          <t>75.28</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>-3.65</v>
+        <v>-0.93</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0.31</v>
+        <v>1.22</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>-5.94</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-6.84</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>211.2</t>
+          <t>513.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>208.8</t>
+          <t>506.95</t>
         </is>
       </c>
       <c r="BA10" t="n">
-        <v>211.85</v>
+        <v>507.62</v>
       </c>
       <c r="BB10" t="n">
-        <v>212.62</v>
+        <v>539.71</v>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>218.66</t>
+          <t>579.34</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>214.95</t>
+          <t>567.64</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>35.52</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>-1.66</v>
+        <v>-7.32</v>
       </c>
       <c r="BG10" t="n">
-        <v>-1.49</v>
+        <v>-11.35</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-114.67</t>
+          <t>-150.55</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>2026/01/28</t>
+          <t>2026/01/23</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>3780357993.411479</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>88604.0</t>
+          <t>3113957769.0</t>
         </is>
       </c>
       <c r="BM10" t="n">
-        <v>88979.2</v>
+        <v>2378551525</v>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>93192.1</t>
+          <t>2140214717.7</t>
         </is>
       </c>
       <c r="BO10" t="n">
-        <v>85249.28</v>
+        <v>2809088593.4</v>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-4212</t>
+          <t>238336807</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>1373.862398550679</t>
+          <t>-119401736.0075471</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>-3999.806227151654</t>
+          <t>29670462.41584921</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>88604.0</t>
+          <t>3113957769.0</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -5399,152 +5399,152 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>2026/01/08</t>
+          <t>2025/09/17</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-7.50</t>
+          <t>-24.37</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-45.46523659305993</t>
+          <t>-2.548050505936548</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>79.97334237021313</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>79.97334237021313</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議留意風險&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;4&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>8.81</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>269.64</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>73.42%</t>
+          <t>14.33%</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
         <is>
-          <t>24.70%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>378065</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
         <is>
-          <t>基本輸出入軟體(Insyde H2O)86.26%、基板管理控制器(BMC)韌體13.74% (2024年)</t>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
         </is>
       </c>
       <c r="CQ10" t="inlineStr">
         <is>
-          <t>系微-資訊服務業-上櫃</t>
+          <t>華碩-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CR10" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CS10" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>518.0</t>
         </is>
       </c>
       <c r="CT10" t="inlineStr">
         <is>
-          <t>209.5</t>
+          <t>518.0</t>
         </is>
       </c>
       <c r="CU10" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>507.0</t>
         </is>
       </c>
       <c r="CV10" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>509.0</t>
         </is>
       </c>
       <c r="CW10" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>346.61</t>
         </is>
       </c>
       <c r="CX10" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - BIOS(嵌入式軟體)</t>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
         </is>
       </c>
       <c r="CY10" t="inlineStr">
@@ -5554,39 +5554,39 @@
       </c>
       <c r="CZ10" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="DA10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DB10" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-0.57</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>463.0</t>
+          <t>3814.39</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>523.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5606,17 +5606,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-11.97</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.032184904779374975</t>
+          <t>0.08897092306775929</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5626,37 +5626,37 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-10-27 00:00:00</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-11-03 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04 00:00:00</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-13 00:00:00</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>278.5</t>
+          <t>714.0</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -5681,22 +5681,22 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-18.57</t>
+          <t>-24.31</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2025/05/21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>628.0</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -5706,67 +5706,67 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/07/22</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2026/01/16</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>510.0</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2025/12/18</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>554.0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>17.63</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>-3.80</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
@@ -5777,131 +5777,131 @@
       <c r="AP11" t="inlineStr"/>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>57.14</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>85.71</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>-0.89</v>
+        <v>2.07</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0.09</v>
+        <v>0.82</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.17</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-3.06</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>212.4</t>
+          <t>512.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>209.4</t>
+          <t>506.75</t>
         </is>
       </c>
       <c r="BA11" t="n">
-        <v>212.6</v>
+        <v>508.22</v>
       </c>
       <c r="BB11" t="n">
-        <v>212.6</v>
+        <v>541.67</v>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>219.32</t>
+          <t>581.56</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>215.3</t>
+          <t>570.64</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>-1.11</v>
+        <v>-7.72</v>
       </c>
       <c r="BG11" t="n">
-        <v>-1.45</v>
+        <v>-12.36</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-114.25</t>
+          <t>-155.04</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>2026/01/28</t>
+          <t>2026/01/23</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>3780357993.411479</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>98962.0</t>
+          <t>1994588280.0</t>
         </is>
       </c>
       <c r="BM11" t="n">
-        <v>99033.60000000001</v>
+        <v>2182504120.2</v>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>95945.6</t>
+          <t>2004189527.9</t>
         </is>
       </c>
       <c r="BO11" t="n">
-        <v>84954.17999999999</v>
+        <v>2771381376.72</v>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>178314592</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>2350.893057769284</t>
+          <t>-146505772.0845282</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>-3512.768388722077</t>
+          <t>-54592547.13532424</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>98962.0</t>
+          <t>1994588280.0</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5911,152 +5911,152 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>2026/01/08</t>
+          <t>2025/09/17</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-22.29</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-45.46523659305993</t>
+          <t>-2.548050505936548</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>79.97334237021313</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>79.97334237021313</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>9.11</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>269.64</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>73.42%</t>
+          <t>14.33%</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>24.70%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>378065</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
         <is>
-          <t>基本輸出入軟體(Insyde H2O)86.26%、基板管理控制器(BMC)韌體13.74% (2024年)</t>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
         </is>
       </c>
       <c r="CQ11" t="inlineStr">
         <is>
-          <t>系微-資訊服務業-上櫃</t>
+          <t>華碩-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CR11" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CS11" t="inlineStr">
         <is>
-          <t>219.0</t>
+          <t>525.0</t>
         </is>
       </c>
       <c r="CT11" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>526.0</t>
         </is>
       </c>
       <c r="CU11" t="inlineStr">
         <is>
-          <t>209.0</t>
+          <t>517.0</t>
         </is>
       </c>
       <c r="CV11" t="inlineStr">
         <is>
-          <t>210.5</t>
+          <t>523.0</t>
         </is>
       </c>
       <c r="CW11" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>346.61</t>
         </is>
       </c>
       <c r="CX11" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - BIOS(嵌入式軟體)</t>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
         </is>
       </c>
       <c r="CY11" t="inlineStr">
@@ -6066,39 +6066,39 @@
       </c>
       <c r="CZ11" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="DA11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DB11" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b2】</t>
+          <t>【d2】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>374.0</t>
+          <t>5244.16</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>526.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6118,17 +6118,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-15.16</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-0.20403482493915</t>
+          <t>0.019365873085243165</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -6138,37 +6138,37 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-90.0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2025-10-27 00:00:00</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-09-25 00:00:00</t>
+          <t>2025-11-03 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04 00:00:00</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-13 00:00:00</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>278.5</t>
+          <t>714.0</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -6178,12 +6178,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -6193,22 +6193,22 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-16.25</t>
+          <t>-23.88</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025/09/10</t>
+          <t>2025/05/21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>258.5</t>
+          <t>628.0</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -6218,67 +6218,67 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>2025/10/29</t>
+          <t>2025/07/22</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2026/01/30</t>
+          <t>2026/01/16</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>203.5</t>
+          <t>510.0</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>2026/01/15</t>
+          <t>2025/12/18</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>554.0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2025-09-17 00:00:00</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>4.87</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
@@ -6289,12 +6289,12 @@
       <c r="AP12" t="inlineStr"/>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>275</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -6304,116 +6304,116 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>78.57</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0.93</v>
+        <v>-0.05</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-6.91</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>210.8</t>
+          <t>508.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>209.7</t>
+          <t>505.45</t>
         </is>
       </c>
       <c r="BA12" t="n">
-        <v>212.78</v>
+        <v>508.48</v>
       </c>
       <c r="BB12" t="n">
-        <v>212.39</v>
+        <v>543.27</v>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>220.01</t>
+          <t>583.58</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>215.68</t>
+          <t>573.88</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>27.54</t>
+          <t>29.35</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>-1.11</v>
+        <v>-9.550000000000001</v>
       </c>
       <c r="BG12" t="n">
-        <v>-1.53</v>
+        <v>-13.52</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-115.07</t>
+          <t>-160.20</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>2026/01/28</t>
+          <t>2026/01/23</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>325411.1518987342</t>
+          <t>3780357993.411479</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>80751.0</t>
+          <t>2723833443.0</t>
         </is>
       </c>
       <c r="BM12" t="n">
-        <v>91827</v>
+        <v>2030500053.8</v>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>115365.6</t>
+          <t>1991924693.0</t>
         </is>
       </c>
       <c r="BO12" t="n">
-        <v>86518.78</v>
+        <v>2759808411.68</v>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>-23538</t>
+          <t>38575360</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>3417.013320767714</t>
+          <t>-163217267.529838</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>-3801.329748511169</t>
+          <t>-53086095.98931026</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>80751.0</t>
+          <t>2723833443.0</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -6423,62 +6423,62 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>220.0</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>2026/01/08</t>
+          <t>2025/09/17</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>-1.59</t>
+          <t>-21.84</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>系微</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>資訊服務業</t>
+          <t>電腦及週邊設備業</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>上櫃</t>
+          <t>上市</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>-45.46523659305993</t>
+          <t>-2.548050505936548</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>79.97334237021313</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>-7.251017219770976</t>
+          <t>79.97334237021313</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -6488,87 +6488,87 @@
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>9.37</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>9.34</t>
+          <t>269.64</t>
         </is>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
-          <t>28.44</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>73.42%</t>
+          <t>14.33%</t>
         </is>
       </c>
       <c r="CM12" t="inlineStr">
         <is>
-          <t>24.70%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="CN12" t="inlineStr">
         <is>
-          <t>20.08</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>378065</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">
         <is>
-          <t>基本輸出入軟體(Insyde H2O)86.26%、基板管理控制器(BMC)韌體13.74% (2024年)</t>
+          <t>電腦產品60.00%、零組件及其他40.00% (2024年)</t>
         </is>
       </c>
       <c r="CQ12" t="inlineStr">
         <is>
-          <t>系微-資訊服務業-上櫃</t>
+          <t>華碩-電腦及週邊設備業-上市</t>
         </is>
       </c>
       <c r="CR12" t="inlineStr">
         <is>
-          <t>資訊服務業右下上櫃</t>
+          <t>電腦及週邊設備業右下上市</t>
         </is>
       </c>
       <c r="CS12" t="inlineStr">
         <is>
-          <t>216.0</t>
+          <t>508.0</t>
         </is>
       </c>
       <c r="CT12" t="inlineStr">
         <is>
-          <t>219.5</t>
+          <t>530.0</t>
         </is>
       </c>
       <c r="CU12" t="inlineStr">
         <is>
-          <t>213.5</t>
+          <t>506.0</t>
         </is>
       </c>
       <c r="CV12" t="inlineStr">
         <is>
-          <t>216.5</t>
+          <t>526.0</t>
         </is>
       </c>
       <c r="CW12" t="inlineStr">
         <is>
-          <t>23.1</t>
+          <t>346.61</t>
         </is>
       </c>
       <c r="CX12" t="inlineStr">
         <is>
-          <t>** 電腦及週邊設備 - BIOS(嵌入式軟體)</t>
+          <t>** 電腦及週邊設備 - 主機板、網路卡、輸出入模組/介面卡、顯示卡、硬碟機、光碟機、磁碟儲存系統、BIOS(嵌入式軟體)、筆記型電腦、桌上型電腦、精簡型電腦、伺服器、其他電腦及週邊設備、隨身碟、記憶卡讀卡機** 通信網路 - 網路設備(如數據機、網路卡、閘道器、路由器、網路電話)、無線通訊設備(如行動電話、衛星定位系統、衛星通訊設備、微波通訊設備、數位機上盒)** 人工智慧 - 智慧設備、移動控制** 運動科技 - 穿戴式裝置</t>
         </is>
       </c>
       <c r="CY12" t="inlineStr">
@@ -6578,22 +6578,26 @@
       </c>
       <c r="CZ12" t="inlineStr">
         <is>
-          <t>7.0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="DA12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="DB12" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>2357</t>
@@ -6601,12 +6605,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3829.784</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6616,7 +6620,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>503.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6626,17 +6630,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.03553361705804612</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -6646,37 +6650,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-65.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-27 00:00:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-03 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-04 00:00:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-08-13 00:00:00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>714.0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>691.0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -6686,12 +6690,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>665.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>640.0</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -6701,227 +6705,227 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-27.21</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11.56</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/05/21</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>628.0</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/11/18</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>563.0</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/07/22</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>623.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026/01/16</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>510.0</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/12/18</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>554.0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-01-13 00:00:00</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17.70</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr"/>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>125</t>
+          <t>254</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3814</t>
+          <t>6096</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>50.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>59.52</t>
         </is>
       </c>
       <c r="AU13" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="AV13" t="n">
-        <v>0</v>
+        <v>-0.96</v>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.74</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.97</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>503.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>503.25</t>
         </is>
       </c>
       <c r="BA13" t="n">
-        <v>0</v>
+        <v>508.08</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>544.77</v>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>585.57</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>576.96</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.95</t>
         </is>
       </c>
       <c r="BF13" t="n">
-        <v>0</v>
+        <v>-12.05</v>
       </c>
       <c r="BG13" t="n">
-        <v>0</v>
+        <v>-14.51</v>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.46</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-164.62</t>
         </is>
       </c>
       <c r="BJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2026/01/23</t>
         </is>
       </c>
       <c r="BK13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3780357993.411479</t>
         </is>
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1933827594.0</t>
         </is>
       </c>
       <c r="BM13" t="n">
-        <v>0</v>
+        <v>1805733402.4</v>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1872261630.2</t>
         </is>
       </c>
       <c r="BO13" t="n">
-        <v>0</v>
+        <v>2746474603.92</v>
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-66528227</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-183241116.900843</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-127171501.2453866</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1933827594.0</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -6931,17 +6935,17 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>673.0</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025/09/17</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-25.26</t>
         </is>
       </c>
       <c r="BX13" t="inlineStr">
@@ -6986,7 +6990,7 @@
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6996,12 +7000,12 @@
       </c>
       <c r="CH13" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="CI13" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
@@ -7011,7 +7015,7 @@
       </c>
       <c r="CK13" t="inlineStr">
         <is>
-          <t>11.17</t>
+          <t>10.87</t>
         </is>
       </c>
       <c r="CL13" t="inlineStr">
@@ -7026,12 +7030,12 @@
       </c>
       <c r="CN13" t="inlineStr">
         <is>
-          <t>27.03</t>
+          <t>27.51</t>
         </is>
       </c>
       <c r="CO13" t="inlineStr">
         <is>
-          <t>388463</t>
+          <t>378065</t>
         </is>
       </c>
       <c r="CP13" t="inlineStr">
@@ -7051,22 +7055,22 @@
       </c>
       <c r="CS13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>513.0</t>
         </is>
       </c>
       <c r="CT13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>513.0</t>
         </is>
       </c>
       <c r="CU13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>502.0</t>
         </is>
       </c>
       <c r="CV13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>503.0</t>
         </is>
       </c>
       <c r="CW13" t="inlineStr">
@@ -7086,7 +7090,7 @@
       </c>
       <c r="CZ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="DA13" t="inlineStr">
@@ -7096,7 +7100,7 @@
       </c>
       <c r="DB13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
